--- a/tame_output/ON/bt/strategyON_20240413.xlsx
+++ b/tame_output/ON/bt/strategyON_20240413.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>51.4%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>68.1%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>69.2%</t>
+          <t>64.9%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.5%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-17.5%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.8%</t>
+          <t>-11.5%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>54.3%</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>60.2%</t>
+          <t>58.0%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>23.0%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.2%</t>
+          <t>-78.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>118.5%</t>
+          <t>117.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>138.1%</t>
+          <t>137.2%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>97.6%</t>
+          <t>97.3%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>29.0%</t>
+          <t>28.8%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-56.7%</t>
+          <t>-56.3%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.2%</t>
+          <t>-73.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>98.3%</t>
+          <t>97.9%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>498.3%</t>
+          <t>491.2%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>6.5%</t>
+          <t>8.6%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-531.6%</t>
+          <t>-531.2%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>16.0%</t>
+          <t>16.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>65.9%</t>
+          <t>65.6%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>46.1%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-44.3%</t>
+          <t>-44.0%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>13.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>46.1%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-10.3%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>73.0%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-213.2%</t>
+          <t>-213.0%</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-28.9%</t>
+          <t>-28.2%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>71.5%</t>
+          <t>70.5%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>72.2%</t>
+          <t>71.0%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>69.9%</t>
+          <t>69.3%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-306.6%</t>
+          <t>-296.3%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-37.8%</t>
+          <t>-37.2%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-21.8%</t>
+          <t>-21.0%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>58.5%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>34.5%</t>
+          <t>27.7%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-152.2%</t>
+          <t>-152.9%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-243.7%</t>
+          <t>-243.2%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>52.6%</t>
+          <t>53.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>51.6%</t>
+          <t>51.1%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.4%</t>
+          <t>62.7%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>41.6%</t>
+          <t>41.4%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>97.9%</t>
+          <t>97.7%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-184.4%</t>
+          <t>-178.1%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1466,27 +1466,27 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-32.6%</t>
+          <t>-32.1%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>49.2%</t>
+          <t>47.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.1%</t>
+          <t>42.7%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1496,17 +1496,17 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.1%</t>
+          <t>-16.1%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.0%</t>
+          <t>34.7%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-146.7%</t>
+          <t>-146.5%</t>
         </is>
       </c>
     </row>
@@ -43733,16 +43733,16 @@
         <v>3.13991794227561</v>
       </c>
       <c r="D1834" t="n">
-        <v>0.858629459151194</v>
+        <v>0.9621230735079426</v>
       </c>
       <c r="E1834" t="n">
-        <v>3.483013301622341</v>
+        <v>3.52441074736504</v>
       </c>
       <c r="F1834" t="n">
-        <v>1.880332741705669</v>
+        <v>1.983826356062417</v>
       </c>
       <c r="G1834" t="n">
-        <v>4.268117587299011</v>
+        <v>4.330213755913061</v>
       </c>
     </row>
     <row r="1835">
@@ -43756,16 +43756,16 @@
         <v>3.138175778137954</v>
       </c>
       <c r="D1835" t="n">
-        <v>0.8580776593093818</v>
+        <v>0.9615712736661304</v>
       </c>
       <c r="E1835" t="n">
-        <v>3.48105041754796</v>
+        <v>3.52244786329066</v>
       </c>
       <c r="F1835" t="n">
-        <v>1.881174505190975</v>
+        <v>1.984668119547724</v>
       </c>
       <c r="G1835" t="n">
-        <v>4.26688048125254</v>
+        <v>4.328976649866589</v>
       </c>
     </row>
     <row r="1836">
@@ -43779,16 +43779,16 @@
         <v>3.118001050765402</v>
       </c>
       <c r="D1836" t="n">
-        <v>0.7523907713670821</v>
+        <v>0.8558843857238307</v>
       </c>
       <c r="E1836" t="n">
-        <v>3.418600934998487</v>
+        <v>3.459998380741187</v>
       </c>
       <c r="F1836" t="n">
-        <v>1.866613431488292</v>
+        <v>1.97010704584504</v>
       </c>
       <c r="G1836" t="n">
-        <v>4.237969109658377</v>
+        <v>4.300065278272426</v>
       </c>
     </row>
     <row r="1837">
@@ -43802,16 +43802,16 @@
         <v>3.118490189491276</v>
       </c>
       <c r="D1837" t="n">
-        <v>0.7582401524823265</v>
+        <v>0.8617337668390751</v>
       </c>
       <c r="E1837" t="n">
-        <v>3.421429826170459</v>
+        <v>3.462827271913159</v>
       </c>
       <c r="F1837" t="n">
-        <v>1.866613431488292</v>
+        <v>1.97010704584504</v>
       </c>
       <c r="G1837" t="n">
-        <v>4.238458248384251</v>
+        <v>4.300554416998301</v>
       </c>
     </row>
     <row r="1838">
@@ -43825,16 +43825,16 @@
         <v>3.122570172112943</v>
       </c>
       <c r="D1838" t="n">
-        <v>0.7100178856352429</v>
+        <v>0.8135114999919916</v>
       </c>
       <c r="E1838" t="n">
-        <v>3.406220902053293</v>
+        <v>3.447618347795992</v>
       </c>
       <c r="F1838" t="n">
-        <v>1.818391164641208</v>
+        <v>1.921884778997957</v>
       </c>
       <c r="G1838" t="n">
-        <v>4.213604870897668</v>
+        <v>4.275701039511717</v>
       </c>
     </row>
     <row r="1839">
@@ -43848,16 +43848,16 @@
         <v>3.157511256610484</v>
       </c>
       <c r="D1839" t="n">
-        <v>0.4728863937854478</v>
+        <v>0.5763800081421965</v>
       </c>
       <c r="E1839" t="n">
-        <v>3.346309389810916</v>
+        <v>3.387706835553616</v>
       </c>
       <c r="F1839" t="n">
-        <v>1.818391164641208</v>
+        <v>1.921884778997957</v>
       </c>
       <c r="G1839" t="n">
-        <v>4.24854595539521</v>
+        <v>4.310642124009259</v>
       </c>
     </row>
     <row r="1840">
@@ -43871,16 +43871,16 @@
         <v>3.156088696795822</v>
       </c>
       <c r="D1840" t="n">
-        <v>0.4779239845130344</v>
+        <v>0.5814175988697829</v>
       </c>
       <c r="E1840" t="n">
-        <v>3.346901866287289</v>
+        <v>3.388299312029988</v>
       </c>
       <c r="F1840" t="n">
-        <v>1.874035620907526</v>
+        <v>1.977529235264274</v>
       </c>
       <c r="G1840" t="n">
-        <v>4.280510069340338</v>
+        <v>4.342606237954387</v>
       </c>
     </row>
     <row r="1841">
@@ -43894,16 +43894,16 @@
         <v>3.13483507841956</v>
       </c>
       <c r="D1841" t="n">
-        <v>0.4214543533367376</v>
+        <v>0.5249479676934862</v>
       </c>
       <c r="E1841" t="n">
-        <v>3.303060395440507</v>
+        <v>3.344457841183207</v>
       </c>
       <c r="F1841" t="n">
-        <v>1.817565989731229</v>
+        <v>1.921059604087977</v>
       </c>
       <c r="G1841" t="n">
-        <v>4.225374672258297</v>
+        <v>4.287470840872346</v>
       </c>
     </row>
     <row r="1842">
@@ -43917,16 +43917,16 @@
         <v>3.13585268755003</v>
       </c>
       <c r="D1842" t="n">
-        <v>0.3556869632873255</v>
+        <v>0.4591805776440741</v>
       </c>
       <c r="E1842" t="n">
-        <v>3.277771048551212</v>
+        <v>3.319168494293912</v>
       </c>
       <c r="F1842" t="n">
-        <v>1.817565989731229</v>
+        <v>1.921059604087977</v>
       </c>
       <c r="G1842" t="n">
-        <v>4.226392281388767</v>
+        <v>4.288488450002816</v>
       </c>
     </row>
     <row r="1843">
@@ -43940,16 +43940,16 @@
         <v>3.126480719537785</v>
       </c>
       <c r="D1843" t="n">
-        <v>0.3421514795106159</v>
+        <v>0.4456450938673645</v>
       </c>
       <c r="E1843" t="n">
-        <v>3.262984887028284</v>
+        <v>3.304382332770984</v>
       </c>
       <c r="F1843" t="n">
-        <v>1.817565989731229</v>
+        <v>1.921059604087977</v>
       </c>
       <c r="G1843" t="n">
-        <v>4.217020313376523</v>
+        <v>4.279116481990572</v>
       </c>
     </row>
     <row r="1844">
@@ -43963,16 +43963,16 @@
         <v>3.116563445493024</v>
       </c>
       <c r="D1844" t="n">
-        <v>0.2603795790828642</v>
+        <v>0.3638731934396128</v>
       </c>
       <c r="E1844" t="n">
-        <v>3.220358852812422</v>
+        <v>3.261756298555122</v>
       </c>
       <c r="F1844" t="n">
-        <v>1.844601563137365</v>
+        <v>1.948095177494114</v>
       </c>
       <c r="G1844" t="n">
-        <v>4.223324383375443</v>
+        <v>4.285420551989492</v>
       </c>
     </row>
     <row r="1845">
@@ -43986,16 +43986,16 @@
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>0.1931704712109866</v>
+        <v>0.2966640855677352</v>
       </c>
       <c r="E1845" t="n">
-        <v>3.198240526497373</v>
+        <v>3.239637972240073</v>
       </c>
       <c r="F1845" t="n">
-        <v>1.844601563137365</v>
+        <v>1.948095177494114</v>
       </c>
       <c r="G1845" t="n">
-        <v>4.228089700209145</v>
+        <v>4.290185868823194</v>
       </c>
     </row>
     <row r="1846">
@@ -44009,16 +44009,16 @@
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>0.1971619240061768</v>
+        <v>0.3006555383629254</v>
       </c>
       <c r="E1846" t="n">
-        <v>3.19766190373469</v>
+        <v>3.239059349477389</v>
       </c>
       <c r="F1846" t="n">
-        <v>1.848593015932555</v>
+        <v>1.952086630289304</v>
       </c>
       <c r="G1846" t="n">
-        <v>4.228309368005499</v>
+        <v>4.290405536619549</v>
       </c>
     </row>
     <row r="1847">
@@ -44032,16 +44032,16 @@
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-0.2205920995406602</v>
+        <v>-0.1170984851839116</v>
       </c>
       <c r="E1847" t="n">
-        <v>3.028487185821018</v>
+        <v>3.069884631563717</v>
       </c>
       <c r="F1847" t="n">
-        <v>1.430838992385719</v>
+        <v>1.534332606742467</v>
       </c>
       <c r="G1847" t="n">
-        <v>3.975583845382461</v>
+        <v>4.03768001399651</v>
       </c>
     </row>
     <row r="1848">
@@ -44055,16 +44055,16 @@
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-0.4422140330987777</v>
+        <v>-0.3387204187420291</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.939704628996693</v>
+        <v>2.981102074739392</v>
       </c>
       <c r="F1848" t="n">
-        <v>1.393312858698349</v>
+        <v>1.496806473055098</v>
       </c>
       <c r="G1848" t="n">
-        <v>3.952934381768961</v>
+        <v>4.01503055038301</v>
       </c>
     </row>
     <row r="1849">
@@ -44078,16 +44078,16 @@
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-0.6502180914518549</v>
+        <v>-0.5467244770951063</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.861395150209387</v>
+        <v>2.902792595952087</v>
       </c>
       <c r="F1849" t="n">
-        <v>1.393312858698349</v>
+        <v>1.496806473055098</v>
       </c>
       <c r="G1849" t="n">
-        <v>3.957826526322886</v>
+        <v>4.019922694936936</v>
       </c>
     </row>
     <row r="1850">
@@ -44101,16 +44101,16 @@
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-0.9206180541607403</v>
+        <v>-0.8171244398039916</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.748316621463821</v>
+        <v>2.78971406720652</v>
       </c>
       <c r="F1850" t="n">
-        <v>1.122912895989464</v>
+        <v>1.226406510346213</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.790668005035543</v>
+        <v>3.852764173649592</v>
       </c>
     </row>
     <row r="1851">
@@ -44124,16 +44124,16 @@
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-1.259776431749262</v>
+        <v>-1.156282817392514</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.605737569734861</v>
+        <v>2.647135015477561</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.783754518400942</v>
+        <v>0.8872481327576904</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.580257277788879</v>
+        <v>3.642353446402928</v>
       </c>
     </row>
     <row r="1852">
@@ -44147,16 +44147,16 @@
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-1.587793653476741</v>
+        <v>-1.484300039119993</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.494868970782638</v>
+        <v>2.536266416525337</v>
       </c>
       <c r="F1852" t="n">
-        <v>0.4557372966734629</v>
+        <v>0.5592309110302113</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.40378523449116</v>
+        <v>3.465881403105209</v>
       </c>
     </row>
     <row r="1853">
@@ -44170,16 +44170,16 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.081118525011919</v>
+        <v>-1.977624910655171</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.305637772577136</v>
+        <v>2.347035218319835</v>
       </c>
       <c r="F1853" t="n">
-        <v>0.3507511824338441</v>
+        <v>0.4542447967905925</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.348892316355957</v>
+        <v>3.410988484970006</v>
       </c>
     </row>
     <row r="1854">
@@ -44193,16 +44193,16 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-2.573503553036016</v>
+        <v>-2.470009938679268</v>
       </c>
       <c r="E1854" t="n">
-        <v>2.109790153411229</v>
+        <v>2.151187599153928</v>
       </c>
       <c r="F1854" t="n">
-        <v>-0.1416338455902526</v>
+        <v>-0.03814023123350418</v>
       </c>
       <c r="G1854" t="n">
-        <v>3.054567691585231</v>
+        <v>3.11666386019928</v>
       </c>
     </row>
     <row r="1855">
@@ -44216,16 +44216,16 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-2.958683943966089</v>
+        <v>-2.85519032960934</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.954260535852063</v>
+        <v>1.995657981594762</v>
       </c>
       <c r="F1855" t="n">
-        <v>-0.1416338455902526</v>
+        <v>-0.03814023123350418</v>
       </c>
       <c r="G1855" t="n">
-        <v>3.053110230398095</v>
+        <v>3.115206399012143</v>
       </c>
     </row>
     <row r="1856">
@@ -44239,16 +44239,16 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-3.302366717192751</v>
+        <v>-3.198873102836003</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.818556550016014</v>
+        <v>1.859953995758714</v>
       </c>
       <c r="F1856" t="n">
-        <v>-0.2495398976174708</v>
+        <v>-0.1460462832607224</v>
       </c>
       <c r="G1856" t="n">
-        <v>2.99013572263638</v>
+        <v>3.052231891250429</v>
       </c>
     </row>
     <row r="1857">
@@ -44262,16 +44262,16 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-3.660017067431099</v>
+        <v>-3.556523453074351</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.671602468576933</v>
+        <v>1.712999914319632</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.6071902478558189</v>
+        <v>-0.5036966334990705</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.771651571149629</v>
+        <v>2.833747739763678</v>
       </c>
     </row>
     <row r="1858">
@@ -44285,16 +44285,16 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-3.96925117042715</v>
+        <v>-3.865757556070401</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.549681754078772</v>
+        <v>1.591079199821472</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.6071902478558189</v>
+        <v>-0.5036966334990705</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.773424497849888</v>
+        <v>2.835520666463937</v>
       </c>
     </row>
     <row r="1859">
@@ -44308,16 +44308,16 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.401056963576938</v>
+        <v>-4.297563349220189</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.363292324286261</v>
+        <v>1.404689770028961</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.7436077442970859</v>
+        <v>-0.6401141299403375</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.677906887452532</v>
+        <v>2.740003056066582</v>
       </c>
     </row>
     <row r="1860">
@@ -44331,16 +44331,16 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-4.727489492444682</v>
+        <v>-4.623995878087933</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.221004087741254</v>
+        <v>1.262401533483954</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.826075994804234</v>
+        <v>-0.7225823804474856</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.616710712150335</v>
+        <v>2.678806880764383</v>
       </c>
     </row>
     <row r="1861">
@@ -44354,16 +44354,16 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.063152139675134</v>
+        <v>-4.959658525318385</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.085319620505039</v>
+        <v>1.126717066247738</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.826075994804234</v>
+        <v>-0.7225823804474856</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.6152913038063</v>
+        <v>2.677387472420349</v>
       </c>
     </row>
     <row r="1862">
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.426778384575448</v>
+        <v>-5.323284770218699</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.9463566827791547</v>
+        <v>0.9877541285218543</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.9242976316713598</v>
+        <v>-0.8208040173146114</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.562845881920266</v>
+        <v>2.624942050534315</v>
       </c>
     </row>
     <row r="1863">
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-5.791905767214194</v>
+        <v>-5.688412152857445</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.7995602447294878</v>
+        <v>0.8409576904721874</v>
       </c>
       <c r="F1863" t="n">
-        <v>-1.220608415970372</v>
+        <v>-1.117114801613624</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.38431392634669</v>
+        <v>2.446410094960739</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.200494544394873</v>
+        <v>-6.097000930038124</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.634886277871975</v>
+        <v>0.6762837236146746</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.629197193151051</v>
+        <v>-1.525703578794302</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.137922204053042</v>
+        <v>2.200018372667091</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.613477028535967</v>
+        <v>-6.509983414179218</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.4648787166869983</v>
+        <v>0.5062761624296979</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.629197193151051</v>
+        <v>-1.525703578794302</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.133107636524502</v>
+        <v>2.195203805138551</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.029868902822964</v>
+        <v>-6.926375288466216</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.2963160175810766</v>
+        <v>0.3377134633237762</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.629197193151051</v>
+        <v>-1.525703578794302</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.13110168713338</v>
+        <v>2.193197855747429</v>
       </c>
     </row>
     <row r="1867">
@@ -44492,16 +44492,16 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.406545913352809</v>
+        <v>-7.30305229899606</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.1559039040378178</v>
+        <v>0.1973013497805174</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.629197193151051</v>
+        <v>-1.525703578794302</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.141360377802059</v>
+        <v>2.203456546416108</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-7.752420735337617</v>
+        <v>-7.648927120980868</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.01365354038958966</v>
+        <v>0.0550509861322892</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.629197193151051</v>
+        <v>-1.525703578794302</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.137459942947754</v>
+        <v>2.199556111561803</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.065245534582596</v>
+        <v>-7.961751920225848</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.1130714592534008</v>
+        <v>-0.07167401351070168</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.629197193151051</v>
+        <v>-1.525703578794302</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.135864863002755</v>
+        <v>2.197961031616804</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.361906876392794</v>
+        <v>-8.258413262036045</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.2279570200482719</v>
+        <v>-0.1865595743055724</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.697940328884929</v>
+        <v>-1.594446714528181</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.098397957491636</v>
+        <v>2.160494126105685</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.795255984503029</v>
+        <v>-8.691762370146281</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.4053229678267694</v>
+        <v>-0.3639255220840698</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.697940328884929</v>
+        <v>-1.594446714528181</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.094371652957232</v>
+        <v>2.156467821571281</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.17825737324566</v>
+        <v>-9.074763758888912</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.5586256246454058</v>
+        <v>-0.5172281789027062</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.697940328884929</v>
+        <v>-1.594446714528181</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.094269551635648</v>
+        <v>2.156365720249697</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.553242699416938</v>
+        <v>-9.449749085060189</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.7060482391424867</v>
+        <v>-0.6646507933997872</v>
       </c>
       <c r="F1873" t="n">
-        <v>-2.072925655056207</v>
+        <v>-1.969432040699458</v>
       </c>
       <c r="G1873" t="n">
-        <v>1.871849871904312</v>
+        <v>1.933946040518361</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.912773021920939</v>
+        <v>-9.80927940756419</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.8445100648460371</v>
+        <v>-0.8031126191033375</v>
       </c>
       <c r="F1874" t="n">
-        <v>-2.072925655056207</v>
+        <v>-1.969432040699458</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.877200175202362</v>
+        <v>1.939296343816411</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-10.23917305058595</v>
+        <v>-10.1356794362292</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.9671540563548651</v>
+        <v>-0.9257566106121655</v>
       </c>
       <c r="F1875" t="n">
-        <v>-2.39932568372122</v>
+        <v>-2.295832069364471</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.689276177960532</v>
+        <v>1.751372346574581</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.45832201866015</v>
+        <v>-10.3548284043034</v>
       </c>
       <c r="E1876" t="n">
-        <v>-1.051771892962775</v>
+        <v>-1.010374447220075</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.618474651795417</v>
+        <v>-2.514981037438669</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.560828547737782</v>
+        <v>1.622924716351831</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.45463109370374</v>
+        <v>-10.35113747934699</v>
       </c>
       <c r="E1877" t="n">
-        <v>-1.050295522980211</v>
+        <v>-1.008898077237511</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.618474651795417</v>
+        <v>-2.514981037438669</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.560828547737782</v>
+        <v>1.622924716351831</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.6588892690336</v>
+        <v>-10.55539565467685</v>
       </c>
       <c r="E1878" t="n">
-        <v>-1.126485595993514</v>
+        <v>-1.085088150250814</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.746113596409406</v>
+        <v>-2.642619982052658</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.489758378088031</v>
+        <v>1.551854546702081</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.87692704066478</v>
+        <v>-10.77343342630803</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.209218150161548</v>
+        <v>-1.167820704418849</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.920884364505305</v>
+        <v>-2.817390750148557</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.389378471714928</v>
+        <v>1.451474640328977</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.80345720899733</v>
+        <v>-10.69996359464058</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.164458516001148</v>
+        <v>-1.123061070258449</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.847414532837857</v>
+        <v>-2.743920918481108</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.448832072208818</v>
+        <v>1.510928240822867</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.97858162638387</v>
+        <v>-10.87508801202713</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.219953062208249</v>
+        <v>-1.178555616465549</v>
       </c>
       <c r="F1881" t="n">
-        <v>-3.0225389502244</v>
+        <v>-2.919045335867652</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.358312642524409</v>
+        <v>1.420408811138458</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-11.21303372039836</v>
+        <v>-11.10954010604162</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.320953064715641</v>
+        <v>-1.279555618972941</v>
       </c>
       <c r="F1882" t="n">
-        <v>-3.0225389502244</v>
+        <v>-2.919045335867652</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.351093477622813</v>
+        <v>1.413189646236862</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.5008375649356</v>
+        <v>-11.39734395057885</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.442746793304512</v>
+        <v>-1.401349347561812</v>
       </c>
       <c r="F1883" t="n">
-        <v>-3.310342794761639</v>
+        <v>-3.20684918040489</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.171738980126494</v>
+        <v>1.233835148740543</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-11.73066201209943</v>
+        <v>-11.62716839774268</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.533560782331485</v>
+        <v>-1.492163336588786</v>
       </c>
       <c r="F1884" t="n">
-        <v>-3.472990331831799</v>
+        <v>-3.369496717475051</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.075266247722954</v>
+        <v>1.137362416337003</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-11.96269093183569</v>
+        <v>-11.85919731747894</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.623678621596876</v>
+        <v>-1.582281175854176</v>
       </c>
       <c r="F1885" t="n">
-        <v>-3.535003029020222</v>
+        <v>-3.431509414663474</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.040752358039014</v>
+        <v>1.102848526653064</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-11.91067541786688</v>
+        <v>-11.80718180351013</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.59888208032295</v>
+        <v>-1.55748463458025</v>
       </c>
       <c r="F1886" t="n">
-        <v>-3.535003029020222</v>
+        <v>-3.431509414663474</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.044742693725415</v>
+        <v>1.106838862339464</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-12.052347259591</v>
+        <v>-11.94885364523425</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.65702604391134</v>
+        <v>-1.61562859816864</v>
       </c>
       <c r="F1887" t="n">
-        <v>-3.535003029020222</v>
+        <v>-3.431509414663474</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.043267466826673</v>
+        <v>1.105363635440723</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-12.15125400005027</v>
+        <v>-12.04776038569352</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.681535329930177</v>
+        <v>-1.640137884187478</v>
       </c>
       <c r="F1888" t="n">
-        <v>-3.633909769479498</v>
+        <v>-3.53041615512275</v>
       </c>
       <c r="G1888" t="n">
-        <v>0.9989768327159809</v>
+        <v>1.06107300133003</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-11.95210189281317</v>
+        <v>-11.84860827845642</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.61492562068202</v>
+        <v>-1.573528174939321</v>
       </c>
       <c r="F1889" t="n">
-        <v>-3.468587243529684</v>
+        <v>-3.365093629172936</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.085119214639186</v>
+        <v>1.147215383253235</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-11.72625674009376</v>
+        <v>-11.62276312573701</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.515008486558048</v>
+        <v>-1.473611040815348</v>
       </c>
       <c r="F1890" t="n">
-        <v>-3.426660567942521</v>
+        <v>-3.323166953585773</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.119854293027692</v>
+        <v>1.181950461641741</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.43998192777107</v>
+        <v>-11.33648831341432</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.399359417072911</v>
+        <v>-1.357961971330211</v>
       </c>
       <c r="F1891" t="n">
-        <v>-3.426660567942521</v>
+        <v>-3.323166953585773</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.120993437583751</v>
+        <v>1.1830896061978</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.49287721581535</v>
+        <v>-11.3893836014586</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.417883758128518</v>
+        <v>-1.376486312385818</v>
       </c>
       <c r="F1892" t="n">
-        <v>-3.421705221854074</v>
+        <v>-3.318211607497326</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.126600419398927</v>
+        <v>1.188696588012976</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.20896848488661</v>
+        <v>-11.10547487052986</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.298586561518382</v>
+        <v>-1.257189115775682</v>
       </c>
       <c r="F1893" t="n">
-        <v>-3.421705221854074</v>
+        <v>-3.318211607497326</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.132334123637563</v>
+        <v>1.194430292251612</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.96198123469365</v>
+        <v>-10.8584876203369</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.209528923835067</v>
+        <v>-1.168131478092366</v>
       </c>
       <c r="F1894" t="n">
-        <v>-3.174717971661122</v>
+        <v>-3.071224357304374</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.270789211359469</v>
+        <v>1.332885379973518</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.69814436748958</v>
+        <v>-10.59465075313283</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.113877658266346</v>
+        <v>-1.072480212523646</v>
       </c>
       <c r="F1895" t="n">
-        <v>-3.174717971661122</v>
+        <v>-3.071224357304374</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.260905730046562</v>
+        <v>1.32300189866061</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.43090256662119</v>
+        <v>-10.32740895226444</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.008815498418361</v>
+        <v>-0.9674180526756611</v>
       </c>
       <c r="F1896" t="n">
-        <v>-3.174717971661122</v>
+        <v>-3.071224357304374</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.259071169547188</v>
+        <v>1.321167338161237</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.1550934032207</v>
+        <v>-10.05159978886395</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.8987921480316277</v>
+        <v>-0.8573947022889272</v>
       </c>
       <c r="F1897" t="n">
-        <v>-3.085698663382389</v>
+        <v>-2.982205049025641</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.312182439540967</v>
+        <v>1.374278608155016</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.13113986224474</v>
+        <v>-10.02764624788799</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.8885422254957507</v>
+        <v>-0.8471447797530511</v>
       </c>
       <c r="F1898" t="n">
-        <v>-3.061745122406431</v>
+        <v>-2.958251508049683</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.327223070272036</v>
+        <v>1.389319238886084</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.867079923921947</v>
+        <v>-9.763586309565197</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.7961785663283845</v>
+        <v>-0.754781120585684</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.797685184083635</v>
+        <v>-2.694191569726887</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.472398717103961</v>
+        <v>1.53449488571801</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.16000030041711</v>
+        <v>-9.056506686060359</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.5161337505867505</v>
+        <v>-0.47473630484405</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.797685184083635</v>
+        <v>-2.694191569726887</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.46961168344366</v>
+        <v>1.531707852057709</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.11981600205092</v>
+        <v>-9.016322387694169</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.4997164073524329</v>
+        <v>-0.4583189616097325</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.757500885717445</v>
+        <v>-2.654007271360697</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.494065886351216</v>
+        <v>1.556162054965265</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.039746206513115</v>
+        <v>-8.936252592156364</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.4683216679165541</v>
+        <v>-0.4269242221738541</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.677431090179641</v>
+        <v>-2.573937475822893</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.541474584894655</v>
+        <v>1.603570753508704</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.806264984283516</v>
+        <v>-8.702771369926765</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.3670047501868621</v>
+        <v>-0.3256073044441616</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.443949867950042</v>
+        <v>-2.340456253593294</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.689487747070267</v>
+        <v>1.751583915684316</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.626556454139642</v>
+        <v>-8.523062839782892</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.2980135484422717</v>
+        <v>-0.2566161026995717</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.386778363787346</v>
+        <v>-2.283284749430598</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.720898439254925</v>
+        <v>1.782994607868974</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.494280980508755</v>
+        <v>-8.390787366152004</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.2497358722428897</v>
+        <v>-0.2083384265001897</v>
       </c>
       <c r="F1905" t="n">
-        <v>-2.25450289015646</v>
+        <v>-2.151009275799712</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.795631210180484</v>
+        <v>1.857727378794533</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.303681305835601</v>
+        <v>-8.200187691478851</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.1706809416859918</v>
+        <v>-0.1292834959432914</v>
       </c>
       <c r="F1906" t="n">
-        <v>-2.063903215483307</v>
+        <v>-1.960409601126559</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.912806075672012</v>
+        <v>1.974902244286061</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.05468150715202</v>
+        <v>-7.95118789279527</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.05817468098890055</v>
+        <v>-0.01677723524620012</v>
       </c>
       <c r="F1907" t="n">
-        <v>-2.063903215483307</v>
+        <v>-1.960409601126559</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.925712416895671</v>
+        <v>1.98780858550972</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.160271496925125</v>
+        <v>-8.056777882568374</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.2283866064973612</v>
+        <v>-0.1869891607546608</v>
       </c>
       <c r="F1908" t="n">
-        <v>-2.169493205256412</v>
+        <v>-2.065999590899663</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.73438249343259</v>
+        <v>1.796478662046639</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.179006399043722</v>
+        <v>-8.075512784686971</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.1873362254677136</v>
+        <v>-0.1459387797250131</v>
       </c>
       <c r="F1909" t="n">
-        <v>-2.169493205256412</v>
+        <v>-2.065999590899663</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.782926835309676</v>
+        <v>1.845023003923725</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>3.088001770449517</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.902268224372909</v>
+        <v>-7.798774610016158</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.07326194361339367</v>
+        <v>-0.03186449787069323</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.987676544146486</v>
+        <v>-1.884182929789737</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.895395843961626</v>
+        <v>1.957492012575675</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>3.079287784196039</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.775375817937839</v>
+        <v>-7.671882203581088</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.03121896729284357</v>
+        <v>0.01017847844985642</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.860784137711416</v>
+        <v>-1.757290523354667</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.96281730156919</v>
+        <v>2.024913470183239</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>3.072327172100946</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.731827411167148</v>
+        <v>-7.628333796810398</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.02076021667966055</v>
+        <v>0.02063722906303944</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.860784137711416</v>
+        <v>-1.757290523354667</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.955856689474097</v>
+        <v>2.017952858088146</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>3.086789526482089</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.48967901771329</v>
+        <v>-7.38618540335654</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.0905614950830258</v>
+        <v>0.1319589408257258</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.860784137711416</v>
+        <v>-1.757290523354667</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.97031904385524</v>
+        <v>2.032415212469289</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>3.081321646941284</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.426449645944942</v>
+        <v>-7.322956031588191</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.1103853642495598</v>
+        <v>0.1517828099922602</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.860784137711416</v>
+        <v>-1.757290523354667</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.964851164314435</v>
+        <v>2.026947332928484</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>3.078819740951861</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.239961953567936</v>
+        <v>-7.136468339211185</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.1824785352109393</v>
+        <v>0.2238759809536397</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.67429644533441</v>
+        <v>-1.570802830977661</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.074241873751216</v>
+        <v>2.136338042365264</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>3.086520719189187</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.218812754664492</v>
+        <v>-7.115319140307742</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.1986391930096421</v>
+        <v>0.2400366387523425</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.653147246430966</v>
+        <v>-1.549653632074218</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.094632371330607</v>
+        <v>2.156728539944656</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>3.082301427536237</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.975047312681048</v>
+        <v>-6.871553698324298</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.2919260781500705</v>
+        <v>0.333323523892771</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.653147246430966</v>
+        <v>-1.549653632074218</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.090413079677658</v>
+        <v>2.152509248291707</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>3.084425741456253</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.711019245487789</v>
+        <v>-6.607525631131038</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.3996616189473903</v>
+        <v>0.4410590646900907</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.451281847615013</v>
+        <v>-1.347788233258264</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.213656632887246</v>
+        <v>2.275752801501295</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>3.077167816439955</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.461168851538714</v>
+        <v>-6.357675237181963</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.4923438515107224</v>
+        <v>0.5337412972534228</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.451281847615013</v>
+        <v>-1.347788233258264</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.206398707870948</v>
+        <v>2.268494876484997</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>3.080766939960604</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.157601362534735</v>
+        <v>-6.054107748177985</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.6173699706329625</v>
+        <v>0.6587674163756629</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.451281847615013</v>
+        <v>-1.347788233258264</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.209997831391597</v>
+        <v>2.272094000005646</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>3.094094446015158</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.084121453682721</v>
+        <v>-5.980627839325971</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.6600894402283219</v>
+        <v>0.7014868859710224</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.377801938762998</v>
+        <v>-1.27430832440625</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.267413282757359</v>
+        <v>2.329509451371408</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>3.093114923631455</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.859088454013898</v>
+        <v>-5.755594839657148</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.749123117712148</v>
+        <v>0.7905205634548484</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.152768939094175</v>
+        <v>-1.049275324737427</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.40145356017495</v>
+        <v>2.463549728788999</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>3.097809724685772</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.644454076377492</v>
+        <v>-5.540960462020741</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.839671669821028</v>
+        <v>0.8810691155637285</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.9381345614577685</v>
+        <v>-0.8346409471010201</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.534928987811111</v>
+        <v>2.59702515642516</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>3.079003983469568</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.37785371940314</v>
+        <v>-5.274360105046389</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.9275060713945646</v>
+        <v>0.9689035171372646</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.9381345614577685</v>
+        <v>-0.8346409471010201</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.516123246594907</v>
+        <v>2.578219415208956</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>3.080747060094445</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.137423222598279</v>
+        <v>-5.033929608241529</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.025421346741386</v>
+        <v>1.066818792484086</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.6977040646529082</v>
+        <v>-0.5942104502961598</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.6621246213027</v>
+        <v>2.72422078991675</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>3.084676373929265</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.894632414948834</v>
+        <v>-4.791138800592083</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.126466983635984</v>
+        <v>1.167864429378685</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.6977040646529082</v>
+        <v>-0.5942104502961598</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.666053935137521</v>
+        <v>2.72815010375157</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>3.085354957846605</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.655027323341745</v>
+        <v>-4.551533708984994</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.22298760419616</v>
+        <v>1.26438504993886</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.6306561169844137</v>
+        <v>-0.5271625026276653</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.706961287655957</v>
+        <v>2.769057456270006</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>3.082353029066599</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.412371734918581</v>
+        <v>-4.308878120561831</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.317047910785419</v>
+        <v>1.358445356528119</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.6306561169844137</v>
+        <v>-0.5271625026276653</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.703959358875951</v>
+        <v>2.76605552749</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>3.083932066077213</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.192350936881571</v>
+        <v>-4.08885732252482</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.406635267010837</v>
+        <v>1.448032712753538</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.4894362719164335</v>
+        <v>-0.385942657559685</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.790270302927353</v>
+        <v>2.852366471541402</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>3.099826248879036</v>
       </c>
       <c r="D1930" t="n">
-        <v>-3.993102306976762</v>
+        <v>-3.889608692620011</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.502228901774584</v>
+        <v>1.543626347517284</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.4894362719164335</v>
+        <v>-0.385942657559685</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.806164485729176</v>
+        <v>2.868260654343226</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>3.100972093319338</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.833587203457392</v>
+        <v>-3.730093589100641</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.567180787622634</v>
+        <v>1.608578233365334</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.3299211683970635</v>
+        <v>-0.2264275540403151</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.9030193922811</v>
+        <v>2.965115560895149</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.467089432050305</v>
+        <v>3.824228273823171</v>
       </c>
       <c r="C1932" t="n">
         <v>3.111060195880778</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.700281570586368</v>
+        <v>-3.6958866323357</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.630591143332484</v>
+        <v>1.632349118632751</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.1966155355260394</v>
+        <v>-0.1922205972753744</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.993090874565155</v>
+        <v>2.995727837515553</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240413.xlsx
+++ b/tame_output/ON/bt/strategyON_20240413.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>63.9%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.9%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.5%</t>
+          <t>-11.6%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>54.3%</t>
+          <t>50.9%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>72.7%</t>
+          <t>70.4%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>28.8%</t>
+          <t>29.0%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,17 +801,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>15.5%</t>
+          <t>20.5%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2021-03-21</t>
+          <t>2024-03-04</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2021-03-24</t>
+          <t>2024-03-19</t>
         </is>
       </c>
       <c r="N3" t="n">
@@ -819,7 +819,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-11.3%</t>
+          <t>-15.3%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-3.5%</t>
+          <t>-4.0%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>58.0%</t>
+          <t>55.9%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>23.0%</t>
+          <t>23.2%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-5.0%</t>
+          <t>-4.8%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>-7.3%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.0%</t>
+          <t>-78.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>117.9%</t>
+          <t>118.6%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>137.2%</t>
+          <t>138.1%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>97.3%</t>
+          <t>97.7%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>28.8%</t>
+          <t>29.1%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-56.3%</t>
+          <t>-56.7%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.7%</t>
+          <t>-73.9%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>97.9%</t>
+          <t>98.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>491.2%</t>
+          <t>502.9%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>6.5%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-531.2%</t>
+          <t>-530.5%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>16.2%</t>
+          <t>14.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>55.3%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>65.6%</t>
+          <t>65.9%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-44.0%</t>
+          <t>-44.3%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>13.1%</t>
+          <t>11.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>-17.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>206.1%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-213.0%</t>
+          <t>-219.5%</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-28.2%</t>
+          <t>-28.8%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>70.5%</t>
+          <t>71.5%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>71.0%</t>
+          <t>72.2%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>69.3%</t>
+          <t>70.0%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-296.3%</t>
+          <t>-306.6%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-37.2%</t>
+          <t>-37.8%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-21.0%</t>
+          <t>-21.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>58.5%</t>
+          <t>59.4%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>27.7%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-152.9%</t>
+          <t>-152.2%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-243.2%</t>
+          <t>-242.5%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>53.1%</t>
+          <t>50.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>51.1%</t>
+          <t>51.5%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>62.7%</t>
+          <t>63.4%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>41.4%</t>
+          <t>41.5%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>97.7%</t>
+          <t>97.9%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-178.1%</t>
+          <t>-184.4%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1471,22 +1471,22 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-32.1%</t>
+          <t>-32.6%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>47.7%</t>
+          <t>45.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>42.7%</t>
+          <t>43.0%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.1%</t>
+          <t>-16.9%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.7%</t>
+          <t>34.1%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-146.5%</t>
+          <t>-152.8%</t>
         </is>
       </c>
     </row>
@@ -43733,16 +43733,16 @@
         <v>3.13991794227561</v>
       </c>
       <c r="D1834" t="n">
-        <v>0.9621230735079426</v>
+        <v>0.858629459151194</v>
       </c>
       <c r="E1834" t="n">
-        <v>3.52441074736504</v>
+        <v>3.483013301622341</v>
       </c>
       <c r="F1834" t="n">
-        <v>1.983826356062417</v>
+        <v>1.880332741705669</v>
       </c>
       <c r="G1834" t="n">
-        <v>4.330213755913061</v>
+        <v>4.268117587299011</v>
       </c>
     </row>
     <row r="1835">
@@ -43756,16 +43756,16 @@
         <v>3.138175778137954</v>
       </c>
       <c r="D1835" t="n">
-        <v>0.9615712736661304</v>
+        <v>0.8580776593093818</v>
       </c>
       <c r="E1835" t="n">
-        <v>3.52244786329066</v>
+        <v>3.48105041754796</v>
       </c>
       <c r="F1835" t="n">
-        <v>1.984668119547724</v>
+        <v>1.881174505190975</v>
       </c>
       <c r="G1835" t="n">
-        <v>4.328976649866589</v>
+        <v>4.26688048125254</v>
       </c>
     </row>
     <row r="1836">
@@ -43779,16 +43779,16 @@
         <v>3.118001050765402</v>
       </c>
       <c r="D1836" t="n">
-        <v>0.8558843857238307</v>
+        <v>0.7523907713670821</v>
       </c>
       <c r="E1836" t="n">
-        <v>3.459998380741187</v>
+        <v>3.418600934998487</v>
       </c>
       <c r="F1836" t="n">
-        <v>1.97010704584504</v>
+        <v>1.866613431488292</v>
       </c>
       <c r="G1836" t="n">
-        <v>4.300065278272426</v>
+        <v>4.237969109658377</v>
       </c>
     </row>
     <row r="1837">
@@ -43796,22 +43796,22 @@
         <v>45299</v>
       </c>
       <c r="B1837" t="n">
-        <v>3.385382209279814</v>
+        <v>3.385382209279815</v>
       </c>
       <c r="C1837" t="n">
         <v>3.118490189491276</v>
       </c>
       <c r="D1837" t="n">
-        <v>0.8617337668390751</v>
+        <v>0.7582401524823265</v>
       </c>
       <c r="E1837" t="n">
-        <v>3.462827271913159</v>
+        <v>3.421429826170459</v>
       </c>
       <c r="F1837" t="n">
-        <v>1.97010704584504</v>
+        <v>1.866613431488292</v>
       </c>
       <c r="G1837" t="n">
-        <v>4.300554416998301</v>
+        <v>4.238458248384251</v>
       </c>
     </row>
     <row r="1838">
@@ -43825,16 +43825,16 @@
         <v>3.122570172112943</v>
       </c>
       <c r="D1838" t="n">
-        <v>0.8135114999919916</v>
+        <v>0.7100178856352429</v>
       </c>
       <c r="E1838" t="n">
-        <v>3.447618347795992</v>
+        <v>3.406220902053293</v>
       </c>
       <c r="F1838" t="n">
-        <v>1.921884778997957</v>
+        <v>1.818391164641208</v>
       </c>
       <c r="G1838" t="n">
-        <v>4.275701039511717</v>
+        <v>4.213604870897668</v>
       </c>
     </row>
     <row r="1839">
@@ -43848,16 +43848,16 @@
         <v>3.157511256610484</v>
       </c>
       <c r="D1839" t="n">
-        <v>0.5763800081421965</v>
+        <v>0.4728863937854478</v>
       </c>
       <c r="E1839" t="n">
-        <v>3.387706835553616</v>
+        <v>3.346309389810916</v>
       </c>
       <c r="F1839" t="n">
-        <v>1.921884778997957</v>
+        <v>1.818391164641208</v>
       </c>
       <c r="G1839" t="n">
-        <v>4.310642124009259</v>
+        <v>4.24854595539521</v>
       </c>
     </row>
     <row r="1840">
@@ -43871,16 +43871,16 @@
         <v>3.156088696795822</v>
       </c>
       <c r="D1840" t="n">
-        <v>0.5814175988697829</v>
+        <v>0.4779239845130344</v>
       </c>
       <c r="E1840" t="n">
-        <v>3.388299312029988</v>
+        <v>3.346901866287289</v>
       </c>
       <c r="F1840" t="n">
-        <v>1.977529235264274</v>
+        <v>1.874035620907526</v>
       </c>
       <c r="G1840" t="n">
-        <v>4.342606237954387</v>
+        <v>4.280510069340338</v>
       </c>
     </row>
     <row r="1841">
@@ -43894,16 +43894,16 @@
         <v>3.13483507841956</v>
       </c>
       <c r="D1841" t="n">
-        <v>0.5249479676934862</v>
+        <v>0.4214543533367376</v>
       </c>
       <c r="E1841" t="n">
-        <v>3.344457841183207</v>
+        <v>3.303060395440507</v>
       </c>
       <c r="F1841" t="n">
-        <v>1.921059604087977</v>
+        <v>1.817565989731229</v>
       </c>
       <c r="G1841" t="n">
-        <v>4.287470840872346</v>
+        <v>4.225374672258297</v>
       </c>
     </row>
     <row r="1842">
@@ -43917,16 +43917,16 @@
         <v>3.13585268755003</v>
       </c>
       <c r="D1842" t="n">
-        <v>0.4591805776440741</v>
+        <v>0.3556869632873255</v>
       </c>
       <c r="E1842" t="n">
-        <v>3.319168494293912</v>
+        <v>3.277771048551212</v>
       </c>
       <c r="F1842" t="n">
-        <v>1.921059604087977</v>
+        <v>1.817565989731229</v>
       </c>
       <c r="G1842" t="n">
-        <v>4.288488450002816</v>
+        <v>4.226392281388767</v>
       </c>
     </row>
     <row r="1843">
@@ -43940,16 +43940,16 @@
         <v>3.126480719537785</v>
       </c>
       <c r="D1843" t="n">
-        <v>0.4456450938673645</v>
+        <v>0.3421514795106159</v>
       </c>
       <c r="E1843" t="n">
-        <v>3.304382332770984</v>
+        <v>3.262984887028284</v>
       </c>
       <c r="F1843" t="n">
-        <v>1.921059604087977</v>
+        <v>1.817565989731229</v>
       </c>
       <c r="G1843" t="n">
-        <v>4.279116481990572</v>
+        <v>4.217020313376523</v>
       </c>
     </row>
     <row r="1844">
@@ -43963,16 +43963,16 @@
         <v>3.116563445493024</v>
       </c>
       <c r="D1844" t="n">
-        <v>0.3638731934396128</v>
+        <v>0.2603795790828642</v>
       </c>
       <c r="E1844" t="n">
-        <v>3.261756298555122</v>
+        <v>3.220358852812422</v>
       </c>
       <c r="F1844" t="n">
-        <v>1.948095177494114</v>
+        <v>1.844601563137365</v>
       </c>
       <c r="G1844" t="n">
-        <v>4.285420551989492</v>
+        <v>4.223324383375443</v>
       </c>
     </row>
     <row r="1845">
@@ -43986,16 +43986,16 @@
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>0.2966640855677352</v>
+        <v>0.1931704712109866</v>
       </c>
       <c r="E1845" t="n">
-        <v>3.239637972240073</v>
+        <v>3.198240526497373</v>
       </c>
       <c r="F1845" t="n">
-        <v>1.948095177494114</v>
+        <v>1.844601563137365</v>
       </c>
       <c r="G1845" t="n">
-        <v>4.290185868823194</v>
+        <v>4.228089700209145</v>
       </c>
     </row>
     <row r="1846">
@@ -44003,22 +44003,22 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201491</v>
+        <v>3.29550733020149</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>0.3006555383629254</v>
+        <v>0.1971619240061768</v>
       </c>
       <c r="E1846" t="n">
-        <v>3.239059349477389</v>
+        <v>3.19766190373469</v>
       </c>
       <c r="F1846" t="n">
-        <v>1.952086630289304</v>
+        <v>1.848593015932555</v>
       </c>
       <c r="G1846" t="n">
-        <v>4.290405536619549</v>
+        <v>4.228309368005499</v>
       </c>
     </row>
     <row r="1847">
@@ -44026,22 +44026,22 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.25879198115301</v>
+        <v>3.258791981153009</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-0.1170984851839116</v>
+        <v>-0.2205920995406602</v>
       </c>
       <c r="E1847" t="n">
-        <v>3.069884631563717</v>
+        <v>3.028487185821018</v>
       </c>
       <c r="F1847" t="n">
-        <v>1.534332606742467</v>
+        <v>1.430838992385719</v>
       </c>
       <c r="G1847" t="n">
-        <v>4.03768001399651</v>
+        <v>3.975583845382461</v>
       </c>
     </row>
     <row r="1848">
@@ -44049,22 +44049,22 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537429</v>
+        <v>3.271168579537428</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-0.3387204187420291</v>
+        <v>-0.4422140330987777</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.981102074739392</v>
+        <v>2.939704628996693</v>
       </c>
       <c r="F1848" t="n">
-        <v>1.496806473055098</v>
+        <v>1.393312858698349</v>
       </c>
       <c r="G1848" t="n">
-        <v>4.01503055038301</v>
+        <v>3.952934381768961</v>
       </c>
     </row>
     <row r="1849">
@@ -44078,16 +44078,16 @@
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-0.5467244770951063</v>
+        <v>-0.6502180914518549</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.902792595952087</v>
+        <v>2.861395150209387</v>
       </c>
       <c r="F1849" t="n">
-        <v>1.496806473055098</v>
+        <v>1.393312858698349</v>
       </c>
       <c r="G1849" t="n">
-        <v>4.019922694936936</v>
+        <v>3.957826526322886</v>
       </c>
     </row>
     <row r="1850">
@@ -44101,16 +44101,16 @@
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-0.8171244398039916</v>
+        <v>-0.9206180541607403</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.78971406720652</v>
+        <v>2.748316621463821</v>
       </c>
       <c r="F1850" t="n">
-        <v>1.226406510346213</v>
+        <v>1.122912895989464</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.852764173649592</v>
+        <v>3.790668005035543</v>
       </c>
     </row>
     <row r="1851">
@@ -44124,16 +44124,16 @@
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-1.156282817392514</v>
+        <v>-1.259776431749262</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.647135015477561</v>
+        <v>2.605737569734861</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.8872481327576904</v>
+        <v>0.783754518400942</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.642353446402928</v>
+        <v>3.580257277788879</v>
       </c>
     </row>
     <row r="1852">
@@ -44141,22 +44141,22 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213499</v>
+        <v>3.223539378213498</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-1.484300039119993</v>
+        <v>-1.587793653476741</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.536266416525337</v>
+        <v>2.494868970782638</v>
       </c>
       <c r="F1852" t="n">
-        <v>0.5592309110302113</v>
+        <v>0.4557372966734629</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.465881403105209</v>
+        <v>3.40378523449116</v>
       </c>
     </row>
     <row r="1853">
@@ -44164,22 +44164,22 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416049</v>
+        <v>3.231167537416048</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-1.977624910655171</v>
+        <v>-2.081118525011919</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.347035218319835</v>
+        <v>2.305637772577136</v>
       </c>
       <c r="F1853" t="n">
-        <v>0.4542447967905925</v>
+        <v>0.3507511824338441</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.410988484970006</v>
+        <v>3.348892316355957</v>
       </c>
     </row>
     <row r="1854">
@@ -44187,22 +44187,22 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382332</v>
+        <v>3.235981977382331</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-2.470009938679268</v>
+        <v>-2.573503553036016</v>
       </c>
       <c r="E1854" t="n">
-        <v>2.151187599153928</v>
+        <v>2.109790153411229</v>
       </c>
       <c r="F1854" t="n">
-        <v>-0.03814023123350418</v>
+        <v>-0.1416338455902526</v>
       </c>
       <c r="G1854" t="n">
-        <v>3.11666386019928</v>
+        <v>3.054567691585231</v>
       </c>
     </row>
     <row r="1855">
@@ -44210,22 +44210,22 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495503</v>
+        <v>3.278199702495502</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-2.85519032960934</v>
+        <v>-2.958683943966089</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.995657981594762</v>
+        <v>1.954260535852063</v>
       </c>
       <c r="F1855" t="n">
-        <v>-0.03814023123350418</v>
+        <v>-0.1416338455902526</v>
       </c>
       <c r="G1855" t="n">
-        <v>3.115206399012143</v>
+        <v>3.053110230398095</v>
       </c>
     </row>
     <row r="1856">
@@ -44233,22 +44233,22 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347059</v>
+        <v>3.299136146347058</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-3.198873102836003</v>
+        <v>-3.302366717192751</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.859953995758714</v>
+        <v>1.818556550016014</v>
       </c>
       <c r="F1856" t="n">
-        <v>-0.1460462832607224</v>
+        <v>-0.2495398976174708</v>
       </c>
       <c r="G1856" t="n">
-        <v>3.052231891250429</v>
+        <v>2.99013572263638</v>
       </c>
     </row>
     <row r="1857">
@@ -44256,22 +44256,22 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130021</v>
+        <v>3.28737757613002</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-3.556523453074351</v>
+        <v>-3.660017067431099</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.712999914319632</v>
+        <v>1.671602468576933</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.5036966334990705</v>
+        <v>-0.6071902478558189</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.833747739763678</v>
+        <v>2.771651571149629</v>
       </c>
     </row>
     <row r="1858">
@@ -44279,22 +44279,22 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178248</v>
+        <v>3.315884374178247</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-3.865757556070401</v>
+        <v>-3.96925117042715</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.591079199821472</v>
+        <v>1.549681754078772</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.5036966334990705</v>
+        <v>-0.6071902478558189</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.835520666463937</v>
+        <v>2.773424497849888</v>
       </c>
     </row>
     <row r="1859">
@@ -44302,22 +44302,22 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207818</v>
+        <v>3.305316798207816</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.297563349220189</v>
+        <v>-4.401056963576938</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.404689770028961</v>
+        <v>1.363292324286261</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.6401141299403375</v>
+        <v>-0.7436077442970859</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.740003056066582</v>
+        <v>2.677906887452532</v>
       </c>
     </row>
     <row r="1860">
@@ -44325,22 +44325,22 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310987</v>
+        <v>3.284619513310985</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-4.623995878087933</v>
+        <v>-4.727489492444682</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.262401533483954</v>
+        <v>1.221004087741254</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.7225823804474856</v>
+        <v>-0.826075994804234</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.678806880764383</v>
+        <v>2.616710712150335</v>
       </c>
     </row>
     <row r="1861">
@@ -44348,22 +44348,22 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006537</v>
+        <v>3.305849539006535</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-4.959658525318385</v>
+        <v>-5.063152139675134</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.126717066247738</v>
+        <v>1.085319620505039</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.7225823804474856</v>
+        <v>-0.826075994804234</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.677387472420349</v>
+        <v>2.6152913038063</v>
       </c>
     </row>
     <row r="1862">
@@ -44371,22 +44371,22 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309428</v>
+        <v>3.311086391309427</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.323284770218699</v>
+        <v>-5.426778384575448</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.9877541285218543</v>
+        <v>0.9463566827791547</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.8208040173146114</v>
+        <v>-0.9242976316713598</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.624942050534315</v>
+        <v>2.562845881920266</v>
       </c>
     </row>
     <row r="1863">
@@ -44394,22 +44394,22 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970909</v>
+        <v>3.304715716970908</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-5.688412152857445</v>
+        <v>-5.791905767214194</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.8409576904721874</v>
+        <v>0.7995602447294878</v>
       </c>
       <c r="F1863" t="n">
-        <v>-1.117114801613624</v>
+        <v>-1.220608415970372</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.446410094960739</v>
+        <v>2.38431392634669</v>
       </c>
     </row>
     <row r="1864">
@@ -44417,22 +44417,22 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330526</v>
+        <v>3.300815818330525</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.097000930038124</v>
+        <v>-6.200494544394873</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.6762837236146746</v>
+        <v>0.634886277871975</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.525703578794302</v>
+        <v>-1.629197193151051</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.200018372667091</v>
+        <v>2.137922204053042</v>
       </c>
     </row>
     <row r="1865">
@@ -44440,22 +44440,22 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191742</v>
+        <v>3.302618194191741</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.509983414179218</v>
+        <v>-6.613477028535967</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.5062761624296979</v>
+        <v>0.4648787166869983</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.525703578794302</v>
+        <v>-1.629197193151051</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.195203805138551</v>
+        <v>2.133107636524502</v>
       </c>
     </row>
     <row r="1866">
@@ -44463,22 +44463,22 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108644</v>
+        <v>3.305023265108643</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-6.926375288466216</v>
+        <v>-7.029868902822964</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.3377134633237762</v>
+        <v>0.2963160175810766</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.525703578794302</v>
+        <v>-1.629197193151051</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.193197855747429</v>
+        <v>2.13110168713338</v>
       </c>
     </row>
     <row r="1867">
@@ -44492,16 +44492,16 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.30305229899606</v>
+        <v>-7.406545913352809</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.1973013497805174</v>
+        <v>0.1559039040378178</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.525703578794302</v>
+        <v>-1.629197193151051</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.203456546416108</v>
+        <v>2.141360377802059</v>
       </c>
     </row>
     <row r="1868">
@@ -44509,22 +44509,22 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094122</v>
+        <v>3.374439043094121</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-7.648927120980868</v>
+        <v>-7.752420735337617</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.0550509861322892</v>
+        <v>0.01365354038958966</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.525703578794302</v>
+        <v>-1.629197193151051</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.199556111561803</v>
+        <v>2.137459942947754</v>
       </c>
     </row>
     <row r="1869">
@@ -44532,22 +44532,22 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199291</v>
+        <v>3.40596051119929</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-7.961751920225848</v>
+        <v>-8.065245534582596</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.07167401351070168</v>
+        <v>-0.1130714592534008</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.525703578794302</v>
+        <v>-1.629197193151051</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.197961031616804</v>
+        <v>2.135864863002755</v>
       </c>
     </row>
     <row r="1870">
@@ -44555,22 +44555,22 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969599</v>
+        <v>3.424633354969598</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.258413262036045</v>
+        <v>-8.361906876392794</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.1865595743055724</v>
+        <v>-0.2279570200482719</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.594446714528181</v>
+        <v>-1.697940328884929</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.160494126105685</v>
+        <v>2.098397957491636</v>
       </c>
     </row>
     <row r="1871">
@@ -44578,22 +44578,22 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923092</v>
+        <v>3.419979433923091</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.691762370146281</v>
+        <v>-8.795255984503029</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.3639255220840698</v>
+        <v>-0.4053229678267694</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.594446714528181</v>
+        <v>-1.697940328884929</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.156467821571281</v>
+        <v>2.094371652957232</v>
       </c>
     </row>
     <row r="1872">
@@ -44601,22 +44601,22 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297755</v>
+        <v>3.458100091297754</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.074763758888912</v>
+        <v>-9.17825737324566</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.5172281789027062</v>
+        <v>-0.5586256246454058</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.594446714528181</v>
+        <v>-1.697940328884929</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.156365720249697</v>
+        <v>2.094269551635648</v>
       </c>
     </row>
     <row r="1873">
@@ -44624,22 +44624,22 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317621</v>
+        <v>3.44775050131762</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.449749085060189</v>
+        <v>-9.553242699416938</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.6646507933997872</v>
+        <v>-0.7060482391424867</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.969432040699458</v>
+        <v>-2.072925655056207</v>
       </c>
       <c r="G1873" t="n">
-        <v>1.933946040518361</v>
+        <v>1.871849871904312</v>
       </c>
     </row>
     <row r="1874">
@@ -44647,22 +44647,22 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737176</v>
+        <v>3.503515506737175</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.80927940756419</v>
+        <v>-9.912773021920939</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.8031126191033375</v>
+        <v>-0.8445100648460371</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.969432040699458</v>
+        <v>-2.072925655056207</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.939296343816411</v>
+        <v>1.877200175202362</v>
       </c>
     </row>
     <row r="1875">
@@ -44670,22 +44670,22 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341319</v>
+        <v>3.503170282341317</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-10.1356794362292</v>
+        <v>-10.23917305058595</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.9257566106121655</v>
+        <v>-0.9671540563548651</v>
       </c>
       <c r="F1875" t="n">
-        <v>-2.295832069364471</v>
+        <v>-2.39932568372122</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.751372346574581</v>
+        <v>1.689276177960532</v>
       </c>
     </row>
     <row r="1876">
@@ -44693,22 +44693,22 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776683</v>
+        <v>3.500446096776681</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.3548284043034</v>
+        <v>-10.45832201866015</v>
       </c>
       <c r="E1876" t="n">
-        <v>-1.010374447220075</v>
+        <v>-1.051771892962775</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.514981037438669</v>
+        <v>-2.618474651795417</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.622924716351831</v>
+        <v>1.560828547737782</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.35113747934699</v>
+        <v>-10.45463109370374</v>
       </c>
       <c r="E1877" t="n">
-        <v>-1.008898077237511</v>
+        <v>-1.050295522980211</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.514981037438669</v>
+        <v>-2.618474651795417</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.622924716351831</v>
+        <v>1.560828547737782</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.55539565467685</v>
+        <v>-10.6588892690336</v>
       </c>
       <c r="E1878" t="n">
-        <v>-1.085088150250814</v>
+        <v>-1.126485595993514</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.642619982052658</v>
+        <v>-2.746113596409406</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.551854546702081</v>
+        <v>1.489758378088031</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.77343342630803</v>
+        <v>-10.87692704066478</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.167820704418849</v>
+        <v>-1.209218150161548</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.817390750148557</v>
+        <v>-2.920884364505305</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.451474640328977</v>
+        <v>1.389378471714928</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.69996359464058</v>
+        <v>-10.80345720899733</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.123061070258449</v>
+        <v>-1.164458516001148</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.743920918481108</v>
+        <v>-2.847414532837857</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.510928240822867</v>
+        <v>1.448832072208818</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.87508801202713</v>
+        <v>-10.97858162638387</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.178555616465549</v>
+        <v>-1.219953062208249</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.919045335867652</v>
+        <v>-3.0225389502244</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.420408811138458</v>
+        <v>1.358312642524409</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880271</v>
+        <v>3.48587501888027</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-11.10954010604162</v>
+        <v>-11.21303372039836</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.279555618972941</v>
+        <v>-1.320953064715641</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.919045335867652</v>
+        <v>-3.0225389502244</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.413189646236862</v>
+        <v>1.351093477622813</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.39734395057885</v>
+        <v>-11.5008375649356</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.401349347561812</v>
+        <v>-1.442746793304512</v>
       </c>
       <c r="F1883" t="n">
-        <v>-3.20684918040489</v>
+        <v>-3.310342794761639</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.233835148740543</v>
+        <v>1.171738980126494</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860586</v>
+        <v>3.493712438860585</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-11.62716839774268</v>
+        <v>-11.73066201209943</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.492163336588786</v>
+        <v>-1.533560782331485</v>
       </c>
       <c r="F1884" t="n">
-        <v>-3.369496717475051</v>
+        <v>-3.472990331831799</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.137362416337003</v>
+        <v>1.075266247722954</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-11.85919731747894</v>
+        <v>-11.96269093183569</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.582281175854176</v>
+        <v>-1.623678621596876</v>
       </c>
       <c r="F1885" t="n">
-        <v>-3.431509414663474</v>
+        <v>-3.535003029020222</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.102848526653064</v>
+        <v>1.040752358039014</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792544</v>
+        <v>3.573670449792543</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-11.80718180351013</v>
+        <v>-11.91067541786688</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.55748463458025</v>
+        <v>-1.59888208032295</v>
       </c>
       <c r="F1886" t="n">
-        <v>-3.431509414663474</v>
+        <v>-3.535003029020222</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.106838862339464</v>
+        <v>1.044742693725415</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628921</v>
+        <v>3.60003468962892</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.94885364523425</v>
+        <v>-12.052347259591</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.61562859816864</v>
+        <v>-1.65702604391134</v>
       </c>
       <c r="F1887" t="n">
-        <v>-3.431509414663474</v>
+        <v>-3.535003029020222</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.105363635440723</v>
+        <v>1.043267466826673</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410719</v>
+        <v>3.691568158410718</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-12.04776038569352</v>
+        <v>-12.15125400005027</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.640137884187478</v>
+        <v>-1.681535329930177</v>
       </c>
       <c r="F1888" t="n">
-        <v>-3.53041615512275</v>
+        <v>-3.633909769479498</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.06107300133003</v>
+        <v>0.9989768327159809</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240579</v>
+        <v>3.676837974240577</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-11.84860827845642</v>
+        <v>-11.95210189281317</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.573528174939321</v>
+        <v>-1.61492562068202</v>
       </c>
       <c r="F1889" t="n">
-        <v>-3.365093629172936</v>
+        <v>-3.468587243529684</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.147215383253235</v>
+        <v>1.085119214639186</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085281</v>
+        <v>3.68515780608528</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-11.62276312573701</v>
+        <v>-11.72625674009376</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.473611040815348</v>
+        <v>-1.515008486558048</v>
       </c>
       <c r="F1890" t="n">
-        <v>-3.323166953585773</v>
+        <v>-3.426660567942521</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.181950461641741</v>
+        <v>1.119854293027692</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282103</v>
+        <v>3.684840248282101</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.33648831341432</v>
+        <v>-11.43998192777107</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.357961971330211</v>
+        <v>-1.399359417072911</v>
       </c>
       <c r="F1891" t="n">
-        <v>-3.323166953585773</v>
+        <v>-3.426660567942521</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.1830896061978</v>
+        <v>1.120993437583751</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116218</v>
+        <v>3.710931958116216</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.3893836014586</v>
+        <v>-11.49287721581535</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.376486312385818</v>
+        <v>-1.417883758128518</v>
       </c>
       <c r="F1892" t="n">
-        <v>-3.318211607497326</v>
+        <v>-3.421705221854074</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.188696588012976</v>
+        <v>1.126600419398927</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.76894809908157</v>
+        <v>3.768948099081568</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.10547487052986</v>
+        <v>-11.20896848488661</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.257189115775682</v>
+        <v>-1.298586561518382</v>
       </c>
       <c r="F1893" t="n">
-        <v>-3.318211607497326</v>
+        <v>-3.421705221854074</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.194430292251612</v>
+        <v>1.132334123637563</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425331</v>
+        <v>3.728574354425328</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.8584876203369</v>
+        <v>-10.96198123469365</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.168131478092366</v>
+        <v>-1.209528923835067</v>
       </c>
       <c r="F1894" t="n">
-        <v>-3.071224357304374</v>
+        <v>-3.174717971661122</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.332885379973518</v>
+        <v>1.270789211359469</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702415</v>
+        <v>3.747699084702413</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.59465075313283</v>
+        <v>-10.69814436748958</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.072480212523646</v>
+        <v>-1.113877658266346</v>
       </c>
       <c r="F1895" t="n">
-        <v>-3.071224357304374</v>
+        <v>-3.174717971661122</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.32300189866061</v>
+        <v>1.260905730046562</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.76631350390623</v>
+        <v>3.766313503906229</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.32740895226444</v>
+        <v>-10.43090256662119</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.9674180526756611</v>
+        <v>-1.008815498418361</v>
       </c>
       <c r="F1896" t="n">
-        <v>-3.071224357304374</v>
+        <v>-3.174717971661122</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.321167338161237</v>
+        <v>1.259071169547188</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.05159978886395</v>
+        <v>-10.1550934032207</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.8573947022889272</v>
+        <v>-0.8987921480316277</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.982205049025641</v>
+        <v>-3.085698663382389</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.374278608155016</v>
+        <v>1.312182439540967</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.02764624788799</v>
+        <v>-10.13113986224474</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.8471447797530511</v>
+        <v>-0.8885422254957507</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.958251508049683</v>
+        <v>-3.061745122406431</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.389319238886084</v>
+        <v>1.327223070272036</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.763586309565197</v>
+        <v>-9.867079923921947</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.754781120585684</v>
+        <v>-0.7961785663283845</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.694191569726887</v>
+        <v>-2.797685184083635</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.53449488571801</v>
+        <v>1.472398717103961</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.056506686060359</v>
+        <v>-9.16000030041711</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.47473630484405</v>
+        <v>-0.5161337505867505</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.694191569726887</v>
+        <v>-2.797685184083635</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.531707852057709</v>
+        <v>1.46961168344366</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.016322387694169</v>
+        <v>-9.11981600205092</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.4583189616097325</v>
+        <v>-0.4997164073524329</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.654007271360697</v>
+        <v>-2.757500885717445</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.556162054965265</v>
+        <v>1.494065886351216</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.936252592156364</v>
+        <v>-9.039746206513115</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.4269242221738541</v>
+        <v>-0.4683216679165541</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.573937475822893</v>
+        <v>-2.677431090179641</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.603570753508704</v>
+        <v>1.541474584894655</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761809</v>
+        <v>3.787326853761811</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.702771369926765</v>
+        <v>-8.806264984283516</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.3256073044441616</v>
+        <v>-0.3670047501868621</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.340456253593294</v>
+        <v>-2.443949867950042</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.751583915684316</v>
+        <v>1.689487747070267</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255786</v>
+        <v>3.801633547255788</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.523062839782892</v>
+        <v>-8.626556454139642</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.2566161026995717</v>
+        <v>-0.2980135484422717</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.283284749430598</v>
+        <v>-2.386778363787346</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.782994607868974</v>
+        <v>1.720898439254925</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860428</v>
+        <v>3.76317867286043</v>
       </c>
       <c r="C1905" t="n">
-        <v>3.14833294427436</v>
+        <v>3.080628998079007</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.390787366152004</v>
+        <v>-8.494280980508755</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.2083384265001897</v>
+        <v>-0.3174398184382419</v>
       </c>
       <c r="F1905" t="n">
-        <v>-2.151009275799712</v>
+        <v>-2.25450289015646</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.857727378794533</v>
+        <v>1.727927263985132</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575954</v>
+        <v>3.784715218575956</v>
       </c>
       <c r="C1906" t="n">
-        <v>3.151148004961996</v>
+        <v>3.083444058766644</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.200187691478851</v>
+        <v>-8.303681305835601</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.1292834959432914</v>
+        <v>-0.2383848878813439</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.960409601126559</v>
+        <v>-2.063903215483307</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.974902244286061</v>
+        <v>1.84510212947666</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430989</v>
+        <v>3.75387899643099</v>
       </c>
       <c r="C1907" t="n">
-        <v>3.164054346185655</v>
+        <v>3.096350399990303</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.95118789279527</v>
+        <v>-8.05468150715202</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.01677723524620012</v>
+        <v>-0.1258786271842527</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.960409601126559</v>
+        <v>-2.063903215483307</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.98780858550972</v>
+        <v>1.858008470700319</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077646</v>
+        <v>3.692928280077648</v>
       </c>
       <c r="C1908" t="n">
-        <v>3.036078416586436</v>
+        <v>2.968374470391084</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.056777882568374</v>
+        <v>-8.160271496925125</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.1869891607546608</v>
+        <v>-0.2960905526927133</v>
       </c>
       <c r="F1908" t="n">
-        <v>-2.065999590899663</v>
+        <v>-2.169493205256412</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.796478662046639</v>
+        <v>1.666678547237238</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457904</v>
+        <v>3.770419008457905</v>
       </c>
       <c r="C1909" t="n">
-        <v>3.084622758463523</v>
+        <v>3.01691881226817</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.075512784686971</v>
+        <v>-8.179006399043722</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.1459387797250131</v>
+        <v>-0.2550401716630657</v>
       </c>
       <c r="F1909" t="n">
-        <v>-2.065999590899663</v>
+        <v>-2.169493205256412</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.845023003923725</v>
+        <v>1.715222889114324</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.76033011118081</v>
+        <v>3.760330111180813</v>
       </c>
       <c r="C1910" t="n">
-        <v>3.088001770449517</v>
+        <v>3.020297824254165</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.798774610016158</v>
+        <v>-7.902268224372909</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.03186449787069323</v>
+        <v>-0.1409658898087458</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.884182929789737</v>
+        <v>-1.987676544146486</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.957492012575675</v>
+        <v>1.827691897766274</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879203</v>
+        <v>3.723562653879206</v>
       </c>
       <c r="C1911" t="n">
-        <v>3.079287784196039</v>
+        <v>3.011583838000687</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.671882203581088</v>
+        <v>-7.775375817937839</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.01017847844985642</v>
+        <v>-0.09892291348819571</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.757290523354667</v>
+        <v>-1.860784137711416</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.024913470183239</v>
+        <v>1.895113355373838</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568107</v>
+        <v>3.72996614056811</v>
       </c>
       <c r="C1912" t="n">
-        <v>3.072327172100946</v>
+        <v>3.004623225905594</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.628333796810398</v>
+        <v>-7.731827411167148</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.02063722906303944</v>
+        <v>-0.08846416287501269</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.757290523354667</v>
+        <v>-1.860784137711416</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.017952858088146</v>
+        <v>1.888152743278745</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963418</v>
+        <v>3.782918957963422</v>
       </c>
       <c r="C1913" t="n">
-        <v>3.086789526482089</v>
+        <v>3.019085580286737</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.38618540335654</v>
+        <v>-7.48967901771329</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.1319589408257258</v>
+        <v>0.02285754888767366</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.757290523354667</v>
+        <v>-1.860784137711416</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.032415212469289</v>
+        <v>1.902615097659888</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192817</v>
+        <v>3.828547911192819</v>
       </c>
       <c r="C1914" t="n">
-        <v>3.081321646941284</v>
+        <v>3.013617700745932</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.322956031588191</v>
+        <v>-7.426449645944942</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.1517828099922602</v>
+        <v>0.04268141805420766</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.757290523354667</v>
+        <v>-1.860784137711416</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.026947332928484</v>
+        <v>1.897147218119083</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262047</v>
+        <v>3.82804935326205</v>
       </c>
       <c r="C1915" t="n">
-        <v>3.078819740951861</v>
+        <v>3.011115794756509</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.136468339211185</v>
+        <v>-7.239961953567936</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.2238759809536397</v>
+        <v>0.1147745890155871</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.570802830977661</v>
+        <v>-1.67429644533441</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.136338042365264</v>
+        <v>2.006537927555863</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389909</v>
+        <v>3.812450103389912</v>
       </c>
       <c r="C1916" t="n">
-        <v>3.086520719189187</v>
+        <v>3.018816772993834</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.115319140307742</v>
+        <v>-7.218812754664492</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.2400366387523425</v>
+        <v>0.1309352468142899</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.549653632074218</v>
+        <v>-1.653147246430966</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.156728539944656</v>
+        <v>2.026928425135255</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788095</v>
+        <v>3.748324832788096</v>
       </c>
       <c r="C1917" t="n">
-        <v>3.082301427536237</v>
+        <v>3.014597481340885</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.871553698324298</v>
+        <v>-6.975047312681048</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.333323523892771</v>
+        <v>0.2242221319547184</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.549653632074218</v>
+        <v>-1.653147246430966</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.152509248291707</v>
+        <v>2.022709133482306</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527526</v>
+        <v>3.824307657527529</v>
       </c>
       <c r="C1918" t="n">
-        <v>3.084425741456253</v>
+        <v>3.016721795260901</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.607525631131038</v>
+        <v>-6.711019245487789</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.4410590646900907</v>
+        <v>0.3319576727520381</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.347788233258264</v>
+        <v>-1.451281847615013</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.275752801501295</v>
+        <v>2.145952686691894</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749185</v>
+        <v>3.826351398749187</v>
       </c>
       <c r="C1919" t="n">
-        <v>3.077167816439955</v>
+        <v>3.009463870244603</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.357675237181963</v>
+        <v>-6.461168851538714</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.5337412972534228</v>
+        <v>0.4246399053153702</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.347788233258264</v>
+        <v>-1.451281847615013</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.268494876484997</v>
+        <v>2.138694761675596</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481498</v>
+        <v>3.835954411481501</v>
       </c>
       <c r="C1920" t="n">
-        <v>3.080766939960604</v>
+        <v>3.013062993765252</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.054107748177985</v>
+        <v>-6.157601362534735</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.6587674163756629</v>
+        <v>0.5496660244376104</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.347788233258264</v>
+        <v>-1.451281847615013</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.272094000005646</v>
+        <v>2.142293885196245</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862987</v>
+        <v>3.78093033586299</v>
       </c>
       <c r="C1921" t="n">
-        <v>3.094094446015158</v>
+        <v>3.026390499819806</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.980627839325971</v>
+        <v>-6.084121453682721</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.7014868859710224</v>
+        <v>0.5923854940329698</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.27430832440625</v>
+        <v>-1.377801938762998</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.329509451371408</v>
+        <v>2.199709336562007</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102782</v>
+        <v>3.773761647102785</v>
       </c>
       <c r="C1922" t="n">
-        <v>3.093114923631455</v>
+        <v>3.025410977436103</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.755594839657148</v>
+        <v>-5.859088454013898</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.7905205634548484</v>
+        <v>0.6814191715167959</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.049275324737427</v>
+        <v>-1.152768939094175</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.463549728788999</v>
+        <v>2.333749613979598</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353077</v>
+        <v>3.764614304353079</v>
       </c>
       <c r="C1923" t="n">
-        <v>3.097809724685772</v>
+        <v>3.03010577849042</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.540960462020741</v>
+        <v>-5.644454076377492</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.8810691155637285</v>
+        <v>0.7719677236256759</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.8346409471010201</v>
+        <v>-0.9381345614577685</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.59702515642516</v>
+        <v>2.467225041615759</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544785</v>
+        <v>3.798811195544787</v>
       </c>
       <c r="C1924" t="n">
-        <v>3.079003983469568</v>
+        <v>3.011300037274216</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.274360105046389</v>
+        <v>-5.37785371940314</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.9689035171372646</v>
+        <v>0.8598021251992125</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.8346409471010201</v>
+        <v>-0.9381345614577685</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.578219415208956</v>
+        <v>2.448419300399555</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712296</v>
+        <v>3.797691308712299</v>
       </c>
       <c r="C1925" t="n">
-        <v>3.080747060094445</v>
+        <v>3.013043113899093</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.033929608241529</v>
+        <v>-5.137423222598279</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.066818792484086</v>
+        <v>0.9577174005460338</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.5942104502961598</v>
+        <v>-0.6977040646529082</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.72422078991675</v>
+        <v>2.594420675107348</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837688</v>
+        <v>3.821589933837689</v>
       </c>
       <c r="C1926" t="n">
-        <v>3.084676373929265</v>
+        <v>3.016972427733913</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.791138800592083</v>
+        <v>-4.894632414948834</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.167864429378685</v>
+        <v>1.058763037440632</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.5942104502961598</v>
+        <v>-0.6977040646529082</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.72815010375157</v>
+        <v>2.598349988942168</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349969</v>
+        <v>3.822323422349971</v>
       </c>
       <c r="C1927" t="n">
-        <v>3.085354957846605</v>
+        <v>3.017651011651253</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.551533708984994</v>
+        <v>-4.655027323341745</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.26438504993886</v>
+        <v>1.155283658000808</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.5271625026276653</v>
+        <v>-0.6306561169844137</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.769057456270006</v>
+        <v>2.639257341460605</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972343</v>
+        <v>3.848613050972344</v>
       </c>
       <c r="C1928" t="n">
-        <v>3.082353029066599</v>
+        <v>3.014649082871247</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.308878120561831</v>
+        <v>-4.412371734918581</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.358445356528119</v>
+        <v>1.249343964590067</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.5271625026276653</v>
+        <v>-0.6306561169844137</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.76605552749</v>
+        <v>2.636255412680599</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145943</v>
+        <v>3.818665376145944</v>
       </c>
       <c r="C1929" t="n">
-        <v>3.083932066077213</v>
+        <v>3.016228119881861</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.08885732252482</v>
+        <v>-4.192350936881571</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.448032712753538</v>
+        <v>1.338931320815485</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.385942657559685</v>
+        <v>-0.4894362719164335</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.852366471541402</v>
+        <v>2.722566356732001</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009955</v>
+        <v>3.843270952009956</v>
       </c>
       <c r="C1930" t="n">
-        <v>3.099826248879036</v>
+        <v>3.032122302683684</v>
       </c>
       <c r="D1930" t="n">
-        <v>-3.889608692620011</v>
+        <v>-3.993102306976762</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.543626347517284</v>
+        <v>1.434524955579232</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.385942657559685</v>
+        <v>-0.4894362719164335</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.868260654343226</v>
+        <v>2.738460539533824</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966259</v>
+        <v>3.845043810966262</v>
       </c>
       <c r="C1931" t="n">
-        <v>3.100972093319338</v>
+        <v>3.033268147123986</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.730093589100641</v>
+        <v>-3.833587203457392</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.608578233365334</v>
+        <v>1.499476841427282</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.2264275540403151</v>
+        <v>-0.3299211683970635</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.965115560895149</v>
+        <v>2.835315446085748</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.824228273823171</v>
+        <v>3.790071705107584</v>
       </c>
       <c r="C1932" t="n">
-        <v>3.111060195880778</v>
+        <v>3.043356249685426</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.6958866323357</v>
+        <v>-3.688915058357654</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.632349118632751</v>
+        <v>1.567433802028617</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.1922205972753744</v>
+        <v>-0.1852490232973261</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.995727837515553</v>
+        <v>2.932206835707031</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240413.xlsx
+++ b/tame_output/ON/bt/strategyON_20240413.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>63.9%</t>
+          <t>51.4%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>68.1%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>69.2%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.5%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-17.5%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.6%</t>
+          <t>-12.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>50.9%</t>
+          <t>18.6%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>70.4%</t>
+          <t>72.7%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>29.0%</t>
+          <t>28.8%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,17 +801,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>20.5%</t>
+          <t>15.5%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2024-03-04</t>
+          <t>2021-03-21</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-03-19</t>
+          <t>2021-03-24</t>
         </is>
       </c>
       <c r="N3" t="n">
@@ -819,7 +819,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-15.3%</t>
+          <t>-11.3%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-4.0%</t>
+          <t>-3.5%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>60.2%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>23.2%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.8%</t>
+          <t>-5.0%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-7.3%</t>
+          <t>-0.5%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.2%</t>
+          <t>-79.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -926,7 +926,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>138.1%</t>
+          <t>138.2%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>97.7%</t>
+          <t>97.6%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-722.5%</t>
+          <t>-741.9%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-56.7%</t>
+          <t>-57.4%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.9%</t>
+          <t>-75.0%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>98.4%</t>
+          <t>98.3%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>502.9%</t>
+          <t>497.9%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>6.5%</t>
+          <t>6.6%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-530.5%</t>
+          <t>-549.9%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-283.6%</t>
+          <t>-291.4%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-44.3%</t>
+          <t>-44.9%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>12.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-17.6%</t>
+          <t>-18.7%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>206.1%</t>
+          <t>347.6%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-219.5%</t>
+          <t>-220.5%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-28.8%</t>
+          <t>-31.4%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>71.5%</t>
+          <t>71.6%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>72.2%</t>
+          <t>72.5%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>69.9%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-37.8%</t>
+          <t>-39.0%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-21.5%</t>
+          <t>-24.4%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>31.1%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-152.2%</t>
+          <t>-152.0%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-242.5%</t>
+          <t>-262.0%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>50.9%</t>
+          <t>49.4%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>51.5%</t>
+          <t>51.6%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.4%</t>
+          <t>63.5%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>41.5%</t>
+          <t>41.6%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>97.9%</t>
+          <t>98.1%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-32.6%</t>
+          <t>-33.7%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>45.7%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.0%</t>
+          <t>43.1%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1496,17 +1496,17 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.9%</t>
+          <t>-16.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.1%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-152.8%</t>
+          <t>-157.7%</t>
         </is>
       </c>
     </row>
@@ -43796,7 +43796,7 @@
         <v>45299</v>
       </c>
       <c r="B1837" t="n">
-        <v>3.385382209279815</v>
+        <v>3.385382209279814</v>
       </c>
       <c r="C1837" t="n">
         <v>3.118490189491276</v>
@@ -43819,7 +43819,7 @@
         <v>45300</v>
       </c>
       <c r="B1838" t="n">
-        <v>3.367379938511406</v>
+        <v>3.367379938511405</v>
       </c>
       <c r="C1838" t="n">
         <v>3.122570172112943</v>
@@ -43888,7 +43888,7 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082127</v>
+        <v>3.299560092082126</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
@@ -43957,7 +43957,7 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.298730590706673</v>
+        <v>3.298730590706672</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
@@ -43980,7 +43980,7 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.29991811929684</v>
+        <v>3.299918119296839</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
@@ -44072,7 +44072,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382194</v>
+        <v>3.272760131382193</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911642</v>
+        <v>3.233800325911641</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207816</v>
+        <v>3.305316798207817</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310985</v>
+        <v>3.284619513310986</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006535</v>
+        <v>3.305849539006537</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097825</v>
+        <v>3.341378723097824</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341317</v>
+        <v>3.503170282341318</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776681</v>
+        <v>3.500446096776682</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407495</v>
+        <v>3.492445136407494</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199887</v>
+        <v>3.496848329199886</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.49996816391063</v>
+        <v>3.499968163910629</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.80345720899733</v>
+        <v>-10.99800317912564</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.164458516001148</v>
+        <v>-1.242276904052471</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.847414532837857</v>
+        <v>-3.041960502966166</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.448832072208818</v>
+        <v>1.332104490131833</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078598</v>
+        <v>3.490055666078597</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.97858162638387</v>
+        <v>-11.17312759651218</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.219953062208249</v>
+        <v>-1.297771450259573</v>
       </c>
       <c r="F1881" t="n">
-        <v>-3.0225389502244</v>
+        <v>-3.217084920352709</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.358312642524409</v>
+        <v>1.241585060447423</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-11.21303372039836</v>
+        <v>-11.40757969052667</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.320953064715641</v>
+        <v>-1.398771452766964</v>
       </c>
       <c r="F1882" t="n">
-        <v>-3.0225389502244</v>
+        <v>-3.217084920352709</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.351093477622813</v>
+        <v>1.234365895545827</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234396</v>
+        <v>3.480688917234395</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.5008375649356</v>
+        <v>-11.69538353506391</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.442746793304512</v>
+        <v>-1.520565181355836</v>
       </c>
       <c r="F1883" t="n">
-        <v>-3.310342794761639</v>
+        <v>-3.504888764889948</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.171738980126494</v>
+        <v>1.055011398049508</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-11.73066201209943</v>
+        <v>-11.92520798222774</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.533560782331485</v>
+        <v>-1.61137917038281</v>
       </c>
       <c r="F1884" t="n">
-        <v>-3.472990331831799</v>
+        <v>-3.667536301960108</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.075266247722954</v>
+        <v>0.9585386656459685</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767399</v>
+        <v>3.492098065767398</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-11.96269093183569</v>
+        <v>-12.157236901964</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.623678621596876</v>
+        <v>-1.7014970096482</v>
       </c>
       <c r="F1885" t="n">
-        <v>-3.535003029020222</v>
+        <v>-3.729548999148531</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.040752358039014</v>
+        <v>0.924024775962029</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-11.91067541786688</v>
+        <v>-12.10522138799519</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.59888208032295</v>
+        <v>-1.676700468374274</v>
       </c>
       <c r="F1886" t="n">
-        <v>-3.535003029020222</v>
+        <v>-3.729548999148531</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.044742693725415</v>
+        <v>0.9280151116484299</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-12.052347259591</v>
+        <v>-12.24689322971931</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.65702604391134</v>
+        <v>-1.734844431962664</v>
       </c>
       <c r="F1887" t="n">
-        <v>-3.535003029020222</v>
+        <v>-3.729548999148531</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.043267466826673</v>
+        <v>0.9265398847496882</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-12.15125400005027</v>
+        <v>-12.34579997017858</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.681535329930177</v>
+        <v>-1.759353717981501</v>
       </c>
       <c r="F1888" t="n">
-        <v>-3.633909769479498</v>
+        <v>-3.828455739607806</v>
       </c>
       <c r="G1888" t="n">
-        <v>0.9989768327159809</v>
+        <v>0.8822492506389956</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240577</v>
+        <v>3.676837974240578</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-11.95210189281317</v>
+        <v>-12.14664786294148</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.61492562068202</v>
+        <v>-1.692744008733345</v>
       </c>
       <c r="F1889" t="n">
-        <v>-3.468587243529684</v>
+        <v>-3.663133213657993</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.085119214639186</v>
+        <v>0.9683916325622004</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.68515780608528</v>
+        <v>3.685157806085281</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-11.72625674009376</v>
+        <v>-11.92080271022207</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.515008486558048</v>
+        <v>-1.592826874609372</v>
       </c>
       <c r="F1890" t="n">
-        <v>-3.426660567942521</v>
+        <v>-3.62120653807083</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.119854293027692</v>
+        <v>1.003126710950707</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282101</v>
+        <v>3.684840248282102</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.43998192777107</v>
+        <v>-11.63452789789938</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.399359417072911</v>
+        <v>-1.477177805124235</v>
       </c>
       <c r="F1891" t="n">
-        <v>-3.426660567942521</v>
+        <v>-3.62120653807083</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.120993437583751</v>
+        <v>1.004265855506766</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116216</v>
+        <v>3.710931958116217</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.49287721581535</v>
+        <v>-11.68742318594366</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.417883758128518</v>
+        <v>-1.495702146179842</v>
       </c>
       <c r="F1892" t="n">
-        <v>-3.421705221854074</v>
+        <v>-3.616251191982383</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.126600419398927</v>
+        <v>1.009872837321942</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081568</v>
+        <v>3.76894809908157</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.20896848488661</v>
+        <v>-11.40351445501492</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.298586561518382</v>
+        <v>-1.376404949569706</v>
       </c>
       <c r="F1893" t="n">
-        <v>-3.421705221854074</v>
+        <v>-3.616251191982383</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.132334123637563</v>
+        <v>1.015606541560578</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425328</v>
+        <v>3.72857435442533</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.96198123469365</v>
+        <v>-11.15652720482196</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.209528923835067</v>
+        <v>-1.287347311886391</v>
       </c>
       <c r="F1894" t="n">
-        <v>-3.174717971661122</v>
+        <v>-3.369263941789431</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.270789211359469</v>
+        <v>1.154061629282484</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702413</v>
+        <v>3.747699084702414</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.69814436748958</v>
+        <v>-10.89269033761789</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.113877658266346</v>
+        <v>-1.19169604631767</v>
       </c>
       <c r="F1895" t="n">
-        <v>-3.174717971661122</v>
+        <v>-3.369263941789431</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.260905730046562</v>
+        <v>1.144178147969576</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.43090256662119</v>
+        <v>-10.6254485367495</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.008815498418361</v>
+        <v>-1.086633886469685</v>
       </c>
       <c r="F1896" t="n">
-        <v>-3.174717971661122</v>
+        <v>-3.369263941789431</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.259071169547188</v>
+        <v>1.142343587470203</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.1550934032207</v>
+        <v>-10.34963937334901</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.8987921480316277</v>
+        <v>-0.9766105360829518</v>
       </c>
       <c r="F1897" t="n">
-        <v>-3.085698663382389</v>
+        <v>-3.280244633510698</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.312182439540967</v>
+        <v>1.195454857463982</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.13113986224474</v>
+        <v>-10.32568583237305</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.8885422254957507</v>
+        <v>-0.9663606135470748</v>
       </c>
       <c r="F1898" t="n">
-        <v>-3.061745122406431</v>
+        <v>-3.25629109253474</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.327223070272036</v>
+        <v>1.21049548819505</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.867079923921947</v>
+        <v>-10.06162589405026</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.7961785663283845</v>
+        <v>-0.8739969543797086</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.797685184083635</v>
+        <v>-2.992231154211944</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.472398717103961</v>
+        <v>1.355671135026975</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.16000030041711</v>
+        <v>-9.35454627054542</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.5161337505867505</v>
+        <v>-0.5939521386380742</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.797685184083635</v>
+        <v>-2.992231154211944</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.46961168344366</v>
+        <v>1.352884101366675</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.11981600205092</v>
+        <v>-9.314361972179229</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.4997164073524329</v>
+        <v>-0.5775347954037566</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.757500885717445</v>
+        <v>-2.952046855845754</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.494065886351216</v>
+        <v>1.37733830427423</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.039746206513115</v>
+        <v>-9.234292176641425</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.4683216679165541</v>
+        <v>-0.5461400559678782</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.677431090179641</v>
+        <v>-2.87197706030795</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.541474584894655</v>
+        <v>1.42474700281767</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761811</v>
+        <v>3.787326853761809</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.806264984283516</v>
+        <v>-9.000810954411826</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.3670047501868621</v>
+        <v>-0.4448231382381858</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.443949867950042</v>
+        <v>-2.638495838078351</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.689487747070267</v>
+        <v>1.572760164993281</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255788</v>
+        <v>3.801633547255786</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.626556454139642</v>
+        <v>-8.821102424267952</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.2980135484422717</v>
+        <v>-0.3758319364935958</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.386778363787346</v>
+        <v>-2.581324333915655</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.720898439254925</v>
+        <v>1.60417085717794</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.76317867286043</v>
+        <v>3.763178672860428</v>
       </c>
       <c r="C1905" t="n">
-        <v>3.080628998079007</v>
+        <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.494280980508755</v>
+        <v>-8.688826950637065</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.3174398184382419</v>
+        <v>-0.3275542602942139</v>
       </c>
       <c r="F1905" t="n">
-        <v>-2.25450289015646</v>
+        <v>-2.449048860284769</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.727927263985132</v>
+        <v>1.678903628103499</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575956</v>
+        <v>3.784715218575954</v>
       </c>
       <c r="C1906" t="n">
-        <v>3.083444058766644</v>
+        <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.303681305835601</v>
+        <v>-8.498227275963911</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.2383848878813439</v>
+        <v>-0.2484993297373155</v>
       </c>
       <c r="F1906" t="n">
-        <v>-2.063903215483307</v>
+        <v>-2.258449185611616</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.84510212947666</v>
+        <v>1.796078493595027</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.75387899643099</v>
+        <v>3.753878996430989</v>
       </c>
       <c r="C1907" t="n">
-        <v>3.096350399990303</v>
+        <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.05468150715202</v>
+        <v>-8.24922747728033</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.1258786271842527</v>
+        <v>-0.1359930690402247</v>
       </c>
       <c r="F1907" t="n">
-        <v>-2.063903215483307</v>
+        <v>-2.258449185611616</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.858008470700319</v>
+        <v>1.808984834818686</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077648</v>
+        <v>3.692928280077646</v>
       </c>
       <c r="C1908" t="n">
-        <v>2.968374470391084</v>
+        <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.160271496925125</v>
+        <v>-8.354817467053435</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.2960905526927133</v>
+        <v>-0.3062049945486849</v>
       </c>
       <c r="F1908" t="n">
-        <v>-2.169493205256412</v>
+        <v>-2.364039175384721</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.666678547237238</v>
+        <v>1.617654911355604</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457905</v>
+        <v>3.770419008457904</v>
       </c>
       <c r="C1909" t="n">
-        <v>3.01691881226817</v>
+        <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.179006399043722</v>
+        <v>-8.373552369172032</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.2550401716630657</v>
+        <v>-0.2651546135190372</v>
       </c>
       <c r="F1909" t="n">
-        <v>-2.169493205256412</v>
+        <v>-2.364039175384721</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.715222889114324</v>
+        <v>1.666199253232691</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180813</v>
+        <v>3.76033011118081</v>
       </c>
       <c r="C1910" t="n">
-        <v>3.020297824254165</v>
+        <v>3.088001770449517</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.902268224372909</v>
+        <v>-8.096814194501219</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.1409658898087458</v>
+        <v>-0.1510803316647178</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.987676544146486</v>
+        <v>-2.182222514274795</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.827691897766274</v>
+        <v>1.778668261884641</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879206</v>
+        <v>3.723562653879203</v>
       </c>
       <c r="C1911" t="n">
-        <v>3.011583838000687</v>
+        <v>3.079287784196039</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.775375817937839</v>
+        <v>-7.969921788066149</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.09892291348819571</v>
+        <v>-0.1090373553441677</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.860784137711416</v>
+        <v>-2.055330107839725</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.895113355373838</v>
+        <v>1.846089719492205</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.72996614056811</v>
+        <v>3.729966140568107</v>
       </c>
       <c r="C1912" t="n">
-        <v>3.004623225905594</v>
+        <v>3.072327172100946</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.731827411167148</v>
+        <v>-7.926373381295458</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.08846416287501269</v>
+        <v>-0.09857860473098468</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.860784137711416</v>
+        <v>-2.055330107839725</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.888152743278745</v>
+        <v>1.839129107397111</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963422</v>
+        <v>3.782918957963418</v>
       </c>
       <c r="C1913" t="n">
-        <v>3.019085580286737</v>
+        <v>3.086789526482089</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.48967901771329</v>
+        <v>-7.6842249878416</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.02285754888767366</v>
+        <v>0.01274310703170167</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.860784137711416</v>
+        <v>-2.055330107839725</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.902615097659888</v>
+        <v>1.853591461778255</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192819</v>
+        <v>3.828547911192817</v>
       </c>
       <c r="C1914" t="n">
-        <v>3.013617700745932</v>
+        <v>3.081321646941284</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.426449645944942</v>
+        <v>-7.620995616073252</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.04268141805420766</v>
+        <v>0.03256697619823612</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.860784137711416</v>
+        <v>-2.055330107839725</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.897147218119083</v>
+        <v>1.84812358223745</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.82804935326205</v>
+        <v>3.828049353262047</v>
       </c>
       <c r="C1915" t="n">
-        <v>3.011115794756509</v>
+        <v>3.078819740951861</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.239961953567936</v>
+        <v>-7.434507923696246</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.1147745890155871</v>
+        <v>0.1046601471596151</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.67429644533441</v>
+        <v>-1.868842415462719</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.006537927555863</v>
+        <v>1.95751429167423</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389912</v>
+        <v>3.812450103389909</v>
       </c>
       <c r="C1916" t="n">
-        <v>3.018816772993834</v>
+        <v>3.086520719189187</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.218812754664492</v>
+        <v>-7.413358724792802</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.1309352468142899</v>
+        <v>0.1208208049583184</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.653147246430966</v>
+        <v>-1.847693216559275</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.026928425135255</v>
+        <v>1.977904789253622</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788096</v>
+        <v>3.748324832788095</v>
       </c>
       <c r="C1917" t="n">
-        <v>3.014597481340885</v>
+        <v>3.082301427536237</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.975047312681048</v>
+        <v>-7.169593282809358</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.2242221319547184</v>
+        <v>0.2141076900987469</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.653147246430966</v>
+        <v>-1.847693216559275</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.022709133482306</v>
+        <v>1.973685497600672</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527529</v>
+        <v>3.824307657527526</v>
       </c>
       <c r="C1918" t="n">
-        <v>3.016721795260901</v>
+        <v>3.084425741456253</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.711019245487789</v>
+        <v>-6.905565215616098</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.3319576727520381</v>
+        <v>0.3218432308960666</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.451281847615013</v>
+        <v>-1.645827817743322</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.145952686691894</v>
+        <v>2.096929050810261</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749187</v>
+        <v>3.826351398749185</v>
       </c>
       <c r="C1919" t="n">
-        <v>3.009463870244603</v>
+        <v>3.077167816439955</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.461168851538714</v>
+        <v>-6.655714821667024</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.4246399053153702</v>
+        <v>0.4145254634593987</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.451281847615013</v>
+        <v>-1.645827817743322</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.138694761675596</v>
+        <v>2.089671125793963</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481501</v>
+        <v>3.835954411481498</v>
       </c>
       <c r="C1920" t="n">
-        <v>3.013062993765252</v>
+        <v>3.080766939960604</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.157601362534735</v>
+        <v>-6.352147332663045</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.5496660244376104</v>
+        <v>0.5395515825816388</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.451281847615013</v>
+        <v>-1.645827817743322</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.142293885196245</v>
+        <v>2.093270249314612</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.78093033586299</v>
+        <v>3.780930335862987</v>
       </c>
       <c r="C1921" t="n">
-        <v>3.026390499819806</v>
+        <v>3.094094446015158</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.084121453682721</v>
+        <v>-6.278667423811031</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.5923854940329698</v>
+        <v>0.5822710521769978</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.377801938762998</v>
+        <v>-1.572347908891307</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.199709336562007</v>
+        <v>2.150685700680374</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102785</v>
+        <v>3.773761647102782</v>
       </c>
       <c r="C1922" t="n">
-        <v>3.025410977436103</v>
+        <v>3.093114923631455</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.859088454013898</v>
+        <v>-6.053634424142208</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.6814191715167959</v>
+        <v>0.6713047296608243</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.152768939094175</v>
+        <v>-1.347314909222484</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.333749613979598</v>
+        <v>2.284725978097964</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353079</v>
+        <v>3.764614304353077</v>
       </c>
       <c r="C1923" t="n">
-        <v>3.03010577849042</v>
+        <v>3.097809724685772</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.644454076377492</v>
+        <v>-5.839000046505801</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.7719677236256759</v>
+        <v>0.7618532817697043</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.9381345614577685</v>
+        <v>-1.132680531586078</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.467225041615759</v>
+        <v>2.418201405734126</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544787</v>
+        <v>3.798811195544785</v>
       </c>
       <c r="C1924" t="n">
-        <v>3.011300037274216</v>
+        <v>3.079003983469568</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.37785371940314</v>
+        <v>-5.57239968953145</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.8598021251992125</v>
+        <v>0.8496876833432405</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.9381345614577685</v>
+        <v>-1.132680531586078</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.448419300399555</v>
+        <v>2.399395664517922</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712299</v>
+        <v>3.797691308712296</v>
       </c>
       <c r="C1925" t="n">
-        <v>3.013043113899093</v>
+        <v>3.080747060094445</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.137423222598279</v>
+        <v>-5.331969192726589</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.9577174005460338</v>
+        <v>0.9476029586900623</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.6977040646529082</v>
+        <v>-0.8922500347812172</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.594420675107348</v>
+        <v>2.545397039225715</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837689</v>
+        <v>3.821589933837688</v>
       </c>
       <c r="C1926" t="n">
-        <v>3.016972427733913</v>
+        <v>3.084676373929265</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.894632414948834</v>
+        <v>-5.089178385077144</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.058763037440632</v>
+        <v>1.04864859558466</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.6977040646529082</v>
+        <v>-0.8922500347812172</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.598349988942168</v>
+        <v>2.549326353060535</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349971</v>
+        <v>3.822323422349969</v>
       </c>
       <c r="C1927" t="n">
-        <v>3.017651011651253</v>
+        <v>3.085354957846605</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.655027323341745</v>
+        <v>-4.849573293470055</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.155283658000808</v>
+        <v>1.145169216144836</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.6306561169844137</v>
+        <v>-0.8252020871127227</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.639257341460605</v>
+        <v>2.590233705578972</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972344</v>
+        <v>3.848613050972343</v>
       </c>
       <c r="C1928" t="n">
-        <v>3.014649082871247</v>
+        <v>3.082353029066599</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.412371734918581</v>
+        <v>-4.606917705046891</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.249343964590067</v>
+        <v>1.239229522734095</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.6306561169844137</v>
+        <v>-0.8252020871127227</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.636255412680599</v>
+        <v>2.587231776798966</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145944</v>
+        <v>3.818665376145943</v>
       </c>
       <c r="C1929" t="n">
-        <v>3.016228119881861</v>
+        <v>3.083932066077213</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.192350936881571</v>
+        <v>-4.386896907009881</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.338931320815485</v>
+        <v>1.328816878959513</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.4894362719164335</v>
+        <v>-0.6839822420447425</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.722566356732001</v>
+        <v>2.673542720850368</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009956</v>
+        <v>3.843270952009955</v>
       </c>
       <c r="C1930" t="n">
-        <v>3.032122302683684</v>
+        <v>3.099826248879036</v>
       </c>
       <c r="D1930" t="n">
-        <v>-3.993102306976762</v>
+        <v>-4.187648277105072</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.434524955579232</v>
+        <v>1.42441051372326</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.4894362719164335</v>
+        <v>-0.6839822420447425</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.738460539533824</v>
+        <v>2.689436903652191</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966262</v>
+        <v>3.845043810966259</v>
       </c>
       <c r="C1931" t="n">
-        <v>3.033268147123986</v>
+        <v>3.100972093319338</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.833587203457392</v>
+        <v>-4.028133173585702</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.499476841427282</v>
+        <v>1.48936239957131</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.3299211683970635</v>
+        <v>-0.5244671385253725</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.835315446085748</v>
+        <v>2.786291810204115</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.790071705107584</v>
+        <v>3.467005179725582</v>
       </c>
       <c r="C1932" t="n">
-        <v>3.043356249685426</v>
+        <v>3.111060195880778</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.688915058357654</v>
+        <v>-3.883461028485964</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.567433802028617</v>
+        <v>1.557319360172645</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.1852490232973261</v>
+        <v>-0.3797949934256351</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.932206835707031</v>
+        <v>2.883183199825397</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240413.xlsx
+++ b/tame_output/ON/bt/strategyON_20240413.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>51.4%</t>
+          <t>63.9%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>68.1%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1929</v>
+        <v>1930</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,12 +628,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>69.2%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.5%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-17.5%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.8%</t>
+          <t>-11.6%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>50.9%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>72.7%</t>
+          <t>73.4%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>28.8%</t>
+          <t>29.2%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1929</v>
+        <v>1930</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,40 +786,40 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>31.1%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>27.6%</t>
+          <t>28.1%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>15.5%</t>
+          <t>20.1%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2021-03-21</t>
+          <t>2024-03-04</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2021-03-24</t>
+          <t>2024-03-19</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-11.3%</t>
+          <t>-14.9%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -834,12 +834,12 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>6.8%</t>
+          <t>7.0%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-3.5%</t>
+          <t>-4.0%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>60.2%</t>
+          <t>58.7%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>23.4%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-5.0%</t>
+          <t>-5.2%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>2.5%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.0%</t>
+          <t>-77.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>118.6%</t>
+          <t>118.1%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1929</v>
+        <v>1930</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,17 +944,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>138.2%</t>
+          <t>137.2%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>97.6%</t>
+          <t>97.7%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -973,11 +973,11 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-741.9%</t>
+          <t>-722.5%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-57.4%</t>
+          <t>-56.3%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.0%</t>
+          <t>-73.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>98.3%</t>
+          <t>98.0%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>497.9%</t>
+          <t>493.0%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>6.6%</t>
+          <t>10.1%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-549.9%</t>
+          <t>-520.1%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>15.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>55.2%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1929</v>
+        <v>1930</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,12 +1102,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>65.9%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1131,11 +1131,11 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-291.4%</t>
+          <t>-283.6%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-44.9%</t>
+          <t>-44.0%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>12.6%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>46.1%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-18.7%</t>
+          <t>-13.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>347.6%</t>
+          <t>90.0%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-220.5%</t>
+          <t>-214.9%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-31.4%</t>
+          <t>-26.8%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>71.6%</t>
+          <t>70.7%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1929</v>
+        <v>1930</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,17 +1260,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>72.5%</t>
+          <t>71.0%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>69.9%</t>
+          <t>70.0%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1289,11 +1289,11 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-306.6%</t>
+          <t>-296.3%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-39.0%</t>
+          <t>-37.2%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-24.4%</t>
+          <t>-19.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>59.4%</t>
+          <t>58.7%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>31.1%</t>
+          <t>36.7%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-152.0%</t>
+          <t>-148.0%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-262.0%</t>
+          <t>-232.2%</t>
         </is>
       </c>
     </row>
@@ -1390,26 +1390,26 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>49.4%</t>
+          <t>56.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>51.6%</t>
+          <t>51.5%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1929</v>
+        <v>1930</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,22 +1418,22 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.5%</t>
+          <t>62.7%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>41.6%</t>
+          <t>42.2%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>98.1%</t>
+          <t>97.7%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1447,11 +1447,11 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-184.4%</t>
+          <t>-178.1%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>12.6%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-33.7%</t>
+          <t>-32.1%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>51.5%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.1%</t>
+          <t>43.0%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.8%</t>
+          <t>-17.4%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>34.1%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-157.7%</t>
+          <t>-132.6%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1932"/>
+  <dimension ref="A1:G1933"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43727,22 +43727,22 @@
         <v>45296</v>
       </c>
       <c r="B1834" t="n">
-        <v>3.317575502045693</v>
+        <v>3.317575502045692</v>
       </c>
       <c r="C1834" t="n">
         <v>3.13991794227561</v>
       </c>
       <c r="D1834" t="n">
-        <v>0.858629459151194</v>
+        <v>0.9621230735079426</v>
       </c>
       <c r="E1834" t="n">
-        <v>3.483013301622341</v>
+        <v>3.52441074736504</v>
       </c>
       <c r="F1834" t="n">
-        <v>1.880332741705669</v>
+        <v>1.983826356062417</v>
       </c>
       <c r="G1834" t="n">
-        <v>4.268117587299011</v>
+        <v>4.330213755913061</v>
       </c>
     </row>
     <row r="1835">
@@ -43750,22 +43750,22 @@
         <v>45297</v>
       </c>
       <c r="B1835" t="n">
-        <v>3.320996253831154</v>
+        <v>3.320996253831153</v>
       </c>
       <c r="C1835" t="n">
         <v>3.138175778137954</v>
       </c>
       <c r="D1835" t="n">
-        <v>0.8580776593093818</v>
+        <v>0.9615712736661304</v>
       </c>
       <c r="E1835" t="n">
-        <v>3.48105041754796</v>
+        <v>3.52244786329066</v>
       </c>
       <c r="F1835" t="n">
-        <v>1.881174505190975</v>
+        <v>1.984668119547724</v>
       </c>
       <c r="G1835" t="n">
-        <v>4.26688048125254</v>
+        <v>4.328976649866589</v>
       </c>
     </row>
     <row r="1836">
@@ -43779,16 +43779,16 @@
         <v>3.118001050765402</v>
       </c>
       <c r="D1836" t="n">
-        <v>0.7523907713670821</v>
+        <v>0.8558843857238307</v>
       </c>
       <c r="E1836" t="n">
-        <v>3.418600934998487</v>
+        <v>3.459998380741187</v>
       </c>
       <c r="F1836" t="n">
-        <v>1.866613431488292</v>
+        <v>1.97010704584504</v>
       </c>
       <c r="G1836" t="n">
-        <v>4.237969109658377</v>
+        <v>4.300065278272426</v>
       </c>
     </row>
     <row r="1837">
@@ -43802,16 +43802,16 @@
         <v>3.118490189491276</v>
       </c>
       <c r="D1837" t="n">
-        <v>0.7582401524823265</v>
+        <v>0.8617337668390751</v>
       </c>
       <c r="E1837" t="n">
-        <v>3.421429826170459</v>
+        <v>3.462827271913159</v>
       </c>
       <c r="F1837" t="n">
-        <v>1.866613431488292</v>
+        <v>1.97010704584504</v>
       </c>
       <c r="G1837" t="n">
-        <v>4.238458248384251</v>
+        <v>4.300554416998301</v>
       </c>
     </row>
     <row r="1838">
@@ -43825,16 +43825,16 @@
         <v>3.122570172112943</v>
       </c>
       <c r="D1838" t="n">
-        <v>0.7100178856352429</v>
+        <v>0.8135114999919916</v>
       </c>
       <c r="E1838" t="n">
-        <v>3.406220902053293</v>
+        <v>3.447618347795992</v>
       </c>
       <c r="F1838" t="n">
-        <v>1.818391164641208</v>
+        <v>1.921884778997957</v>
       </c>
       <c r="G1838" t="n">
-        <v>4.213604870897668</v>
+        <v>4.275701039511717</v>
       </c>
     </row>
     <row r="1839">
@@ -43842,22 +43842,22 @@
         <v>45301</v>
       </c>
       <c r="B1839" t="n">
-        <v>3.376932391386095</v>
+        <v>3.376932391386094</v>
       </c>
       <c r="C1839" t="n">
         <v>3.157511256610484</v>
       </c>
       <c r="D1839" t="n">
-        <v>0.4728863937854478</v>
+        <v>0.5763800081421965</v>
       </c>
       <c r="E1839" t="n">
-        <v>3.346309389810916</v>
+        <v>3.387706835553616</v>
       </c>
       <c r="F1839" t="n">
-        <v>1.818391164641208</v>
+        <v>1.921884778997957</v>
       </c>
       <c r="G1839" t="n">
-        <v>4.24854595539521</v>
+        <v>4.310642124009259</v>
       </c>
     </row>
     <row r="1840">
@@ -43865,22 +43865,22 @@
         <v>45302</v>
       </c>
       <c r="B1840" t="n">
-        <v>3.367370539998562</v>
+        <v>3.367370539998561</v>
       </c>
       <c r="C1840" t="n">
         <v>3.156088696795822</v>
       </c>
       <c r="D1840" t="n">
-        <v>0.4779239845130344</v>
+        <v>0.5814175988697829</v>
       </c>
       <c r="E1840" t="n">
-        <v>3.346901866287289</v>
+        <v>3.388299312029988</v>
       </c>
       <c r="F1840" t="n">
-        <v>1.874035620907526</v>
+        <v>1.977529235264274</v>
       </c>
       <c r="G1840" t="n">
-        <v>4.280510069340338</v>
+        <v>4.342606237954387</v>
       </c>
     </row>
     <row r="1841">
@@ -43894,16 +43894,16 @@
         <v>3.13483507841956</v>
       </c>
       <c r="D1841" t="n">
-        <v>0.4214543533367376</v>
+        <v>0.5249479676934862</v>
       </c>
       <c r="E1841" t="n">
-        <v>3.303060395440507</v>
+        <v>3.344457841183207</v>
       </c>
       <c r="F1841" t="n">
-        <v>1.817565989731229</v>
+        <v>1.921059604087977</v>
       </c>
       <c r="G1841" t="n">
-        <v>4.225374672258297</v>
+        <v>4.287470840872346</v>
       </c>
     </row>
     <row r="1842">
@@ -43917,16 +43917,16 @@
         <v>3.13585268755003</v>
       </c>
       <c r="D1842" t="n">
-        <v>0.3556869632873255</v>
+        <v>0.4591805776440741</v>
       </c>
       <c r="E1842" t="n">
-        <v>3.277771048551212</v>
+        <v>3.319168494293912</v>
       </c>
       <c r="F1842" t="n">
-        <v>1.817565989731229</v>
+        <v>1.921059604087977</v>
       </c>
       <c r="G1842" t="n">
-        <v>4.226392281388767</v>
+        <v>4.288488450002816</v>
       </c>
     </row>
     <row r="1843">
@@ -43940,16 +43940,16 @@
         <v>3.126480719537785</v>
       </c>
       <c r="D1843" t="n">
-        <v>0.3421514795106159</v>
+        <v>0.4456450938673645</v>
       </c>
       <c r="E1843" t="n">
-        <v>3.262984887028284</v>
+        <v>3.304382332770984</v>
       </c>
       <c r="F1843" t="n">
-        <v>1.817565989731229</v>
+        <v>1.921059604087977</v>
       </c>
       <c r="G1843" t="n">
-        <v>4.217020313376523</v>
+        <v>4.279116481990572</v>
       </c>
     </row>
     <row r="1844">
@@ -43957,22 +43957,22 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.298730590706672</v>
+        <v>3.298730590706673</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
       </c>
       <c r="D1844" t="n">
-        <v>0.2603795790828642</v>
+        <v>0.3638731934396128</v>
       </c>
       <c r="E1844" t="n">
-        <v>3.220358852812422</v>
+        <v>3.261756298555122</v>
       </c>
       <c r="F1844" t="n">
-        <v>1.844601563137365</v>
+        <v>1.948095177494114</v>
       </c>
       <c r="G1844" t="n">
-        <v>4.223324383375443</v>
+        <v>4.285420551989492</v>
       </c>
     </row>
     <row r="1845">
@@ -43980,22 +43980,22 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296839</v>
+        <v>3.29991811929684</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>0.1931704712109866</v>
+        <v>0.2966640855677352</v>
       </c>
       <c r="E1845" t="n">
-        <v>3.198240526497373</v>
+        <v>3.239637972240073</v>
       </c>
       <c r="F1845" t="n">
-        <v>1.844601563137365</v>
+        <v>1.948095177494114</v>
       </c>
       <c r="G1845" t="n">
-        <v>4.228089700209145</v>
+        <v>4.290185868823194</v>
       </c>
     </row>
     <row r="1846">
@@ -44009,16 +44009,16 @@
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>0.1971619240061768</v>
+        <v>0.3006555383629254</v>
       </c>
       <c r="E1846" t="n">
-        <v>3.19766190373469</v>
+        <v>3.239059349477389</v>
       </c>
       <c r="F1846" t="n">
-        <v>1.848593015932555</v>
+        <v>1.952086630289304</v>
       </c>
       <c r="G1846" t="n">
-        <v>4.228309368005499</v>
+        <v>4.290405536619549</v>
       </c>
     </row>
     <row r="1847">
@@ -44032,16 +44032,16 @@
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-0.2205920995406602</v>
+        <v>-0.1170984851839116</v>
       </c>
       <c r="E1847" t="n">
-        <v>3.028487185821018</v>
+        <v>3.069884631563717</v>
       </c>
       <c r="F1847" t="n">
-        <v>1.430838992385719</v>
+        <v>1.534332606742467</v>
       </c>
       <c r="G1847" t="n">
-        <v>3.975583845382461</v>
+        <v>4.03768001399651</v>
       </c>
     </row>
     <row r="1848">
@@ -44055,16 +44055,16 @@
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-0.4422140330987777</v>
+        <v>-0.3387204187420291</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.939704628996693</v>
+        <v>2.981102074739392</v>
       </c>
       <c r="F1848" t="n">
-        <v>1.393312858698349</v>
+        <v>1.496806473055098</v>
       </c>
       <c r="G1848" t="n">
-        <v>3.952934381768961</v>
+        <v>4.01503055038301</v>
       </c>
     </row>
     <row r="1849">
@@ -44072,22 +44072,22 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382193</v>
+        <v>3.272760131382194</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-0.6502180914518549</v>
+        <v>-0.5467244770951063</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.861395150209387</v>
+        <v>2.902792595952087</v>
       </c>
       <c r="F1849" t="n">
-        <v>1.393312858698349</v>
+        <v>1.496806473055098</v>
       </c>
       <c r="G1849" t="n">
-        <v>3.957826526322886</v>
+        <v>4.019922694936936</v>
       </c>
     </row>
     <row r="1850">
@@ -44101,16 +44101,16 @@
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-0.9206180541607403</v>
+        <v>-0.8171244398039916</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.748316621463821</v>
+        <v>2.78971406720652</v>
       </c>
       <c r="F1850" t="n">
-        <v>1.122912895989464</v>
+        <v>1.226406510346213</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.790668005035543</v>
+        <v>3.852764173649592</v>
       </c>
     </row>
     <row r="1851">
@@ -44124,16 +44124,16 @@
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-1.259776431749262</v>
+        <v>-1.156282817392514</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.605737569734861</v>
+        <v>2.647135015477561</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.783754518400942</v>
+        <v>0.8872481327576904</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.580257277788879</v>
+        <v>3.642353446402928</v>
       </c>
     </row>
     <row r="1852">
@@ -44147,16 +44147,16 @@
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-1.587793653476741</v>
+        <v>-1.484300039119993</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.494868970782638</v>
+        <v>2.536266416525337</v>
       </c>
       <c r="F1852" t="n">
-        <v>0.4557372966734629</v>
+        <v>0.5592309110302113</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.40378523449116</v>
+        <v>3.465881403105209</v>
       </c>
     </row>
     <row r="1853">
@@ -44164,22 +44164,22 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416048</v>
+        <v>3.231167537416047</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.081118525011919</v>
+        <v>-1.977624910655171</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.305637772577136</v>
+        <v>2.347035218319835</v>
       </c>
       <c r="F1853" t="n">
-        <v>0.3507511824338441</v>
+        <v>0.4542447967905925</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.348892316355957</v>
+        <v>3.410988484970006</v>
       </c>
     </row>
     <row r="1854">
@@ -44187,22 +44187,22 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382331</v>
+        <v>3.23598197738233</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-2.573503553036016</v>
+        <v>-2.470009938679268</v>
       </c>
       <c r="E1854" t="n">
-        <v>2.109790153411229</v>
+        <v>2.151187599153928</v>
       </c>
       <c r="F1854" t="n">
-        <v>-0.1416338455902526</v>
+        <v>-0.03814023123350418</v>
       </c>
       <c r="G1854" t="n">
-        <v>3.054567691585231</v>
+        <v>3.11666386019928</v>
       </c>
     </row>
     <row r="1855">
@@ -44210,22 +44210,22 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495502</v>
+        <v>3.278199702495501</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-2.958683943966089</v>
+        <v>-2.85519032960934</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.954260535852063</v>
+        <v>1.995657981594762</v>
       </c>
       <c r="F1855" t="n">
-        <v>-0.1416338455902526</v>
+        <v>-0.03814023123350418</v>
       </c>
       <c r="G1855" t="n">
-        <v>3.053110230398095</v>
+        <v>3.115206399012143</v>
       </c>
     </row>
     <row r="1856">
@@ -44233,22 +44233,22 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347058</v>
+        <v>3.299136146347057</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-3.302366717192751</v>
+        <v>-3.198873102836003</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.818556550016014</v>
+        <v>1.859953995758714</v>
       </c>
       <c r="F1856" t="n">
-        <v>-0.2495398976174708</v>
+        <v>-0.1460462832607224</v>
       </c>
       <c r="G1856" t="n">
-        <v>2.99013572263638</v>
+        <v>3.052231891250429</v>
       </c>
     </row>
     <row r="1857">
@@ -44256,22 +44256,22 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.28737757613002</v>
+        <v>3.287377576130019</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-3.660017067431099</v>
+        <v>-3.556523453074351</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.671602468576933</v>
+        <v>1.712999914319632</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.6071902478558189</v>
+        <v>-0.5036966334990705</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.771651571149629</v>
+        <v>2.833747739763678</v>
       </c>
     </row>
     <row r="1858">
@@ -44279,22 +44279,22 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178247</v>
+        <v>3.315884374178246</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-3.96925117042715</v>
+        <v>-3.865757556070401</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.549681754078772</v>
+        <v>1.591079199821472</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.6071902478558189</v>
+        <v>-0.5036966334990705</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.773424497849888</v>
+        <v>2.835520666463937</v>
       </c>
     </row>
     <row r="1859">
@@ -44302,22 +44302,22 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207817</v>
+        <v>3.305316798207815</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.401056963576938</v>
+        <v>-4.297563349220189</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.363292324286261</v>
+        <v>1.404689770028961</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.7436077442970859</v>
+        <v>-0.6401141299403375</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.677906887452532</v>
+        <v>2.740003056066582</v>
       </c>
     </row>
     <row r="1860">
@@ -44325,22 +44325,22 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310986</v>
+        <v>3.284619513310984</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-4.727489492444682</v>
+        <v>-4.623995878087933</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.221004087741254</v>
+        <v>1.262401533483954</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.826075994804234</v>
+        <v>-0.7225823804474856</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.616710712150335</v>
+        <v>2.678806880764383</v>
       </c>
     </row>
     <row r="1861">
@@ -44348,22 +44348,22 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006537</v>
+        <v>3.305849539006535</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.063152139675134</v>
+        <v>-4.959658525318385</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.085319620505039</v>
+        <v>1.126717066247738</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.826075994804234</v>
+        <v>-0.7225823804474856</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.6152913038063</v>
+        <v>2.677387472420349</v>
       </c>
     </row>
     <row r="1862">
@@ -44371,22 +44371,22 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309427</v>
+        <v>3.311086391309426</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.426778384575448</v>
+        <v>-5.323284770218699</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.9463566827791547</v>
+        <v>0.9877541285218543</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.9242976316713598</v>
+        <v>-0.8208040173146114</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.562845881920266</v>
+        <v>2.624942050534315</v>
       </c>
     </row>
     <row r="1863">
@@ -44394,22 +44394,22 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970908</v>
+        <v>3.304715716970907</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-5.791905767214194</v>
+        <v>-5.688412152857445</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.7995602447294878</v>
+        <v>0.8409576904721874</v>
       </c>
       <c r="F1863" t="n">
-        <v>-1.220608415970372</v>
+        <v>-1.117114801613624</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.38431392634669</v>
+        <v>2.446410094960739</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.200494544394873</v>
+        <v>-6.097000930038124</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.634886277871975</v>
+        <v>0.6762837236146746</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.629197193151051</v>
+        <v>-1.525703578794302</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.137922204053042</v>
+        <v>2.200018372667091</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.613477028535967</v>
+        <v>-6.509983414179218</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.4648787166869983</v>
+        <v>0.5062761624296979</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.629197193151051</v>
+        <v>-1.525703578794302</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.133107636524502</v>
+        <v>2.195203805138551</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.029868902822964</v>
+        <v>-6.926375288466216</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.2963160175810766</v>
+        <v>0.3377134633237762</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.629197193151051</v>
+        <v>-1.525703578794302</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.13110168713338</v>
+        <v>2.193197855747429</v>
       </c>
     </row>
     <row r="1867">
@@ -44492,16 +44492,16 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.406545913352809</v>
+        <v>-7.30305229899606</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.1559039040378178</v>
+        <v>0.1973013497805174</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.629197193151051</v>
+        <v>-1.525703578794302</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.141360377802059</v>
+        <v>2.203456546416108</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-7.752420735337617</v>
+        <v>-7.648927120980868</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.01365354038958966</v>
+        <v>0.0550509861322892</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.629197193151051</v>
+        <v>-1.525703578794302</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.137459942947754</v>
+        <v>2.199556111561803</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.065245534582596</v>
+        <v>-7.961751920225848</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.1130714592534008</v>
+        <v>-0.07167401351070168</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.629197193151051</v>
+        <v>-1.525703578794302</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.135864863002755</v>
+        <v>2.197961031616804</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.361906876392794</v>
+        <v>-8.258413262036045</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.2279570200482719</v>
+        <v>-0.1865595743055724</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.697940328884929</v>
+        <v>-1.594446714528181</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.098397957491636</v>
+        <v>2.160494126105685</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.795255984503029</v>
+        <v>-8.691762370146281</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.4053229678267694</v>
+        <v>-0.3639255220840698</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.697940328884929</v>
+        <v>-1.594446714528181</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.094371652957232</v>
+        <v>2.156467821571281</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.17825737324566</v>
+        <v>-9.074763758888912</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.5586256246454058</v>
+        <v>-0.5172281789027062</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.697940328884929</v>
+        <v>-1.594446714528181</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.094269551635648</v>
+        <v>2.156365720249697</v>
       </c>
     </row>
     <row r="1873">
@@ -44624,22 +44624,22 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.44775050131762</v>
+        <v>3.447750501317621</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.553242699416938</v>
+        <v>-9.449749085060189</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.7060482391424867</v>
+        <v>-0.6646507933997872</v>
       </c>
       <c r="F1873" t="n">
-        <v>-2.072925655056207</v>
+        <v>-1.969432040699458</v>
       </c>
       <c r="G1873" t="n">
-        <v>1.871849871904312</v>
+        <v>1.933946040518361</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.912773021920939</v>
+        <v>-9.80927940756419</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.8445100648460371</v>
+        <v>-0.8031126191033375</v>
       </c>
       <c r="F1874" t="n">
-        <v>-2.072925655056207</v>
+        <v>-1.969432040699458</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.877200175202362</v>
+        <v>1.939296343816411</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-10.23917305058595</v>
+        <v>-10.1356794362292</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.9671540563548651</v>
+        <v>-0.9257566106121655</v>
       </c>
       <c r="F1875" t="n">
-        <v>-2.39932568372122</v>
+        <v>-2.295832069364471</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.689276177960532</v>
+        <v>1.751372346574581</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.45832201866015</v>
+        <v>-10.3548284043034</v>
       </c>
       <c r="E1876" t="n">
-        <v>-1.051771892962775</v>
+        <v>-1.010374447220075</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.618474651795417</v>
+        <v>-2.514981037438669</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.560828547737782</v>
+        <v>1.622924716351831</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,22 +44716,22 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407494</v>
+        <v>3.492445136407497</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.45463109370374</v>
+        <v>-10.35113747934699</v>
       </c>
       <c r="E1877" t="n">
-        <v>-1.050295522980211</v>
+        <v>-1.008898077237511</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.618474651795417</v>
+        <v>-2.514981037438669</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.560828547737782</v>
+        <v>1.622924716351831</v>
       </c>
     </row>
     <row r="1878">
@@ -44739,22 +44739,22 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611697</v>
+        <v>3.502786823611699</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.6588892690336</v>
+        <v>-10.55539565467685</v>
       </c>
       <c r="E1878" t="n">
-        <v>-1.126485595993514</v>
+        <v>-1.085088150250814</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.746113596409406</v>
+        <v>-2.642619982052658</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.489758378088031</v>
+        <v>1.551854546702081</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199886</v>
+        <v>3.496848329199889</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.87692704066478</v>
+        <v>-10.77343342630803</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.209218150161548</v>
+        <v>-1.167820704418849</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.920884364505305</v>
+        <v>-2.817390750148557</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.389378471714928</v>
+        <v>1.451474640328977</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910629</v>
+        <v>3.499968163910631</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.99800317912564</v>
+        <v>-10.69996359464058</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.242276904052471</v>
+        <v>-1.123061070258449</v>
       </c>
       <c r="F1880" t="n">
-        <v>-3.041960502966166</v>
+        <v>-2.743920918481108</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.332104490131833</v>
+        <v>1.510928240822867</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078597</v>
+        <v>3.490055666078599</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-11.17312759651218</v>
+        <v>-10.87508801202713</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.297771450259573</v>
+        <v>-1.178555616465549</v>
       </c>
       <c r="F1881" t="n">
-        <v>-3.217084920352709</v>
+        <v>-2.919045335867652</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.241585060447423</v>
+        <v>1.420408811138458</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.48587501888027</v>
+        <v>3.485875018880271</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-11.40757969052667</v>
+        <v>-11.10954010604162</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.398771452766964</v>
+        <v>-1.279555618972941</v>
       </c>
       <c r="F1882" t="n">
-        <v>-3.217084920352709</v>
+        <v>-2.919045335867652</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.234365895545827</v>
+        <v>1.413189646236862</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234395</v>
+        <v>3.480688917234397</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.69538353506391</v>
+        <v>-11.39734395057885</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.520565181355836</v>
+        <v>-1.401349347561812</v>
       </c>
       <c r="F1883" t="n">
-        <v>-3.504888764889948</v>
+        <v>-3.20684918040489</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.055011398049508</v>
+        <v>1.233835148740543</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860585</v>
+        <v>3.493712438860586</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-11.92520798222774</v>
+        <v>-11.62716839774268</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.61137917038281</v>
+        <v>-1.492163336588786</v>
       </c>
       <c r="F1884" t="n">
-        <v>-3.667536301960108</v>
+        <v>-3.369496717475051</v>
       </c>
       <c r="G1884" t="n">
-        <v>0.9585386656459685</v>
+        <v>1.137362416337003</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767398</v>
+        <v>3.4920980657674</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-12.157236901964</v>
+        <v>-11.85919731747894</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.7014970096482</v>
+        <v>-1.582281175854176</v>
       </c>
       <c r="F1885" t="n">
-        <v>-3.729548999148531</v>
+        <v>-3.431509414663474</v>
       </c>
       <c r="G1885" t="n">
-        <v>0.924024775962029</v>
+        <v>1.102848526653064</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792543</v>
+        <v>3.573670449792544</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-12.10522138799519</v>
+        <v>-11.80718180351013</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.676700468374274</v>
+        <v>-1.55748463458025</v>
       </c>
       <c r="F1886" t="n">
-        <v>-3.729548999148531</v>
+        <v>-3.431509414663474</v>
       </c>
       <c r="G1886" t="n">
-        <v>0.9280151116484299</v>
+        <v>1.106838862339464</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.60003468962892</v>
+        <v>3.600034689628922</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-12.24689322971931</v>
+        <v>-11.94885364523425</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.734844431962664</v>
+        <v>-1.61562859816864</v>
       </c>
       <c r="F1887" t="n">
-        <v>-3.729548999148531</v>
+        <v>-3.431509414663474</v>
       </c>
       <c r="G1887" t="n">
-        <v>0.9265398847496882</v>
+        <v>1.105363635440723</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410718</v>
+        <v>3.69156815841072</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-12.34579997017858</v>
+        <v>-12.04776038569352</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.759353717981501</v>
+        <v>-1.640137884187478</v>
       </c>
       <c r="F1888" t="n">
-        <v>-3.828455739607806</v>
+        <v>-3.53041615512275</v>
       </c>
       <c r="G1888" t="n">
-        <v>0.8822492506389956</v>
+        <v>1.06107300133003</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240578</v>
+        <v>3.676837974240579</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-12.14664786294148</v>
+        <v>-11.84860827845642</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.692744008733345</v>
+        <v>-1.573528174939321</v>
       </c>
       <c r="F1889" t="n">
-        <v>-3.663133213657993</v>
+        <v>-3.365093629172936</v>
       </c>
       <c r="G1889" t="n">
-        <v>0.9683916325622004</v>
+        <v>1.147215383253235</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-11.92080271022207</v>
+        <v>-11.62276312573701</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.592826874609372</v>
+        <v>-1.473611040815348</v>
       </c>
       <c r="F1890" t="n">
-        <v>-3.62120653807083</v>
+        <v>-3.323166953585773</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.003126710950707</v>
+        <v>1.181950461641741</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282102</v>
+        <v>3.684840248282103</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.63452789789938</v>
+        <v>-11.33648831341432</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.477177805124235</v>
+        <v>-1.357961971330211</v>
       </c>
       <c r="F1891" t="n">
-        <v>-3.62120653807083</v>
+        <v>-3.323166953585773</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.004265855506766</v>
+        <v>1.1830896061978</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116217</v>
+        <v>3.710931958116218</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.68742318594366</v>
+        <v>-11.3893836014586</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.495702146179842</v>
+        <v>-1.376486312385818</v>
       </c>
       <c r="F1892" t="n">
-        <v>-3.616251191982383</v>
+        <v>-3.318211607497326</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.009872837321942</v>
+        <v>1.188696588012976</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.40351445501492</v>
+        <v>-11.10547487052986</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.376404949569706</v>
+        <v>-1.257189115775682</v>
       </c>
       <c r="F1893" t="n">
-        <v>-3.616251191982383</v>
+        <v>-3.318211607497326</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.015606541560578</v>
+        <v>1.194430292251612</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-11.15652720482196</v>
+        <v>-10.8584876203369</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.287347311886391</v>
+        <v>-1.168131478092366</v>
       </c>
       <c r="F1894" t="n">
-        <v>-3.369263941789431</v>
+        <v>-3.071224357304374</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.154061629282484</v>
+        <v>1.332885379973518</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.89269033761789</v>
+        <v>-10.59465075313283</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.19169604631767</v>
+        <v>-1.072480212523646</v>
       </c>
       <c r="F1895" t="n">
-        <v>-3.369263941789431</v>
+        <v>-3.071224357304374</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.144178147969576</v>
+        <v>1.32300189866061</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906229</v>
+        <v>3.76631350390623</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.6254485367495</v>
+        <v>-10.32740895226444</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.086633886469685</v>
+        <v>-0.9674180526756611</v>
       </c>
       <c r="F1896" t="n">
-        <v>-3.369263941789431</v>
+        <v>-3.071224357304374</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.142343587470203</v>
+        <v>1.321167338161237</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.34963937334901</v>
+        <v>-10.05159978886395</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.9766105360829518</v>
+        <v>-0.8573947022889272</v>
       </c>
       <c r="F1897" t="n">
-        <v>-3.280244633510698</v>
+        <v>-2.982205049025641</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.195454857463982</v>
+        <v>1.374278608155016</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.32568583237305</v>
+        <v>-10.02764624788799</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.9663606135470748</v>
+        <v>-0.8471447797530511</v>
       </c>
       <c r="F1898" t="n">
-        <v>-3.25629109253474</v>
+        <v>-2.958251508049683</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.21049548819505</v>
+        <v>1.389319238886084</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487776</v>
+        <v>3.789307536487775</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.06162589405026</v>
+        <v>-9.763586309565197</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.8739969543797086</v>
+        <v>-0.754781120585684</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.992231154211944</v>
+        <v>-2.694191569726887</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.355671135026975</v>
+        <v>1.53449488571801</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309729</v>
+        <v>3.833249172309728</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.35454627054542</v>
+        <v>-9.056506686060359</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.5939521386380742</v>
+        <v>-0.47473630484405</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.992231154211944</v>
+        <v>-2.694191569726887</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.352884101366675</v>
+        <v>1.531707852057709</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858732</v>
+        <v>3.839370871858731</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.314361972179229</v>
+        <v>-9.016322387694169</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.5775347954037566</v>
+        <v>-0.4583189616097325</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.952046855845754</v>
+        <v>-2.654007271360697</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.37733830427423</v>
+        <v>1.556162054965265</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096478</v>
+        <v>3.856158176096477</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.234292176641425</v>
+        <v>-8.936252592156364</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.5461400559678782</v>
+        <v>-0.4269242221738541</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.87197706030795</v>
+        <v>-2.573937475822893</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.42474700281767</v>
+        <v>1.603570753508704</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761809</v>
+        <v>3.78732685376181</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-9.000810954411826</v>
+        <v>-8.702771369926765</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.4448231382381858</v>
+        <v>-0.3256073044441616</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.638495838078351</v>
+        <v>-2.340456253593294</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.572760164993281</v>
+        <v>1.751583915684316</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255786</v>
+        <v>3.801633547255787</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.821102424267952</v>
+        <v>-8.523062839782892</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.3758319364935958</v>
+        <v>-0.2566161026995717</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.581324333915655</v>
+        <v>-2.283284749430598</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.60417085717794</v>
+        <v>1.782994607868974</v>
       </c>
     </row>
     <row r="1905">
@@ -45363,19 +45363,19 @@
         <v>3.763178672860428</v>
       </c>
       <c r="C1905" t="n">
-        <v>3.14833294427436</v>
+        <v>3.084805682093905</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.688826950637065</v>
+        <v>-8.390787366152004</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.3275542602942139</v>
+        <v>-0.2718656886806445</v>
       </c>
       <c r="F1905" t="n">
-        <v>-2.449048860284769</v>
+        <v>-2.151009275799712</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.678903628103499</v>
+        <v>1.794200116614078</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575954</v>
+        <v>3.784715218575953</v>
       </c>
       <c r="C1906" t="n">
-        <v>3.151148004961996</v>
+        <v>3.087620742781541</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.498227275963911</v>
+        <v>-8.200187691478851</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.2484993297373155</v>
+        <v>-0.1928107581237462</v>
       </c>
       <c r="F1906" t="n">
-        <v>-2.258449185611616</v>
+        <v>-1.960409601126559</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.796078493595027</v>
+        <v>1.911374982105607</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430989</v>
+        <v>3.753878996430988</v>
       </c>
       <c r="C1907" t="n">
-        <v>3.164054346185655</v>
+        <v>3.1005270840052</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.24922747728033</v>
+        <v>-7.95118789279527</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.1359930690402247</v>
+        <v>-0.08030449742665491</v>
       </c>
       <c r="F1907" t="n">
-        <v>-2.258449185611616</v>
+        <v>-1.960409601126559</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.808984834818686</v>
+        <v>1.924281323329265</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077646</v>
+        <v>3.692928280077645</v>
       </c>
       <c r="C1908" t="n">
-        <v>3.036078416586436</v>
+        <v>2.972551154405981</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.354817467053435</v>
+        <v>-8.056777882568374</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.3062049945486849</v>
+        <v>-0.2505164229351156</v>
       </c>
       <c r="F1908" t="n">
-        <v>-2.364039175384721</v>
+        <v>-2.065999590899663</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.617654911355604</v>
+        <v>1.732951399866184</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457904</v>
+        <v>3.770419008457902</v>
       </c>
       <c r="C1909" t="n">
-        <v>3.084622758463523</v>
+        <v>3.021095496283068</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.373552369172032</v>
+        <v>-8.075512784686971</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.2651546135190372</v>
+        <v>-0.2094660419054679</v>
       </c>
       <c r="F1909" t="n">
-        <v>-2.364039175384721</v>
+        <v>-2.065999590899663</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.666199253232691</v>
+        <v>1.78149574174327</v>
       </c>
     </row>
     <row r="1910">
@@ -45478,19 +45478,19 @@
         <v>3.76033011118081</v>
       </c>
       <c r="C1910" t="n">
-        <v>3.088001770449517</v>
+        <v>3.024474508269063</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.096814194501219</v>
+        <v>-7.798774610016158</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.1510803316647178</v>
+        <v>-0.09539176005114802</v>
       </c>
       <c r="F1910" t="n">
-        <v>-2.182222514274795</v>
+        <v>-1.884182929789737</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.778668261884641</v>
+        <v>1.89396475039522</v>
       </c>
     </row>
     <row r="1911">
@@ -45501,19 +45501,19 @@
         <v>3.723562653879203</v>
       </c>
       <c r="C1911" t="n">
-        <v>3.079287784196039</v>
+        <v>3.015760522015584</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.969921788066149</v>
+        <v>-7.671882203581088</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.1090373553441677</v>
+        <v>-0.05334878373059837</v>
       </c>
       <c r="F1911" t="n">
-        <v>-2.055330107839725</v>
+        <v>-1.757290523354667</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.846089719492205</v>
+        <v>1.961386208002784</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568107</v>
+        <v>3.729966140568106</v>
       </c>
       <c r="C1912" t="n">
-        <v>3.072327172100946</v>
+        <v>3.008799909920491</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.926373381295458</v>
+        <v>-7.628333796810398</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.09857860473098468</v>
+        <v>-0.04289003311741535</v>
       </c>
       <c r="F1912" t="n">
-        <v>-2.055330107839725</v>
+        <v>-1.757290523354667</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.839129107397111</v>
+        <v>1.954425595907691</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963418</v>
+        <v>3.782918957963417</v>
       </c>
       <c r="C1913" t="n">
-        <v>3.086789526482089</v>
+        <v>3.023262264301634</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.6842249878416</v>
+        <v>-7.38618540335654</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.01274310703170167</v>
+        <v>0.068431678645271</v>
       </c>
       <c r="F1913" t="n">
-        <v>-2.055330107839725</v>
+        <v>-1.757290523354667</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.853591461778255</v>
+        <v>1.968887950288834</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192817</v>
+        <v>3.828547911192815</v>
       </c>
       <c r="C1914" t="n">
-        <v>3.081321646941284</v>
+        <v>3.017794384760829</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.620995616073252</v>
+        <v>-7.322956031588191</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.03256697619823612</v>
+        <v>0.08825554781180545</v>
       </c>
       <c r="F1914" t="n">
-        <v>-2.055330107839725</v>
+        <v>-1.757290523354667</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.84812358223745</v>
+        <v>1.963420070748029</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262047</v>
+        <v>3.828049353262045</v>
       </c>
       <c r="C1915" t="n">
-        <v>3.078819740951861</v>
+        <v>3.015292478771406</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.434507923696246</v>
+        <v>-7.136468339211185</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.1046601471596151</v>
+        <v>0.1603487187731849</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.868842415462719</v>
+        <v>-1.570802830977661</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.95751429167423</v>
+        <v>2.07281078018481</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389909</v>
+        <v>3.812450103389908</v>
       </c>
       <c r="C1916" t="n">
-        <v>3.086520719189187</v>
+        <v>3.022993457008732</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.413358724792802</v>
+        <v>-7.115319140307742</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.1208208049583184</v>
+        <v>0.1765093765718877</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.847693216559275</v>
+        <v>-1.549653632074218</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.977904789253622</v>
+        <v>2.093201277764202</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788095</v>
+        <v>3.748324832788093</v>
       </c>
       <c r="C1917" t="n">
-        <v>3.082301427536237</v>
+        <v>3.018774165355782</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.169593282809358</v>
+        <v>-6.871553698324298</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.2141076900987469</v>
+        <v>0.2697962617123162</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.847693216559275</v>
+        <v>-1.549653632074218</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.973685497600672</v>
+        <v>2.088981986111252</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527526</v>
+        <v>3.824307657527525</v>
       </c>
       <c r="C1918" t="n">
-        <v>3.084425741456253</v>
+        <v>3.020898479275798</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.905565215616098</v>
+        <v>-6.607525631131038</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.3218432308960666</v>
+        <v>0.3775318025096359</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.645827817743322</v>
+        <v>-1.347788233258264</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.096929050810261</v>
+        <v>2.21222553932084</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749185</v>
+        <v>3.826351398749184</v>
       </c>
       <c r="C1919" t="n">
-        <v>3.077167816439955</v>
+        <v>3.013640554259501</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.655714821667024</v>
+        <v>-6.357675237181963</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.4145254634593987</v>
+        <v>0.470214035072968</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.645827817743322</v>
+        <v>-1.347788233258264</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.089671125793963</v>
+        <v>2.204967614304542</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481498</v>
+        <v>3.835954411481497</v>
       </c>
       <c r="C1920" t="n">
-        <v>3.080766939960604</v>
+        <v>3.017239677780149</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.352147332663045</v>
+        <v>-6.054107748177985</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.5395515825816388</v>
+        <v>0.5952401541952081</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.645827817743322</v>
+        <v>-1.347788233258264</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.093270249314612</v>
+        <v>2.208566737825191</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862987</v>
+        <v>3.780930335862986</v>
       </c>
       <c r="C1921" t="n">
-        <v>3.094094446015158</v>
+        <v>3.030567183834703</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.278667423811031</v>
+        <v>-5.980627839325971</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.5822710521769978</v>
+        <v>0.6379596237905676</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.572347908891307</v>
+        <v>-1.27430832440625</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.150685700680374</v>
+        <v>2.265982189190953</v>
       </c>
     </row>
     <row r="1922">
@@ -45754,19 +45754,19 @@
         <v>3.773761647102782</v>
       </c>
       <c r="C1922" t="n">
-        <v>3.093114923631455</v>
+        <v>3.029587661451</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.053634424142208</v>
+        <v>-5.755594839657148</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.6713047296608243</v>
+        <v>0.7269933012743937</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.347314909222484</v>
+        <v>-1.049275324737427</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.284725978097964</v>
+        <v>2.400022466608544</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353077</v>
+        <v>3.764614304353074</v>
       </c>
       <c r="C1923" t="n">
-        <v>3.097809724685772</v>
+        <v>3.034282462505317</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.839000046505801</v>
+        <v>-5.540960462020741</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.7618532817697043</v>
+        <v>0.8175418533832737</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.132680531586078</v>
+        <v>-0.8346409471010201</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.418201405734126</v>
+        <v>2.533497894244706</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544785</v>
+        <v>3.798811195544783</v>
       </c>
       <c r="C1924" t="n">
-        <v>3.079003983469568</v>
+        <v>3.015476721289113</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.57239968953145</v>
+        <v>-5.274360105046389</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.8496876833432405</v>
+        <v>0.9053762549568098</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.132680531586078</v>
+        <v>-0.8346409471010201</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.399395664517922</v>
+        <v>2.514692153028501</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712296</v>
+        <v>3.797691308712294</v>
       </c>
       <c r="C1925" t="n">
-        <v>3.080747060094445</v>
+        <v>3.01721979791399</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.331969192726589</v>
+        <v>-5.033929608241529</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.9476029586900623</v>
+        <v>1.003291530303632</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.8922500347812172</v>
+        <v>-0.5942104502961598</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.545397039225715</v>
+        <v>2.660693527736295</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837688</v>
+        <v>3.821589933837685</v>
       </c>
       <c r="C1926" t="n">
-        <v>3.084676373929265</v>
+        <v>3.021149111748811</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.089178385077144</v>
+        <v>-4.791138800592083</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.04864859558466</v>
+        <v>1.10433716719823</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.8922500347812172</v>
+        <v>-0.5942104502961598</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.549326353060535</v>
+        <v>2.664622841571115</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349969</v>
+        <v>3.822323422349966</v>
       </c>
       <c r="C1927" t="n">
-        <v>3.085354957846605</v>
+        <v>3.021827695666151</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.849573293470055</v>
+        <v>-4.551533708984994</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.145169216144836</v>
+        <v>1.200857787758405</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.8252020871127227</v>
+        <v>-0.5271625026276653</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.590233705578972</v>
+        <v>2.705530194089552</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972343</v>
+        <v>3.84861305097234</v>
       </c>
       <c r="C1928" t="n">
-        <v>3.082353029066599</v>
+        <v>3.018825766886144</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.606917705046891</v>
+        <v>-4.308878120561831</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.239229522734095</v>
+        <v>1.294918094347664</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.8252020871127227</v>
+        <v>-0.5271625026276653</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.587231776798966</v>
+        <v>2.702528265309545</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145943</v>
+        <v>3.818665376145939</v>
       </c>
       <c r="C1929" t="n">
-        <v>3.083932066077213</v>
+        <v>3.020404803896758</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.386896907009881</v>
+        <v>-4.08885732252482</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.328816878959513</v>
+        <v>1.384505450573083</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.6839822420447425</v>
+        <v>-0.385942657559685</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.673542720850368</v>
+        <v>2.788839209360948</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009955</v>
+        <v>3.843270952009951</v>
       </c>
       <c r="C1930" t="n">
-        <v>3.099826248879036</v>
+        <v>3.036298986698581</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.187648277105072</v>
+        <v>-3.889608692620011</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.42441051372326</v>
+        <v>1.48009908533683</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.6839822420447425</v>
+        <v>-0.385942657559685</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.689436903652191</v>
+        <v>2.804733392162771</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966259</v>
+        <v>3.845043810966258</v>
       </c>
       <c r="C1931" t="n">
-        <v>3.100972093319338</v>
+        <v>3.037444831138883</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.028133173585702</v>
+        <v>-3.730093589100641</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.48936239957131</v>
+        <v>1.545050971184879</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.5244671385253725</v>
+        <v>-0.2264275540403151</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.786291810204115</v>
+        <v>2.901588298714695</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,45 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.467005179725582</v>
+        <v>3.791269976046995</v>
       </c>
       <c r="C1932" t="n">
-        <v>3.111060195880778</v>
+        <v>3.047532933700323</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.883461028485964</v>
+        <v>-3.585421444000904</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.557319360172645</v>
+        <v>1.613007931786214</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.3797949934256351</v>
+        <v>-0.0817554089405777</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.883183199825397</v>
+        <v>2.998479688335977</v>
+      </c>
+    </row>
+    <row r="1933">
+      <c r="A1933" s="2" t="n">
+        <v>45395</v>
+      </c>
+      <c r="B1933" t="n">
+        <v>3.790003607620887</v>
+      </c>
+      <c r="C1933" t="n">
+        <v>3.141638863081794</v>
+      </c>
+      <c r="D1933" t="n">
+        <v>-3.585421444000904</v>
+      </c>
+      <c r="E1933" t="n">
+        <v>1.613007931786214</v>
+      </c>
+      <c r="F1933" t="n">
+        <v>-0.0817554089405777</v>
+      </c>
+      <c r="G1933" t="n">
+        <v>3.134702660068162</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240413.xlsx
+++ b/tame_output/ON/bt/strategyON_20240413.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>63.9%</t>
+          <t>51.3%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>67.8%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>68.6%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.5%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-17.5%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.6%</t>
+          <t>-12.9%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>50.9%</t>
+          <t>16.5%</t>
         </is>
       </c>
     </row>
@@ -758,22 +758,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>73.4%</t>
+          <t>65.9%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>29.2%</t>
+          <t>29.9%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>59.0%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -791,17 +791,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>31.1%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>28.1%</t>
+          <t>27.6%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>20.1%</t>
+          <t>25.5%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -811,35 +811,35 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-03-19</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-14.9%</t>
+          <t>-15.8%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-3.5%</t>
+          <t>-6.0%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>-2.3%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>7.0%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-4.0%</t>
+          <t>-4.4%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>58.7%</t>
+          <t>51.5%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>23.4%</t>
+          <t>23.6%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-5.2%</t>
+          <t>-4.4%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>-19.4%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.5%</t>
+          <t>-80.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>118.1%</t>
+          <t>119.1%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>137.2%</t>
+          <t>139.0%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>97.7%</t>
+          <t>97.6%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-722.5%</t>
+          <t>-741.9%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-56.3%</t>
+          <t>-58.4%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.1%</t>
+          <t>-76.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>98.0%</t>
+          <t>98.8%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>493.0%</t>
+          <t>605.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-520.1%</t>
+          <t>-574.8%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>15.7%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.2%</t>
+          <t>55.5%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.7%</t>
+          <t>99.8%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-283.6%</t>
+          <t>-291.4%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-44.0%</t>
+          <t>-45.7%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-13.5%</t>
+          <t>-25.3%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>90.0%</t>
+          <t>-24.2%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-214.9%</t>
+          <t>-230.4%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-26.8%</t>
+          <t>-31.2%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>70.7%</t>
+          <t>71.6%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>71.0%</t>
+          <t>72.4%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>69.9%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-296.3%</t>
+          <t>-304.6%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-37.2%</t>
+          <t>-38.9%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-19.3%</t>
+          <t>-25.1%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>58.7%</t>
+          <t>59.5%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>36.7%</t>
+          <t>31.3%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-148.0%</t>
+          <t>-151.2%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-232.2%</t>
+          <t>-260.0%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>56.8%</t>
+          <t>50.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>51.5%</t>
+          <t>51.6%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>62.7%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>42.2%</t>
+          <t>41.6%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>97.7%</t>
+          <t>98.1%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-178.1%</t>
+          <t>-183.1%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.6%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-32.1%</t>
+          <t>-33.6%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>51.5%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.0%</t>
+          <t>43.1%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.4%</t>
+          <t>-16.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.1%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-132.6%</t>
+          <t>-154.5%</t>
         </is>
       </c>
     </row>
@@ -43727,22 +43727,22 @@
         <v>45296</v>
       </c>
       <c r="B1834" t="n">
-        <v>3.317575502045692</v>
+        <v>3.317575502045693</v>
       </c>
       <c r="C1834" t="n">
         <v>3.13991794227561</v>
       </c>
       <c r="D1834" t="n">
-        <v>0.9621230735079426</v>
+        <v>0.858629459151194</v>
       </c>
       <c r="E1834" t="n">
-        <v>3.52441074736504</v>
+        <v>3.483013301622341</v>
       </c>
       <c r="F1834" t="n">
-        <v>1.983826356062417</v>
+        <v>1.880332741705669</v>
       </c>
       <c r="G1834" t="n">
-        <v>4.330213755913061</v>
+        <v>4.268117587299011</v>
       </c>
     </row>
     <row r="1835">
@@ -43750,22 +43750,22 @@
         <v>45297</v>
       </c>
       <c r="B1835" t="n">
-        <v>3.320996253831153</v>
+        <v>3.320996253831154</v>
       </c>
       <c r="C1835" t="n">
         <v>3.138175778137954</v>
       </c>
       <c r="D1835" t="n">
-        <v>0.9615712736661304</v>
+        <v>0.6096876458968121</v>
       </c>
       <c r="E1835" t="n">
-        <v>3.52244786329066</v>
+        <v>3.381694412182932</v>
       </c>
       <c r="F1835" t="n">
-        <v>1.984668119547724</v>
+        <v>1.901385464850205</v>
       </c>
       <c r="G1835" t="n">
-        <v>4.328976649866589</v>
+        <v>4.279007057048078</v>
       </c>
     </row>
     <row r="1836">
@@ -43779,16 +43779,16 @@
         <v>3.118001050765402</v>
       </c>
       <c r="D1836" t="n">
-        <v>0.8558843857238307</v>
+        <v>0.5040007579545125</v>
       </c>
       <c r="E1836" t="n">
-        <v>3.459998380741187</v>
+        <v>3.319244929633459</v>
       </c>
       <c r="F1836" t="n">
-        <v>1.97010704584504</v>
+        <v>1.886824391147522</v>
       </c>
       <c r="G1836" t="n">
-        <v>4.300065278272426</v>
+        <v>4.250095685453915</v>
       </c>
     </row>
     <row r="1837">
@@ -43796,22 +43796,22 @@
         <v>45299</v>
       </c>
       <c r="B1837" t="n">
-        <v>3.385382209279814</v>
+        <v>3.385382209279815</v>
       </c>
       <c r="C1837" t="n">
         <v>3.118490189491276</v>
       </c>
       <c r="D1837" t="n">
-        <v>0.8617337668390751</v>
+        <v>0.5098501390697568</v>
       </c>
       <c r="E1837" t="n">
-        <v>3.462827271913159</v>
+        <v>3.322073820805431</v>
       </c>
       <c r="F1837" t="n">
-        <v>1.97010704584504</v>
+        <v>1.886824391147522</v>
       </c>
       <c r="G1837" t="n">
-        <v>4.300554416998301</v>
+        <v>4.250584824179789</v>
       </c>
     </row>
     <row r="1838">
@@ -43819,22 +43819,22 @@
         <v>45300</v>
       </c>
       <c r="B1838" t="n">
-        <v>3.367379938511405</v>
+        <v>3.367379938511406</v>
       </c>
       <c r="C1838" t="n">
         <v>3.122570172112943</v>
       </c>
       <c r="D1838" t="n">
-        <v>0.8135114999919916</v>
+        <v>0.4616278722226733</v>
       </c>
       <c r="E1838" t="n">
-        <v>3.447618347795992</v>
+        <v>3.306864896688265</v>
       </c>
       <c r="F1838" t="n">
-        <v>1.921884778997957</v>
+        <v>1.838602124300438</v>
       </c>
       <c r="G1838" t="n">
-        <v>4.275701039511717</v>
+        <v>4.225731446693206</v>
       </c>
     </row>
     <row r="1839">
@@ -43842,22 +43842,22 @@
         <v>45301</v>
       </c>
       <c r="B1839" t="n">
-        <v>3.376932391386094</v>
+        <v>3.376932391386096</v>
       </c>
       <c r="C1839" t="n">
         <v>3.157511256610484</v>
       </c>
       <c r="D1839" t="n">
-        <v>0.5763800081421965</v>
+        <v>0.2244963803728782</v>
       </c>
       <c r="E1839" t="n">
-        <v>3.387706835553616</v>
+        <v>3.246953384445888</v>
       </c>
       <c r="F1839" t="n">
-        <v>1.921884778997957</v>
+        <v>1.838602124300438</v>
       </c>
       <c r="G1839" t="n">
-        <v>4.310642124009259</v>
+        <v>4.260672531190748</v>
       </c>
     </row>
     <row r="1840">
@@ -43865,22 +43865,22 @@
         <v>45302</v>
       </c>
       <c r="B1840" t="n">
-        <v>3.367370539998561</v>
+        <v>3.367370539998563</v>
       </c>
       <c r="C1840" t="n">
         <v>3.156088696795822</v>
       </c>
       <c r="D1840" t="n">
-        <v>0.5814175988697829</v>
+        <v>0.2295339711004648</v>
       </c>
       <c r="E1840" t="n">
-        <v>3.388299312029988</v>
+        <v>3.247545860922261</v>
       </c>
       <c r="F1840" t="n">
-        <v>1.977529235264274</v>
+        <v>1.894246580566755</v>
       </c>
       <c r="G1840" t="n">
-        <v>4.342606237954387</v>
+        <v>4.292636645135876</v>
       </c>
     </row>
     <row r="1841">
@@ -43888,22 +43888,22 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082126</v>
+        <v>3.299560092082128</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
       </c>
       <c r="D1841" t="n">
-        <v>0.5249479676934862</v>
+        <v>0.173064339924168</v>
       </c>
       <c r="E1841" t="n">
-        <v>3.344457841183207</v>
+        <v>3.20370439007548</v>
       </c>
       <c r="F1841" t="n">
-        <v>1.921059604087977</v>
+        <v>1.837776949390459</v>
       </c>
       <c r="G1841" t="n">
-        <v>4.287470840872346</v>
+        <v>4.237501248053835</v>
       </c>
     </row>
     <row r="1842">
@@ -43911,22 +43911,22 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.293490533757925</v>
+        <v>3.293490533757926</v>
       </c>
       <c r="C1842" t="n">
         <v>3.13585268755003</v>
       </c>
       <c r="D1842" t="n">
-        <v>0.4591805776440741</v>
+        <v>0.1072969498747559</v>
       </c>
       <c r="E1842" t="n">
-        <v>3.319168494293912</v>
+        <v>3.178415043186185</v>
       </c>
       <c r="F1842" t="n">
-        <v>1.921059604087977</v>
+        <v>1.837776949390459</v>
       </c>
       <c r="G1842" t="n">
-        <v>4.288488450002816</v>
+        <v>4.238518857184305</v>
       </c>
     </row>
     <row r="1843">
@@ -43934,22 +43934,22 @@
         <v>45305</v>
       </c>
       <c r="B1843" t="n">
-        <v>3.293766719760743</v>
+        <v>3.293766719760744</v>
       </c>
       <c r="C1843" t="n">
         <v>3.126480719537785</v>
       </c>
       <c r="D1843" t="n">
-        <v>0.4456450938673645</v>
+        <v>0.09376146609804631</v>
       </c>
       <c r="E1843" t="n">
-        <v>3.304382332770984</v>
+        <v>3.163628881663257</v>
       </c>
       <c r="F1843" t="n">
-        <v>1.921059604087977</v>
+        <v>1.837776949390459</v>
       </c>
       <c r="G1843" t="n">
-        <v>4.279116481990572</v>
+        <v>4.22914688917206</v>
       </c>
     </row>
     <row r="1844">
@@ -43957,22 +43957,22 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.298730590706673</v>
+        <v>3.298730590706674</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
       </c>
       <c r="D1844" t="n">
-        <v>0.3638731934396128</v>
+        <v>0.01198956567029463</v>
       </c>
       <c r="E1844" t="n">
-        <v>3.261756298555122</v>
+        <v>3.121002847447394</v>
       </c>
       <c r="F1844" t="n">
-        <v>1.948095177494114</v>
+        <v>1.864812522796595</v>
       </c>
       <c r="G1844" t="n">
-        <v>4.285420551989492</v>
+        <v>4.235450959170981</v>
       </c>
     </row>
     <row r="1845">
@@ -43980,22 +43980,22 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.29991811929684</v>
+        <v>3.299918119296841</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>0.2966640855677352</v>
+        <v>-0.05521954220158304</v>
       </c>
       <c r="E1845" t="n">
-        <v>3.239637972240073</v>
+        <v>3.098884521132345</v>
       </c>
       <c r="F1845" t="n">
-        <v>1.948095177494114</v>
+        <v>1.864812522796595</v>
       </c>
       <c r="G1845" t="n">
-        <v>4.290185868823194</v>
+        <v>4.240216276004683</v>
       </c>
     </row>
     <row r="1846">
@@ -44003,22 +44003,22 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.29550733020149</v>
+        <v>3.295507330201492</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>0.3006555383629254</v>
+        <v>-0.05122808940639284</v>
       </c>
       <c r="E1846" t="n">
-        <v>3.239059349477389</v>
+        <v>3.098305898369662</v>
       </c>
       <c r="F1846" t="n">
-        <v>1.952086630289304</v>
+        <v>1.868803975591785</v>
       </c>
       <c r="G1846" t="n">
-        <v>4.290405536619549</v>
+        <v>4.240435943801038</v>
       </c>
     </row>
     <row r="1847">
@@ -44026,22 +44026,22 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153009</v>
+        <v>3.258791981153011</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-0.1170984851839116</v>
+        <v>-0.4689821129532298</v>
       </c>
       <c r="E1847" t="n">
-        <v>3.069884631563717</v>
+        <v>2.92913118045599</v>
       </c>
       <c r="F1847" t="n">
-        <v>1.534332606742467</v>
+        <v>1.451049952044948</v>
       </c>
       <c r="G1847" t="n">
-        <v>4.03768001399651</v>
+        <v>3.987710421177999</v>
       </c>
     </row>
     <row r="1848">
@@ -44049,22 +44049,22 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537428</v>
+        <v>3.27116857953743</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-0.3387204187420291</v>
+        <v>-0.6906040465113473</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.981102074739392</v>
+        <v>2.840348623631665</v>
       </c>
       <c r="F1848" t="n">
-        <v>1.496806473055098</v>
+        <v>1.413523818357579</v>
       </c>
       <c r="G1848" t="n">
-        <v>4.01503055038301</v>
+        <v>3.965060957564499</v>
       </c>
     </row>
     <row r="1849">
@@ -44072,22 +44072,22 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382194</v>
+        <v>3.272760131382195</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-0.5467244770951063</v>
+        <v>-0.8986081048644246</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.902792595952087</v>
+        <v>2.762039144844359</v>
       </c>
       <c r="F1849" t="n">
-        <v>1.496806473055098</v>
+        <v>1.413523818357579</v>
       </c>
       <c r="G1849" t="n">
-        <v>4.019922694936936</v>
+        <v>3.969953102118424</v>
       </c>
     </row>
     <row r="1850">
@@ -44095,22 +44095,22 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074625</v>
+        <v>3.251475576074626</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-0.8171244398039916</v>
+        <v>-1.16900806757331</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.78971406720652</v>
+        <v>2.648960616098793</v>
       </c>
       <c r="F1850" t="n">
-        <v>1.226406510346213</v>
+        <v>1.143123855648694</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.852764173649592</v>
+        <v>3.802794580831081</v>
       </c>
     </row>
     <row r="1851">
@@ -44118,22 +44118,22 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911641</v>
+        <v>3.233800325911643</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-1.156282817392514</v>
+        <v>-1.508166445161832</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.647135015477561</v>
+        <v>2.506381564369834</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.8872481327576904</v>
+        <v>0.8039654780601719</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.642353446402928</v>
+        <v>3.592383853584417</v>
       </c>
     </row>
     <row r="1852">
@@ -44141,22 +44141,22 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213498</v>
+        <v>3.2235393782135</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-1.484300039119993</v>
+        <v>-1.836183666889311</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.536266416525337</v>
+        <v>2.39551296541761</v>
       </c>
       <c r="F1852" t="n">
-        <v>0.5592309110302113</v>
+        <v>0.4759482563326928</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.465881403105209</v>
+        <v>3.415911810286698</v>
       </c>
     </row>
     <row r="1853">
@@ -44164,22 +44164,22 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416047</v>
+        <v>3.23116753741605</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-1.977624910655171</v>
+        <v>-2.32950853842449</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.347035218319835</v>
+        <v>2.206281767212107</v>
       </c>
       <c r="F1853" t="n">
-        <v>0.4542447967905925</v>
+        <v>0.370962142093074</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.410988484970006</v>
+        <v>3.361018892151495</v>
       </c>
     </row>
     <row r="1854">
@@ -44187,22 +44187,22 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.23598197738233</v>
+        <v>3.235981977382333</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-2.470009938679268</v>
+        <v>-2.821893566448586</v>
       </c>
       <c r="E1854" t="n">
-        <v>2.151187599153928</v>
+        <v>2.010434148046201</v>
       </c>
       <c r="F1854" t="n">
-        <v>-0.03814023123350418</v>
+        <v>-0.1214228859310227</v>
       </c>
       <c r="G1854" t="n">
-        <v>3.11666386019928</v>
+        <v>3.066694267380769</v>
       </c>
     </row>
     <row r="1855">
@@ -44210,22 +44210,22 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495501</v>
+        <v>3.278199702495503</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-2.85519032960934</v>
+        <v>-3.207073957378659</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.995657981594762</v>
+        <v>1.854904530487035</v>
       </c>
       <c r="F1855" t="n">
-        <v>-0.03814023123350418</v>
+        <v>-0.1214228859310227</v>
       </c>
       <c r="G1855" t="n">
-        <v>3.115206399012143</v>
+        <v>3.065236806193632</v>
       </c>
     </row>
     <row r="1856">
@@ -44233,22 +44233,22 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347057</v>
+        <v>3.29913614634706</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-3.198873102836003</v>
+        <v>-3.550756730605322</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.859953995758714</v>
+        <v>1.719200544650986</v>
       </c>
       <c r="F1856" t="n">
-        <v>-0.1460462832607224</v>
+        <v>-0.2293289379582409</v>
       </c>
       <c r="G1856" t="n">
-        <v>3.052231891250429</v>
+        <v>3.002262298431918</v>
       </c>
     </row>
     <row r="1857">
@@ -44256,22 +44256,22 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130019</v>
+        <v>3.287377576130022</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-3.556523453074351</v>
+        <v>-3.90840708084367</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.712999914319632</v>
+        <v>1.572246463211905</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.5036966334990705</v>
+        <v>-0.586979288196589</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.833747739763678</v>
+        <v>2.783778146945167</v>
       </c>
     </row>
     <row r="1858">
@@ -44279,22 +44279,22 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178246</v>
+        <v>3.315884374178249</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-3.865757556070401</v>
+        <v>-4.217641183839721</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.591079199821472</v>
+        <v>1.450325748713744</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.5036966334990705</v>
+        <v>-0.586979288196589</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.835520666463937</v>
+        <v>2.785551073645427</v>
       </c>
     </row>
     <row r="1859">
@@ -44302,22 +44302,22 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207815</v>
+        <v>3.305316798207819</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.297563349220189</v>
+        <v>-4.649446976989508</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.404689770028961</v>
+        <v>1.263936318921233</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.6401141299403375</v>
+        <v>-0.7233967846378559</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.740003056066582</v>
+        <v>2.690033463248071</v>
       </c>
     </row>
     <row r="1860">
@@ -44325,22 +44325,22 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310984</v>
+        <v>3.284619513310988</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-4.623995878087933</v>
+        <v>-4.975879505857252</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.262401533483954</v>
+        <v>1.121648082376226</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.7225823804474856</v>
+        <v>-0.8058650351450041</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.678806880764383</v>
+        <v>2.628837287945872</v>
       </c>
     </row>
     <row r="1861">
@@ -44348,22 +44348,22 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006535</v>
+        <v>3.305849539006538</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-4.959658525318385</v>
+        <v>-5.311542153087704</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.126717066247738</v>
+        <v>0.9859636151400104</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.7225823804474856</v>
+        <v>-0.8058650351450041</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.677387472420349</v>
+        <v>2.627417879601837</v>
       </c>
     </row>
     <row r="1862">
@@ -44371,22 +44371,22 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309426</v>
+        <v>3.311086391309429</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.323284770218699</v>
+        <v>-5.675168397988018</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.9877541285218543</v>
+        <v>0.847000677414127</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.8208040173146114</v>
+        <v>-0.9040866720121299</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.624942050534315</v>
+        <v>2.574972457715804</v>
       </c>
     </row>
     <row r="1863">
@@ -44394,22 +44394,22 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970907</v>
+        <v>3.30471571697091</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-5.688412152857445</v>
+        <v>-6.040295780626765</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.8409576904721874</v>
+        <v>0.7002042393644596</v>
       </c>
       <c r="F1863" t="n">
-        <v>-1.117114801613624</v>
+        <v>-1.200397456311142</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.446410094960739</v>
+        <v>2.396440502142227</v>
       </c>
     </row>
     <row r="1864">
@@ -44417,22 +44417,22 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330525</v>
+        <v>3.300815818330527</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.097000930038124</v>
+        <v>-6.448884557807443</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.6762837236146746</v>
+        <v>0.5355302725069473</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.525703578794302</v>
+        <v>-1.608986233491821</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.200018372667091</v>
+        <v>2.150048779848579</v>
       </c>
     </row>
     <row r="1865">
@@ -44440,22 +44440,22 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191741</v>
+        <v>3.302618194191743</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.509983414179218</v>
+        <v>-6.861867041948536</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.5062761624296979</v>
+        <v>0.3655227113219706</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.525703578794302</v>
+        <v>-1.608986233491821</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.195203805138551</v>
+        <v>2.14523421232004</v>
       </c>
     </row>
     <row r="1866">
@@ -44463,22 +44463,22 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108643</v>
+        <v>3.305023265108645</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-6.926375288466216</v>
+        <v>-7.278258916235534</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.3377134633237762</v>
+        <v>0.1969600122160489</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.525703578794302</v>
+        <v>-1.608986233491821</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.193197855747429</v>
+        <v>2.143228262928917</v>
       </c>
     </row>
     <row r="1867">
@@ -44486,22 +44486,22 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097824</v>
+        <v>3.341378723097826</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.30305229899606</v>
+        <v>-7.654935926765378</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.1973013497805174</v>
+        <v>0.05654789867279009</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.525703578794302</v>
+        <v>-1.608986233491821</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.203456546416108</v>
+        <v>2.153486953597596</v>
       </c>
     </row>
     <row r="1868">
@@ -44509,22 +44509,22 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094121</v>
+        <v>3.374439043094123</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-7.648927120980868</v>
+        <v>-8.000810748750187</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.0550509861322892</v>
+        <v>-0.0857024649754381</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.525703578794302</v>
+        <v>-1.608986233491821</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.199556111561803</v>
+        <v>2.149586518743292</v>
       </c>
     </row>
     <row r="1869">
@@ -44532,22 +44532,22 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.40596051119929</v>
+        <v>3.405960511199292</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-7.961751920225848</v>
+        <v>-8.313635547995165</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.07167401351070168</v>
+        <v>-0.2124274646184285</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.525703578794302</v>
+        <v>-1.608986233491821</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.197961031616804</v>
+        <v>2.147991438798293</v>
       </c>
     </row>
     <row r="1870">
@@ -44555,22 +44555,22 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969598</v>
+        <v>3.4246333549696</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.258413262036045</v>
+        <v>-8.610296889805364</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.1865595743055724</v>
+        <v>-0.3273130254132997</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.594446714528181</v>
+        <v>-1.677729369225699</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.160494126105685</v>
+        <v>2.110524533287173</v>
       </c>
     </row>
     <row r="1871">
@@ -44578,22 +44578,22 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923091</v>
+        <v>3.419979433923093</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.691762370146281</v>
+        <v>-9.043645997915599</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.3639255220840698</v>
+        <v>-0.5046789731917971</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.594446714528181</v>
+        <v>-1.677729369225699</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.156467821571281</v>
+        <v>2.106498228752771</v>
       </c>
     </row>
     <row r="1872">
@@ -44601,22 +44601,22 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297754</v>
+        <v>3.458100091297756</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.074763758888912</v>
+        <v>-9.42664738665823</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.5172281789027062</v>
+        <v>-0.6579816300104335</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.594446714528181</v>
+        <v>-1.677729369225699</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.156365720249697</v>
+        <v>2.106396127431187</v>
       </c>
     </row>
     <row r="1873">
@@ -44624,22 +44624,22 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317621</v>
+        <v>3.447750501317622</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.449749085060189</v>
+        <v>-9.801632712829507</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.6646507933997872</v>
+        <v>-0.8054042445075145</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.969432040699458</v>
+        <v>-2.052714695396977</v>
       </c>
       <c r="G1873" t="n">
-        <v>1.933946040518361</v>
+        <v>1.88397644769985</v>
       </c>
     </row>
     <row r="1874">
@@ -44647,22 +44647,22 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737175</v>
+        <v>3.503515506737177</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.80927940756419</v>
+        <v>-10.16116303533351</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.8031126191033375</v>
+        <v>-0.9438660702110644</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.969432040699458</v>
+        <v>-2.052714695396977</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.939296343816411</v>
+        <v>1.8893267509979</v>
       </c>
     </row>
     <row r="1875">
@@ -44670,22 +44670,22 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341318</v>
+        <v>3.50317028234132</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-10.1356794362292</v>
+        <v>-10.48756306399852</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.9257566106121655</v>
+        <v>-1.066510061719893</v>
       </c>
       <c r="F1875" t="n">
-        <v>-2.295832069364471</v>
+        <v>-2.37911472406199</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.751372346574581</v>
+        <v>1.70140275375607</v>
       </c>
     </row>
     <row r="1876">
@@ -44693,22 +44693,22 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776682</v>
+        <v>3.500446096776684</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.3548284043034</v>
+        <v>-10.70671203207272</v>
       </c>
       <c r="E1876" t="n">
-        <v>-1.010374447220075</v>
+        <v>-1.151127898327803</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.514981037438669</v>
+        <v>-2.598263692136187</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.622924716351831</v>
+        <v>1.57295512353332</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,22 +44716,22 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407497</v>
+        <v>3.492445136407496</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.35113747934699</v>
+        <v>-10.70302110711631</v>
       </c>
       <c r="E1877" t="n">
-        <v>-1.008898077237511</v>
+        <v>-1.149651528345239</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.514981037438669</v>
+        <v>-2.598263692136187</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.622924716351831</v>
+        <v>1.57295512353332</v>
       </c>
     </row>
     <row r="1878">
@@ -44739,22 +44739,22 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611699</v>
+        <v>3.502786823611698</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.55539565467685</v>
+        <v>-10.90727928244617</v>
       </c>
       <c r="E1878" t="n">
-        <v>-1.085088150250814</v>
+        <v>-1.225841601358542</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.642619982052658</v>
+        <v>-2.725902636750176</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.551854546702081</v>
+        <v>1.501884953883569</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199889</v>
+        <v>3.496848329199888</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.77343342630803</v>
+        <v>-11.12531705407735</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.167820704418849</v>
+        <v>-1.308574155526576</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.817390750148557</v>
+        <v>-2.900673404846075</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.451474640328977</v>
+        <v>1.401505047510466</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.69996359464058</v>
+        <v>-11.24639319253821</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.123061070258449</v>
+        <v>-1.341632909417499</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.743920918481108</v>
+        <v>-3.021749543306936</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.510928240822867</v>
+        <v>1.344231065927371</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078599</v>
+        <v>3.490055666078598</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.87508801202713</v>
+        <v>-11.42151760992475</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.178555616465549</v>
+        <v>-1.397127455624601</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.919045335867652</v>
+        <v>-3.19687396069348</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.420408811138458</v>
+        <v>1.253711636242961</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880271</v>
+        <v>3.485875018880272</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-11.10954010604162</v>
+        <v>-11.65596970393924</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.279555618972941</v>
+        <v>-1.498127458131992</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.919045335867652</v>
+        <v>-3.19687396069348</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.413189646236862</v>
+        <v>1.246492471341365</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.39734395057885</v>
+        <v>-11.94377354847648</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.401349347561812</v>
+        <v>-1.619921186720864</v>
       </c>
       <c r="F1883" t="n">
-        <v>-3.20684918040489</v>
+        <v>-3.484677805230718</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.233835148740543</v>
+        <v>1.067137973845046</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-11.62716839774268</v>
+        <v>-12.17359799564031</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.492163336588786</v>
+        <v>-1.710735175747837</v>
       </c>
       <c r="F1884" t="n">
-        <v>-3.369496717475051</v>
+        <v>-3.647325342300878</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.137362416337003</v>
+        <v>0.9706652414415062</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-11.85919731747894</v>
+        <v>-12.40562691537657</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.582281175854176</v>
+        <v>-1.800853015013228</v>
       </c>
       <c r="F1885" t="n">
-        <v>-3.431509414663474</v>
+        <v>-3.709338039489301</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.102848526653064</v>
+        <v>0.9361513517575673</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-11.80718180351013</v>
+        <v>-12.35361140140776</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.55748463458025</v>
+        <v>-1.776056473739302</v>
       </c>
       <c r="F1886" t="n">
-        <v>-3.431509414663474</v>
+        <v>-3.709338039489301</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.106838862339464</v>
+        <v>0.9401416874439681</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.94885364523425</v>
+        <v>-12.49528324313188</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.61562859816864</v>
+        <v>-1.834200437327691</v>
       </c>
       <c r="F1887" t="n">
-        <v>-3.431509414663474</v>
+        <v>-3.709338039489301</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.105363635440723</v>
+        <v>0.9386664605452264</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-12.04776038569352</v>
+        <v>-12.59418998359115</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.640137884187478</v>
+        <v>-1.858709723346529</v>
       </c>
       <c r="F1888" t="n">
-        <v>-3.53041615512275</v>
+        <v>-3.808244779948577</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.06107300133003</v>
+        <v>0.8943758264345334</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240579</v>
+        <v>3.67683797424058</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-11.84860827845642</v>
+        <v>-12.39503787635405</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.573528174939321</v>
+        <v>-1.792100014098372</v>
       </c>
       <c r="F1889" t="n">
-        <v>-3.365093629172936</v>
+        <v>-3.642922253998763</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.147215383253235</v>
+        <v>0.9805182083577382</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085281</v>
+        <v>3.685157806085282</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-11.62276312573701</v>
+        <v>-12.16919272363464</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.473611040815348</v>
+        <v>-1.692182879974399</v>
       </c>
       <c r="F1890" t="n">
-        <v>-3.323166953585773</v>
+        <v>-3.6009955784116</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.181950461641741</v>
+        <v>1.015253286746245</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282103</v>
+        <v>3.684840248282104</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.33648831341432</v>
+        <v>-11.88291791131195</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.357961971330211</v>
+        <v>-1.576533810489262</v>
       </c>
       <c r="F1891" t="n">
-        <v>-3.323166953585773</v>
+        <v>-3.6009955784116</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.1830896061978</v>
+        <v>1.016392431302304</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116218</v>
+        <v>3.710931958116219</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.3893836014586</v>
+        <v>-11.93581319935623</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.376486312385818</v>
+        <v>-1.595058151544869</v>
       </c>
       <c r="F1892" t="n">
-        <v>-3.318211607497326</v>
+        <v>-3.596040232323154</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.188696588012976</v>
+        <v>1.021999413117479</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.76894809908157</v>
+        <v>3.768948099081571</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.10547487052986</v>
+        <v>-11.65190446842748</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.257189115775682</v>
+        <v>-1.475760954934733</v>
       </c>
       <c r="F1893" t="n">
-        <v>-3.318211607497326</v>
+        <v>-3.596040232323154</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.194430292251612</v>
+        <v>1.027733117356116</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.72857435442533</v>
+        <v>3.728574354425332</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.8584876203369</v>
+        <v>-11.40491721823453</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.168131478092366</v>
+        <v>-1.386703317251418</v>
       </c>
       <c r="F1894" t="n">
-        <v>-3.071224357304374</v>
+        <v>-3.349052982130202</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.332885379973518</v>
+        <v>1.166188205078022</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702414</v>
+        <v>3.747699084702416</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.59465075313283</v>
+        <v>-11.14108035103046</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.072480212523646</v>
+        <v>-1.291052051682697</v>
       </c>
       <c r="F1895" t="n">
-        <v>-3.071224357304374</v>
+        <v>-3.349052982130202</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.32300189866061</v>
+        <v>1.156304723765115</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.76631350390623</v>
+        <v>3.766313503906231</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.32740895226444</v>
+        <v>-10.87383855016206</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.9674180526756611</v>
+        <v>-1.185989891834712</v>
       </c>
       <c r="F1896" t="n">
-        <v>-3.071224357304374</v>
+        <v>-3.349052982130202</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.321167338161237</v>
+        <v>1.154470163265741</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.78468094578195</v>
+        <v>3.784680945781952</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.05159978886395</v>
+        <v>-10.59802938676158</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.8573947022889272</v>
+        <v>-1.075966541447979</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.982205049025641</v>
+        <v>-3.260033673851468</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.374278608155016</v>
+        <v>1.20758143325952</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567246</v>
+        <v>3.800825778567248</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.02764624788799</v>
+        <v>-10.57407584578562</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.8471447797530511</v>
+        <v>-1.065716618912102</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.958251508049683</v>
+        <v>-3.23608013287551</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.389319238886084</v>
+        <v>1.222622063990588</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487775</v>
+        <v>3.789307536487778</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.763586309565197</v>
+        <v>-10.31001590746282</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.754781120585684</v>
+        <v>-0.9733529597447355</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.694191569726887</v>
+        <v>-2.972020194552714</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.53449488571801</v>
+        <v>1.367797710822513</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309728</v>
+        <v>3.83324917230973</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.056506686060359</v>
+        <v>-9.602936283957987</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.47473630484405</v>
+        <v>-0.6933081440031015</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.694191569726887</v>
+        <v>-2.972020194552714</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.531707852057709</v>
+        <v>1.365010677162213</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858731</v>
+        <v>3.839370871858733</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.016322387694169</v>
+        <v>-9.562751985591797</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.4583189616097325</v>
+        <v>-0.6768908007687839</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.654007271360697</v>
+        <v>-2.931835896186524</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.556162054965265</v>
+        <v>1.389464880069768</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096477</v>
+        <v>3.856158176096479</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.936252592156364</v>
+        <v>-9.482682190053993</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.4269242221738541</v>
+        <v>-0.645496061332905</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.573937475822893</v>
+        <v>-2.85176610064872</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.603570753508704</v>
+        <v>1.436873578613208</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.78732685376181</v>
+        <v>3.787326853761811</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.702771369926765</v>
+        <v>-9.249200967824393</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.3256073044441616</v>
+        <v>-0.5441791436032131</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.340456253593294</v>
+        <v>-2.618284878419121</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.751583915684316</v>
+        <v>1.584886740788819</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255787</v>
+        <v>3.801633547255788</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.523062839782892</v>
+        <v>-9.06949243768052</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.2566161026995717</v>
+        <v>-0.4751879418586227</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.283284749430598</v>
+        <v>-2.561113374256425</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.782994607868974</v>
+        <v>1.616297432973478</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860428</v>
+        <v>3.76317867286043</v>
       </c>
       <c r="C1905" t="n">
-        <v>3.084805682093905</v>
+        <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.390787366152004</v>
+        <v>-8.937216964049632</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.2718656886806445</v>
+        <v>-0.4269102656592407</v>
       </c>
       <c r="F1905" t="n">
-        <v>-2.151009275799712</v>
+        <v>-2.428837900625539</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.794200116614078</v>
+        <v>1.691030203899037</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575953</v>
+        <v>3.784715218575956</v>
       </c>
       <c r="C1906" t="n">
-        <v>3.087620742781541</v>
+        <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.200187691478851</v>
+        <v>-8.746617289376479</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.1928107581237462</v>
+        <v>-0.3478553351023428</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.960409601126559</v>
+        <v>-2.238238225952386</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.911374982105607</v>
+        <v>1.808205069390565</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430988</v>
+        <v>3.75387899643099</v>
       </c>
       <c r="C1907" t="n">
-        <v>3.1005270840052</v>
+        <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.95118789279527</v>
+        <v>-8.497617490692898</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.08030449742665491</v>
+        <v>-0.2353490744052515</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.960409601126559</v>
+        <v>-2.238238225952386</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.924281323329265</v>
+        <v>1.821111410614224</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077645</v>
+        <v>3.692928280077648</v>
       </c>
       <c r="C1908" t="n">
-        <v>2.972551154405981</v>
+        <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.056777882568374</v>
+        <v>-8.603207480466002</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.2505164229351156</v>
+        <v>-0.4055609999137122</v>
       </c>
       <c r="F1908" t="n">
-        <v>-2.065999590899663</v>
+        <v>-2.343828215725491</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.732951399866184</v>
+        <v>1.629781487151142</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457902</v>
+        <v>3.770419008457906</v>
       </c>
       <c r="C1909" t="n">
-        <v>3.021095496283068</v>
+        <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.075512784686971</v>
+        <v>-8.621942382584599</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.2094660419054679</v>
+        <v>-0.3645106188840646</v>
       </c>
       <c r="F1909" t="n">
-        <v>-2.065999590899663</v>
+        <v>-2.343828215725491</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.78149574174327</v>
+        <v>1.678325829028229</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.76033011118081</v>
+        <v>3.760330111180812</v>
       </c>
       <c r="C1910" t="n">
-        <v>3.024474508269063</v>
+        <v>3.088001770449517</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.798774610016158</v>
+        <v>-8.345204207913786</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.09539176005114802</v>
+        <v>-0.2504363370297447</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.884182929789737</v>
+        <v>-2.162011554615565</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.89396475039522</v>
+        <v>1.790794837680179</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879203</v>
+        <v>3.723562653879204</v>
       </c>
       <c r="C1911" t="n">
-        <v>3.015760522015584</v>
+        <v>3.079287784196039</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.671882203581088</v>
+        <v>-8.218311801478716</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.05334878373059837</v>
+        <v>-0.2083933607091946</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.757290523354667</v>
+        <v>-2.035119148180495</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.961386208002784</v>
+        <v>1.858216295287743</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568106</v>
+        <v>3.729966140568108</v>
       </c>
       <c r="C1912" t="n">
-        <v>3.008799909920491</v>
+        <v>3.072327172100946</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.628333796810398</v>
+        <v>-8.174763394708025</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.04289003311741535</v>
+        <v>-0.1979346100960115</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.757290523354667</v>
+        <v>-2.035119148180495</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.954425595907691</v>
+        <v>1.851255683192649</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963417</v>
+        <v>3.78291895796342</v>
       </c>
       <c r="C1913" t="n">
-        <v>3.023262264301634</v>
+        <v>3.086789526482089</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.38618540335654</v>
+        <v>-7.932615001254167</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.068431678645271</v>
+        <v>-0.08661289833332519</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.757290523354667</v>
+        <v>-2.035119148180495</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.968887950288834</v>
+        <v>1.865718037573793</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192815</v>
+        <v>3.828547911192818</v>
       </c>
       <c r="C1914" t="n">
-        <v>3.017794384760829</v>
+        <v>3.081321646941284</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.322956031588191</v>
+        <v>-7.869385629485818</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.08825554781180545</v>
+        <v>-0.06678902916679075</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.757290523354667</v>
+        <v>-2.035119148180495</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.963420070748029</v>
+        <v>1.860250158032988</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262045</v>
+        <v>3.828049353262049</v>
       </c>
       <c r="C1915" t="n">
-        <v>3.015292478771406</v>
+        <v>3.078819740951861</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.136468339211185</v>
+        <v>-7.682897937108812</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.1603487187731849</v>
+        <v>0.005304141794588713</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.570802830977661</v>
+        <v>-1.848631455803489</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.07281078018481</v>
+        <v>1.969640867469768</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389908</v>
+        <v>3.812450103389911</v>
       </c>
       <c r="C1916" t="n">
-        <v>3.022993457008732</v>
+        <v>3.086520719189187</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.115319140307742</v>
+        <v>-7.661748738205369</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.1765093765718877</v>
+        <v>0.02146479959329151</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.549653632074218</v>
+        <v>-1.827482256900045</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.093201277764202</v>
+        <v>1.99003136504916</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788093</v>
+        <v>3.748324832788096</v>
       </c>
       <c r="C1917" t="n">
-        <v>3.018774165355782</v>
+        <v>3.082301427536237</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.871553698324298</v>
+        <v>-7.417983296221925</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.2697962617123162</v>
+        <v>0.11475168473372</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.549653632074218</v>
+        <v>-1.827482256900045</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.088981986111252</v>
+        <v>1.98581207339621</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527525</v>
+        <v>3.824307657527528</v>
       </c>
       <c r="C1918" t="n">
-        <v>3.020898479275798</v>
+        <v>3.084425741456253</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.607525631131038</v>
+        <v>-7.153955229028664</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.3775318025096359</v>
+        <v>0.2224872255310402</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.347788233258264</v>
+        <v>-1.625616858084092</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.21222553932084</v>
+        <v>2.109055626605798</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749184</v>
+        <v>3.826351398749186</v>
       </c>
       <c r="C1919" t="n">
-        <v>3.013640554259501</v>
+        <v>3.077167816439955</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.357675237181963</v>
+        <v>-6.90410483507959</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.470214035072968</v>
+        <v>0.3151694580943722</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.347788233258264</v>
+        <v>-1.625616858084092</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.204967614304542</v>
+        <v>2.101797701589501</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481497</v>
+        <v>3.8359544114815</v>
       </c>
       <c r="C1920" t="n">
-        <v>3.017239677780149</v>
+        <v>3.080766939960604</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.054107748177985</v>
+        <v>-6.600537346075611</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.5952401541952081</v>
+        <v>0.4401955772166124</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.347788233258264</v>
+        <v>-1.625616858084092</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.208566737825191</v>
+        <v>2.105396825110149</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862986</v>
+        <v>3.780930335862989</v>
       </c>
       <c r="C1921" t="n">
-        <v>3.030567183834703</v>
+        <v>3.094094446015158</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.980627839325971</v>
+        <v>-6.527057437223597</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.6379596237905676</v>
+        <v>0.4829150468119718</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.27430832440625</v>
+        <v>-1.552136949232077</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.265982189190953</v>
+        <v>2.162812276475912</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102782</v>
+        <v>3.773761647102784</v>
       </c>
       <c r="C1922" t="n">
-        <v>3.029587661451</v>
+        <v>3.093114923631455</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.755594839657148</v>
+        <v>-6.302024437554774</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.7269933012743937</v>
+        <v>0.5719487242957979</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.049275324737427</v>
+        <v>-1.327103949563254</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.400022466608544</v>
+        <v>2.296852553893503</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353074</v>
+        <v>3.764614304353079</v>
       </c>
       <c r="C1923" t="n">
-        <v>3.034282462505317</v>
+        <v>3.097809724685772</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.540960462020741</v>
+        <v>-6.087390059918367</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.8175418533832737</v>
+        <v>0.6624972764046779</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.8346409471010201</v>
+        <v>-1.112469571926848</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.533497894244706</v>
+        <v>2.430327981529664</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544783</v>
+        <v>3.798811195544786</v>
       </c>
       <c r="C1924" t="n">
-        <v>3.015476721289113</v>
+        <v>3.079003983469568</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.274360105046389</v>
+        <v>-5.820789702944015</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.9053762549568098</v>
+        <v>0.7503316779782141</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.8346409471010201</v>
+        <v>-1.112469571926848</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.514692153028501</v>
+        <v>2.41152224031346</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712294</v>
+        <v>3.797691308712298</v>
       </c>
       <c r="C1925" t="n">
-        <v>3.01721979791399</v>
+        <v>3.080747060094445</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.033929608241529</v>
+        <v>-5.580359206139155</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.003291530303632</v>
+        <v>0.8482469533250359</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.5942104502961598</v>
+        <v>-0.8720390751219873</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.660693527736295</v>
+        <v>2.557523615021253</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837685</v>
+        <v>3.821589933837689</v>
       </c>
       <c r="C1926" t="n">
-        <v>3.021149111748811</v>
+        <v>3.084676373929265</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.791138800592083</v>
+        <v>-5.33756839848971</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.10433716719823</v>
+        <v>0.9492925902196343</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.5942104502961598</v>
+        <v>-0.8720390751219873</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.664622841571115</v>
+        <v>2.561452928856073</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349966</v>
+        <v>3.822323422349971</v>
       </c>
       <c r="C1927" t="n">
-        <v>3.021827695666151</v>
+        <v>3.085354957846605</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.551533708984994</v>
+        <v>-5.097963306882621</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.200857787758405</v>
+        <v>1.04581321077981</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.5271625026276653</v>
+        <v>-0.8049911274534928</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.705530194089552</v>
+        <v>2.60236028137451</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.84861305097234</v>
+        <v>3.848613050972345</v>
       </c>
       <c r="C1928" t="n">
-        <v>3.018825766886144</v>
+        <v>3.082353029066599</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.308878120561831</v>
+        <v>-4.855307718459457</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.294918094347664</v>
+        <v>1.139873517369069</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.5271625026276653</v>
+        <v>-0.8049911274534928</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.702528265309545</v>
+        <v>2.599358352594503</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145939</v>
+        <v>3.818665376145945</v>
       </c>
       <c r="C1929" t="n">
-        <v>3.020404803896758</v>
+        <v>3.083932066077213</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.08885732252482</v>
+        <v>-4.635286920422446</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.384505450573083</v>
+        <v>1.229460873594487</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.385942657559685</v>
+        <v>-0.6637712823855125</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.788839209360948</v>
+        <v>2.685669296645906</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009951</v>
+        <v>3.843270952009957</v>
       </c>
       <c r="C1930" t="n">
-        <v>3.036298986698581</v>
+        <v>3.099826248879036</v>
       </c>
       <c r="D1930" t="n">
-        <v>-3.889608692620011</v>
+        <v>-4.436038290517637</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.48009908533683</v>
+        <v>1.325054508358234</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.385942657559685</v>
+        <v>-0.6637712823855125</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.804733392162771</v>
+        <v>2.701563479447729</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966258</v>
+        <v>3.845043810966261</v>
       </c>
       <c r="C1931" t="n">
-        <v>3.037444831138883</v>
+        <v>3.100972093319338</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.730093589100641</v>
+        <v>-4.276523186998268</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.545050971184879</v>
+        <v>1.390006394206284</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.2264275540403151</v>
+        <v>-0.5042561788661426</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.901588298714695</v>
+        <v>2.798418385999653</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046995</v>
+        <v>3.791269976046998</v>
       </c>
       <c r="C1932" t="n">
-        <v>3.047532933700323</v>
+        <v>3.111060195880778</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.585421444000904</v>
+        <v>-4.13185104189853</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.613007931786214</v>
+        <v>1.457963354807619</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.0817554089405777</v>
+        <v>-0.3595840337664052</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.998479688335977</v>
+        <v>2.895309775620935</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.790003607620887</v>
+        <v>3.445944781420092</v>
       </c>
       <c r="C1933" t="n">
-        <v>3.141638863081794</v>
+        <v>2.922598507788898</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.585421444000904</v>
+        <v>-4.13185104189853</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.613007931786214</v>
+        <v>1.457963354807619</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.0817554089405777</v>
+        <v>-0.3595840337664052</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.134702660068162</v>
+        <v>2.915662304775266</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240413.xlsx
+++ b/tame_output/ON/bt/strategyON_20240413.xlsx
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-80.1%</t>
+          <t>-79.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>119.1%</t>
+          <t>119.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>139.0%</t>
+          <t>138.9%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>97.6%</t>
+          <t>97.7%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-741.9%</t>
+          <t>-722.5%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-58.4%</t>
+          <t>-57.6%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.7%</t>
+          <t>-75.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>605.8%</t>
+          <t>601.4%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-574.8%</t>
+          <t>-555.0%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>13.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.8%</t>
+          <t>99.7%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-291.4%</t>
+          <t>-283.6%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-45.7%</t>
+          <t>-45.0%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>11.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-25.3%</t>
+          <t>-19.1%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-24.2%</t>
+          <t>-516.7%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-230.4%</t>
+          <t>-222.5%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-31.2%</t>
+          <t>-28.5%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>71.6%</t>
+          <t>71.5%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>72.4%</t>
+          <t>72.2%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>69.9%</t>
+          <t>70.0%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-304.6%</t>
+          <t>-304.7%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-38.9%</t>
+          <t>-37.7%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-25.1%</t>
+          <t>-22.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>59.5%</t>
+          <t>59.4%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>31.3%</t>
+          <t>34.9%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-151.2%</t>
+          <t>-151.5%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-260.0%</t>
+          <t>-240.6%</t>
         </is>
       </c>
     </row>
@@ -1390,12 +1390,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>50.3%</t>
+          <t>50.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>51.6%</t>
+          <t>51.8%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>63.8%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>41.6%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>98.1%</t>
+          <t>97.8%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-183.1%</t>
+          <t>-183.2%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1466,32 +1466,32 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-33.6%</t>
+          <t>-32.5%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>44.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.1%</t>
+          <t>43.2%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.8%</t>
+          <t>-16.7%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>34.0%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -43750,22 +43750,22 @@
         <v>45297</v>
       </c>
       <c r="B1835" t="n">
-        <v>3.320996253831154</v>
+        <v>3.320996253831153</v>
       </c>
       <c r="C1835" t="n">
         <v>3.138175778137954</v>
       </c>
       <c r="D1835" t="n">
-        <v>0.6096876458968121</v>
+        <v>0.6128114976131679</v>
       </c>
       <c r="E1835" t="n">
-        <v>3.381694412182932</v>
+        <v>3.382943952869474</v>
       </c>
       <c r="F1835" t="n">
-        <v>1.901385464850205</v>
+        <v>1.899967151891663</v>
       </c>
       <c r="G1835" t="n">
-        <v>4.279007057048078</v>
+        <v>4.278156069272953</v>
       </c>
     </row>
     <row r="1836">
@@ -43779,16 +43779,16 @@
         <v>3.118001050765402</v>
       </c>
       <c r="D1836" t="n">
-        <v>0.5040007579545125</v>
+        <v>0.5071246096708681</v>
       </c>
       <c r="E1836" t="n">
-        <v>3.319244929633459</v>
+        <v>3.320494470320002</v>
       </c>
       <c r="F1836" t="n">
-        <v>1.886824391147522</v>
+        <v>1.88540607818898</v>
       </c>
       <c r="G1836" t="n">
-        <v>4.250095685453915</v>
+        <v>4.249244697678789</v>
       </c>
     </row>
     <row r="1837">
@@ -43796,22 +43796,22 @@
         <v>45299</v>
       </c>
       <c r="B1837" t="n">
-        <v>3.385382209279815</v>
+        <v>3.385382209279814</v>
       </c>
       <c r="C1837" t="n">
         <v>3.118490189491276</v>
       </c>
       <c r="D1837" t="n">
-        <v>0.5098501390697568</v>
+        <v>0.5129739907861125</v>
       </c>
       <c r="E1837" t="n">
-        <v>3.322073820805431</v>
+        <v>3.323323361491973</v>
       </c>
       <c r="F1837" t="n">
-        <v>1.886824391147522</v>
+        <v>1.88540607818898</v>
       </c>
       <c r="G1837" t="n">
-        <v>4.250584824179789</v>
+        <v>4.249733836404664</v>
       </c>
     </row>
     <row r="1838">
@@ -43819,22 +43819,22 @@
         <v>45300</v>
       </c>
       <c r="B1838" t="n">
-        <v>3.367379938511406</v>
+        <v>3.367379938511405</v>
       </c>
       <c r="C1838" t="n">
         <v>3.122570172112943</v>
       </c>
       <c r="D1838" t="n">
-        <v>0.4616278722226733</v>
+        <v>0.464751723939029</v>
       </c>
       <c r="E1838" t="n">
-        <v>3.306864896688265</v>
+        <v>3.308114437374807</v>
       </c>
       <c r="F1838" t="n">
-        <v>1.838602124300438</v>
+        <v>1.837183811341896</v>
       </c>
       <c r="G1838" t="n">
-        <v>4.225731446693206</v>
+        <v>4.224880458918081</v>
       </c>
     </row>
     <row r="1839">
@@ -43842,22 +43842,22 @@
         <v>45301</v>
       </c>
       <c r="B1839" t="n">
-        <v>3.376932391386096</v>
+        <v>3.376932391386094</v>
       </c>
       <c r="C1839" t="n">
         <v>3.157511256610484</v>
       </c>
       <c r="D1839" t="n">
-        <v>0.2244963803728782</v>
+        <v>0.2276202320892339</v>
       </c>
       <c r="E1839" t="n">
-        <v>3.246953384445888</v>
+        <v>3.248202925132431</v>
       </c>
       <c r="F1839" t="n">
-        <v>1.838602124300438</v>
+        <v>1.837183811341896</v>
       </c>
       <c r="G1839" t="n">
-        <v>4.260672531190748</v>
+        <v>4.259821543415622</v>
       </c>
     </row>
     <row r="1840">
@@ -43865,22 +43865,22 @@
         <v>45302</v>
       </c>
       <c r="B1840" t="n">
-        <v>3.367370539998563</v>
+        <v>3.367370539998561</v>
       </c>
       <c r="C1840" t="n">
         <v>3.156088696795822</v>
       </c>
       <c r="D1840" t="n">
-        <v>0.2295339711004648</v>
+        <v>0.2326578228168204</v>
       </c>
       <c r="E1840" t="n">
-        <v>3.247545860922261</v>
+        <v>3.248795401608803</v>
       </c>
       <c r="F1840" t="n">
-        <v>1.894246580566755</v>
+        <v>1.892828267608213</v>
       </c>
       <c r="G1840" t="n">
-        <v>4.292636645135876</v>
+        <v>4.291785657360751</v>
       </c>
     </row>
     <row r="1841">
@@ -43888,22 +43888,22 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082128</v>
+        <v>3.299560092082126</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
       </c>
       <c r="D1841" t="n">
-        <v>0.173064339924168</v>
+        <v>0.1761881916405236</v>
       </c>
       <c r="E1841" t="n">
-        <v>3.20370439007548</v>
+        <v>3.204953930762022</v>
       </c>
       <c r="F1841" t="n">
-        <v>1.837776949390459</v>
+        <v>1.836358636431916</v>
       </c>
       <c r="G1841" t="n">
-        <v>4.237501248053835</v>
+        <v>4.23665026027871</v>
       </c>
     </row>
     <row r="1842">
@@ -43911,22 +43911,22 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.293490533757926</v>
+        <v>3.293490533757924</v>
       </c>
       <c r="C1842" t="n">
         <v>3.13585268755003</v>
       </c>
       <c r="D1842" t="n">
-        <v>0.1072969498747559</v>
+        <v>0.1104208015911116</v>
       </c>
       <c r="E1842" t="n">
-        <v>3.178415043186185</v>
+        <v>3.179664583872727</v>
       </c>
       <c r="F1842" t="n">
-        <v>1.837776949390459</v>
+        <v>1.836358636431916</v>
       </c>
       <c r="G1842" t="n">
-        <v>4.238518857184305</v>
+        <v>4.237667869409179</v>
       </c>
     </row>
     <row r="1843">
@@ -43934,22 +43934,22 @@
         <v>45305</v>
       </c>
       <c r="B1843" t="n">
-        <v>3.293766719760744</v>
+        <v>3.293766719760742</v>
       </c>
       <c r="C1843" t="n">
         <v>3.126480719537785</v>
       </c>
       <c r="D1843" t="n">
-        <v>0.09376146609804631</v>
+        <v>0.09688531781440196</v>
       </c>
       <c r="E1843" t="n">
-        <v>3.163628881663257</v>
+        <v>3.164878422349799</v>
       </c>
       <c r="F1843" t="n">
-        <v>1.837776949390459</v>
+        <v>1.836358636431916</v>
       </c>
       <c r="G1843" t="n">
-        <v>4.22914688917206</v>
+        <v>4.228295901396935</v>
       </c>
     </row>
     <row r="1844">
@@ -43957,22 +43957,22 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.298730590706674</v>
+        <v>3.298730590706672</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
       </c>
       <c r="D1844" t="n">
-        <v>0.01198956567029463</v>
+        <v>0.01511341738665029</v>
       </c>
       <c r="E1844" t="n">
-        <v>3.121002847447394</v>
+        <v>3.122252388133937</v>
       </c>
       <c r="F1844" t="n">
-        <v>1.864812522796595</v>
+        <v>1.863394209838053</v>
       </c>
       <c r="G1844" t="n">
-        <v>4.235450959170981</v>
+        <v>4.234599971395856</v>
       </c>
     </row>
     <row r="1845">
@@ -43980,22 +43980,22 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296841</v>
+        <v>3.299918119296839</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.05521954220158304</v>
+        <v>-0.05209569048522739</v>
       </c>
       <c r="E1845" t="n">
-        <v>3.098884521132345</v>
+        <v>3.100134061818888</v>
       </c>
       <c r="F1845" t="n">
-        <v>1.864812522796595</v>
+        <v>1.863394209838053</v>
       </c>
       <c r="G1845" t="n">
-        <v>4.240216276004683</v>
+        <v>4.239365288229558</v>
       </c>
     </row>
     <row r="1846">
@@ -44003,22 +44003,22 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201492</v>
+        <v>3.295507330201489</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-0.05122808940639284</v>
+        <v>-0.04810423769003719</v>
       </c>
       <c r="E1846" t="n">
-        <v>3.098305898369662</v>
+        <v>3.099555439056204</v>
       </c>
       <c r="F1846" t="n">
-        <v>1.868803975591785</v>
+        <v>1.867385662633243</v>
       </c>
       <c r="G1846" t="n">
-        <v>4.240435943801038</v>
+        <v>4.239584956025912</v>
       </c>
     </row>
     <row r="1847">
@@ -44026,22 +44026,22 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153011</v>
+        <v>3.258791981153008</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-0.4689821129532298</v>
+        <v>-0.4658582612368742</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.92913118045599</v>
+        <v>2.930380721142532</v>
       </c>
       <c r="F1847" t="n">
-        <v>1.451049952044948</v>
+        <v>1.449631639086406</v>
       </c>
       <c r="G1847" t="n">
-        <v>3.987710421177999</v>
+        <v>3.986859433402874</v>
       </c>
     </row>
     <row r="1848">
@@ -44049,22 +44049,22 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.27116857953743</v>
+        <v>3.271168579537427</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-0.6906040465113473</v>
+        <v>-0.6874801947949917</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.840348623631665</v>
+        <v>2.841598164318207</v>
       </c>
       <c r="F1848" t="n">
-        <v>1.413523818357579</v>
+        <v>1.412105505399037</v>
       </c>
       <c r="G1848" t="n">
-        <v>3.965060957564499</v>
+        <v>3.964209969789374</v>
       </c>
     </row>
     <row r="1849">
@@ -44072,22 +44072,22 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382195</v>
+        <v>3.272760131382193</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-0.8986081048644246</v>
+        <v>-0.8954842531480689</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.762039144844359</v>
+        <v>2.763288685530902</v>
       </c>
       <c r="F1849" t="n">
-        <v>1.413523818357579</v>
+        <v>1.412105505399037</v>
       </c>
       <c r="G1849" t="n">
-        <v>3.969953102118424</v>
+        <v>3.969102114343299</v>
       </c>
     </row>
     <row r="1850">
@@ -44095,22 +44095,22 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074626</v>
+        <v>3.251475576074624</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.16900806757331</v>
+        <v>-1.165884215856954</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.648960616098793</v>
+        <v>2.650210156785335</v>
       </c>
       <c r="F1850" t="n">
-        <v>1.143123855648694</v>
+        <v>1.141705542690152</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.802794580831081</v>
+        <v>3.801943593055956</v>
       </c>
     </row>
     <row r="1851">
@@ -44118,22 +44118,22 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911643</v>
+        <v>3.233800325911641</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-1.508166445161832</v>
+        <v>-1.505042593445476</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.506381564369834</v>
+        <v>2.507631105056376</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.8039654780601719</v>
+        <v>0.8025471651016296</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.592383853584417</v>
+        <v>3.591532865809292</v>
       </c>
     </row>
     <row r="1852">
@@ -44141,22 +44141,22 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.2235393782135</v>
+        <v>3.223539378213497</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-1.836183666889311</v>
+        <v>-1.833059815172956</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.39551296541761</v>
+        <v>2.396762506104152</v>
       </c>
       <c r="F1852" t="n">
-        <v>0.4759482563326928</v>
+        <v>0.4745299433741504</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.415911810286698</v>
+        <v>3.415060822511572</v>
       </c>
     </row>
     <row r="1853">
@@ -44164,22 +44164,22 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.23116753741605</v>
+        <v>3.231167537416047</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.32950853842449</v>
+        <v>-2.326384686708134</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.206281767212107</v>
+        <v>2.20753130789865</v>
       </c>
       <c r="F1853" t="n">
-        <v>0.370962142093074</v>
+        <v>0.3695438291345317</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.361018892151495</v>
+        <v>3.36016790437637</v>
       </c>
     </row>
     <row r="1854">
@@ -44187,22 +44187,22 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382333</v>
+        <v>3.23598197738233</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-2.821893566448586</v>
+        <v>-2.818769714732231</v>
       </c>
       <c r="E1854" t="n">
-        <v>2.010434148046201</v>
+        <v>2.011683688732743</v>
       </c>
       <c r="F1854" t="n">
-        <v>-0.1214228859310227</v>
+        <v>-0.122841198889565</v>
       </c>
       <c r="G1854" t="n">
-        <v>3.066694267380769</v>
+        <v>3.065843279605644</v>
       </c>
     </row>
     <row r="1855">
@@ -44210,22 +44210,22 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495503</v>
+        <v>3.278199702495501</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.207073957378659</v>
+        <v>-3.203950105662303</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.854904530487035</v>
+        <v>1.856154071173577</v>
       </c>
       <c r="F1855" t="n">
-        <v>-0.1214228859310227</v>
+        <v>-0.122841198889565</v>
       </c>
       <c r="G1855" t="n">
-        <v>3.065236806193632</v>
+        <v>3.064385818418507</v>
       </c>
     </row>
     <row r="1856">
@@ -44233,22 +44233,22 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.29913614634706</v>
+        <v>3.299136146347057</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-3.550756730605322</v>
+        <v>-3.547632878888966</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.719200544650986</v>
+        <v>1.720450085337528</v>
       </c>
       <c r="F1856" t="n">
-        <v>-0.2293289379582409</v>
+        <v>-0.2307472509167832</v>
       </c>
       <c r="G1856" t="n">
-        <v>3.002262298431918</v>
+        <v>3.001411310656792</v>
       </c>
     </row>
     <row r="1857">
@@ -44256,22 +44256,22 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130022</v>
+        <v>3.287377576130019</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-3.90840708084367</v>
+        <v>-3.905283229127314</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.572246463211905</v>
+        <v>1.573496003898447</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.586979288196589</v>
+        <v>-0.5883976011551313</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.783778146945167</v>
+        <v>2.782927159170042</v>
       </c>
     </row>
     <row r="1858">
@@ -44279,22 +44279,22 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178249</v>
+        <v>3.315884374178246</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.217641183839721</v>
+        <v>-4.214517332123365</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.450325748713744</v>
+        <v>1.451575289400286</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.586979288196589</v>
+        <v>-0.5883976011551313</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.785551073645427</v>
+        <v>2.784700085870301</v>
       </c>
     </row>
     <row r="1859">
@@ -44302,22 +44302,22 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207819</v>
+        <v>3.305316798207815</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.649446976989508</v>
+        <v>-4.646323125273152</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.263936318921233</v>
+        <v>1.265185859607776</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.7233967846378559</v>
+        <v>-0.7248150975963983</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.690033463248071</v>
+        <v>2.689182475472945</v>
       </c>
     </row>
     <row r="1860">
@@ -44325,22 +44325,22 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310988</v>
+        <v>3.284619513310984</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-4.975879505857252</v>
+        <v>-4.972755654140896</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.121648082376226</v>
+        <v>1.122897623062769</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.8058650351450041</v>
+        <v>-0.8072833481035464</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.628837287945872</v>
+        <v>2.627986300170747</v>
       </c>
     </row>
     <row r="1861">
@@ -44348,22 +44348,22 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006538</v>
+        <v>3.305849539006534</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.311542153087704</v>
+        <v>-5.308418301371349</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.9859636151400104</v>
+        <v>0.9872131558265527</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.8058650351450041</v>
+        <v>-0.8072833481035464</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.627417879601837</v>
+        <v>2.626566891826712</v>
       </c>
     </row>
     <row r="1862">
@@ -44371,22 +44371,22 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309429</v>
+        <v>3.311086391309426</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.675168397988018</v>
+        <v>-5.672044546271662</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.847000677414127</v>
+        <v>0.8482502181006693</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.9040866720121299</v>
+        <v>-0.9055049849706722</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.574972457715804</v>
+        <v>2.574121469940678</v>
       </c>
     </row>
     <row r="1863">
@@ -44394,22 +44394,22 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.30471571697091</v>
+        <v>3.304715716970907</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.040295780626765</v>
+        <v>-6.037171928910409</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.7002042393644596</v>
+        <v>0.7014537800510019</v>
       </c>
       <c r="F1863" t="n">
-        <v>-1.200397456311142</v>
+        <v>-1.201815769269685</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.396440502142227</v>
+        <v>2.395589514367102</v>
       </c>
     </row>
     <row r="1864">
@@ -44417,22 +44417,22 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330527</v>
+        <v>3.300815818330524</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.448884557807443</v>
+        <v>-6.445760706091088</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.5355302725069473</v>
+        <v>0.5367798131934891</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.608986233491821</v>
+        <v>-1.610404546450363</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.150048779848579</v>
+        <v>2.149197792073454</v>
       </c>
     </row>
     <row r="1865">
@@ -44440,22 +44440,22 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191743</v>
+        <v>3.30261819419174</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.861867041948536</v>
+        <v>-6.858743190232182</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.3655227113219706</v>
+        <v>0.3667722520085124</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.608986233491821</v>
+        <v>-1.610404546450363</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.14523421232004</v>
+        <v>2.144383224544915</v>
       </c>
     </row>
     <row r="1866">
@@ -44463,22 +44463,22 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108645</v>
+        <v>3.305023265108642</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.278258916235534</v>
+        <v>-7.275135064519179</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.1969600122160489</v>
+        <v>0.1982095529025907</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.608986233491821</v>
+        <v>-1.610404546450363</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.143228262928917</v>
+        <v>2.142377275153792</v>
       </c>
     </row>
     <row r="1867">
@@ -44486,22 +44486,22 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097826</v>
+        <v>3.341378723097824</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.654935926765378</v>
+        <v>-7.651812075049023</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.05654789867279009</v>
+        <v>0.0577974393593319</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.608986233491821</v>
+        <v>-1.610404546450363</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.153486953597596</v>
+        <v>2.152635965822471</v>
       </c>
     </row>
     <row r="1868">
@@ -44509,22 +44509,22 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094123</v>
+        <v>3.37443904309412</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.000810748750187</v>
+        <v>-7.997686897033832</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.0857024649754381</v>
+        <v>-0.08445292428889628</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.608986233491821</v>
+        <v>-1.610404546450363</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.149586518743292</v>
+        <v>2.148735530968166</v>
       </c>
     </row>
     <row r="1869">
@@ -44532,22 +44532,22 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199292</v>
+        <v>3.405960511199289</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.313635547995165</v>
+        <v>-8.310511696278811</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.2124274646184285</v>
+        <v>-0.2111779239318867</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.608986233491821</v>
+        <v>-1.610404546450363</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.147991438798293</v>
+        <v>2.147140451023167</v>
       </c>
     </row>
     <row r="1870">
@@ -44555,22 +44555,22 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.4246333549696</v>
+        <v>3.424633354969597</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.610296889805364</v>
+        <v>-8.607173038089009</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.3273130254132997</v>
+        <v>-0.3260634847267578</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.677729369225699</v>
+        <v>-1.679147682184242</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.110524533287173</v>
+        <v>2.109673545512048</v>
       </c>
     </row>
     <row r="1871">
@@ -44578,22 +44578,22 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923093</v>
+        <v>3.41997943392309</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-9.043645997915599</v>
+        <v>-9.040522146199244</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.5046789731917971</v>
+        <v>-0.5034294325052553</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.677729369225699</v>
+        <v>-1.679147682184242</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.106498228752771</v>
+        <v>2.105647240977645</v>
       </c>
     </row>
     <row r="1872">
@@ -44601,22 +44601,22 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297756</v>
+        <v>3.458100091297753</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.42664738665823</v>
+        <v>-9.423523534941875</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.6579816300104335</v>
+        <v>-0.6567320893238917</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.677729369225699</v>
+        <v>-1.679147682184242</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.106396127431187</v>
+        <v>2.105545139656061</v>
       </c>
     </row>
     <row r="1873">
@@ -44624,22 +44624,22 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317622</v>
+        <v>3.44775050131762</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.801632712829507</v>
+        <v>-9.798508861113152</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.8054042445075145</v>
+        <v>-0.8041547038209722</v>
       </c>
       <c r="F1873" t="n">
-        <v>-2.052714695396977</v>
+        <v>-2.054133008355519</v>
       </c>
       <c r="G1873" t="n">
-        <v>1.88397644769985</v>
+        <v>1.883125459924725</v>
       </c>
     </row>
     <row r="1874">
@@ -44647,22 +44647,22 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737177</v>
+        <v>3.503515506737174</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-10.16116303533351</v>
+        <v>-10.15803918361715</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.9438660702110644</v>
+        <v>-0.942616529524523</v>
       </c>
       <c r="F1874" t="n">
-        <v>-2.052714695396977</v>
+        <v>-2.054133008355519</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.8893267509979</v>
+        <v>1.888475763222775</v>
       </c>
     </row>
     <row r="1875">
@@ -44670,22 +44670,22 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.50317028234132</v>
+        <v>3.503170282341316</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-10.48756306399852</v>
+        <v>-10.48443921228217</v>
       </c>
       <c r="E1875" t="n">
-        <v>-1.066510061719893</v>
+        <v>-1.065260521033351</v>
       </c>
       <c r="F1875" t="n">
-        <v>-2.37911472406199</v>
+        <v>-2.380533037020532</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.70140275375607</v>
+        <v>1.700551765980945</v>
       </c>
     </row>
     <row r="1876">
@@ -44693,22 +44693,22 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776684</v>
+        <v>3.50044609677668</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.70671203207272</v>
+        <v>-10.70358818035636</v>
       </c>
       <c r="E1876" t="n">
-        <v>-1.151127898327803</v>
+        <v>-1.14987835764126</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.598263692136187</v>
+        <v>-2.59968200509473</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.57295512353332</v>
+        <v>1.572104135758195</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,22 +44716,22 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407496</v>
+        <v>3.492445136407494</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.70302110711631</v>
+        <v>-10.69989725539995</v>
       </c>
       <c r="E1877" t="n">
-        <v>-1.149651528345239</v>
+        <v>-1.148401987658696</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.598263692136187</v>
+        <v>-2.59968200509473</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.57295512353332</v>
+        <v>1.572104135758195</v>
       </c>
     </row>
     <row r="1878">
@@ -44739,22 +44739,22 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611698</v>
+        <v>3.502786823611697</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.90727928244617</v>
+        <v>-10.90415543072982</v>
       </c>
       <c r="E1878" t="n">
-        <v>-1.225841601358542</v>
+        <v>-1.224592060671999</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.725902636750176</v>
+        <v>-2.727320949708719</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.501884953883569</v>
+        <v>1.501033966108444</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199888</v>
+        <v>3.496848329199886</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-11.12531705407735</v>
+        <v>-11.12219320236099</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.308574155526576</v>
+        <v>-1.307324614840035</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.900673404846075</v>
+        <v>-2.902091717804617</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.401505047510466</v>
+        <v>1.400654059735341</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910631</v>
+        <v>3.499968163910629</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-11.24639319253821</v>
+        <v>-11.04872337069355</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.341632909417499</v>
+        <v>-1.262564980679634</v>
       </c>
       <c r="F1880" t="n">
-        <v>-3.021749543306936</v>
+        <v>-2.828621886137169</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.344231065927371</v>
+        <v>1.460107660229231</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078598</v>
+        <v>3.490055666078597</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-11.42151760992475</v>
+        <v>-11.22384778808009</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.397127455624601</v>
+        <v>-1.318059526886734</v>
       </c>
       <c r="F1881" t="n">
-        <v>-3.19687396069348</v>
+        <v>-3.003746303523713</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.253711636242961</v>
+        <v>1.369588230544821</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880272</v>
+        <v>3.485875018880269</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-11.65596970393924</v>
+        <v>-11.45829988209458</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.498127458131992</v>
+        <v>-1.419059529394126</v>
       </c>
       <c r="F1882" t="n">
-        <v>-3.19687396069348</v>
+        <v>-3.003746303523713</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.246492471341365</v>
+        <v>1.362369065643225</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234397</v>
+        <v>3.480688917234395</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.94377354847648</v>
+        <v>-11.74610372663182</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.619921186720864</v>
+        <v>-1.540853257982997</v>
       </c>
       <c r="F1883" t="n">
-        <v>-3.484677805230718</v>
+        <v>-3.291550148060951</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.067137973845046</v>
+        <v>1.183014568146906</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860586</v>
+        <v>3.493712438860584</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-12.17359799564031</v>
+        <v>-11.97592817379564</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.710735175747837</v>
+        <v>-1.631667247009972</v>
       </c>
       <c r="F1884" t="n">
-        <v>-3.647325342300878</v>
+        <v>-3.454197685131112</v>
       </c>
       <c r="G1884" t="n">
-        <v>0.9706652414415062</v>
+        <v>1.086541835743366</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.4920980657674</v>
+        <v>3.492098065767398</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-12.40562691537657</v>
+        <v>-12.2079570935319</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.800853015013228</v>
+        <v>-1.721785086275362</v>
       </c>
       <c r="F1885" t="n">
-        <v>-3.709338039489301</v>
+        <v>-3.516210382319535</v>
       </c>
       <c r="G1885" t="n">
-        <v>0.9361513517575673</v>
+        <v>1.052027946059427</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792544</v>
+        <v>3.573670449792542</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-12.35361140140776</v>
+        <v>-12.15594157956309</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.776056473739302</v>
+        <v>-1.696988545001435</v>
       </c>
       <c r="F1886" t="n">
-        <v>-3.709338039489301</v>
+        <v>-3.516210382319535</v>
       </c>
       <c r="G1886" t="n">
-        <v>0.9401416874439681</v>
+        <v>1.056018281745828</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628922</v>
+        <v>3.600034689628919</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-12.49528324313188</v>
+        <v>-12.29761342128721</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.834200437327691</v>
+        <v>-1.755132508589825</v>
       </c>
       <c r="F1887" t="n">
-        <v>-3.709338039489301</v>
+        <v>-3.516210382319535</v>
       </c>
       <c r="G1887" t="n">
-        <v>0.9386664605452264</v>
+        <v>1.054543054847086</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.69156815841072</v>
+        <v>3.691568158410717</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-12.59418998359115</v>
+        <v>-12.39652016174649</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.858709723346529</v>
+        <v>-1.779641794608664</v>
       </c>
       <c r="F1888" t="n">
-        <v>-3.808244779948577</v>
+        <v>-3.61511712277881</v>
       </c>
       <c r="G1888" t="n">
-        <v>0.8943758264345334</v>
+        <v>1.010252420736393</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.67683797424058</v>
+        <v>3.676837974240577</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-12.39503787635405</v>
+        <v>-12.19736805450939</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.792100014098372</v>
+        <v>-1.713032085360507</v>
       </c>
       <c r="F1889" t="n">
-        <v>-3.642922253998763</v>
+        <v>-3.449794596828997</v>
       </c>
       <c r="G1889" t="n">
-        <v>0.9805182083577382</v>
+        <v>1.096394802659598</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085282</v>
+        <v>3.685157806085279</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-12.16919272363464</v>
+        <v>-11.97152290178998</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.692182879974399</v>
+        <v>-1.613114951236534</v>
       </c>
       <c r="F1890" t="n">
-        <v>-3.6009955784116</v>
+        <v>-3.407867921241833</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.015253286746245</v>
+        <v>1.131129881048105</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282104</v>
+        <v>3.6848402482821</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.88291791131195</v>
+        <v>-11.68524808946728</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.576533810489262</v>
+        <v>-1.497465881751397</v>
       </c>
       <c r="F1891" t="n">
-        <v>-3.6009955784116</v>
+        <v>-3.407867921241833</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.016392431302304</v>
+        <v>1.132269025604164</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116219</v>
+        <v>3.710931958116215</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.93581319935623</v>
+        <v>-11.73814337751157</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.595058151544869</v>
+        <v>-1.515990222807004</v>
       </c>
       <c r="F1892" t="n">
-        <v>-3.596040232323154</v>
+        <v>-3.402912575153387</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.021999413117479</v>
+        <v>1.137876007419339</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081571</v>
+        <v>3.768948099081567</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.65190446842748</v>
+        <v>-11.45423464658282</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.475760954934733</v>
+        <v>-1.396693026196868</v>
       </c>
       <c r="F1893" t="n">
-        <v>-3.596040232323154</v>
+        <v>-3.402912575153387</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.027733117356116</v>
+        <v>1.143609711657976</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425332</v>
+        <v>3.728574354425326</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-11.40491721823453</v>
+        <v>-11.20724739638987</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.386703317251418</v>
+        <v>-1.307635388513552</v>
       </c>
       <c r="F1894" t="n">
-        <v>-3.349052982130202</v>
+        <v>-3.155925324960435</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.166188205078022</v>
+        <v>1.282064799379882</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702416</v>
+        <v>3.747699084702411</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-11.14108035103046</v>
+        <v>-10.9434105291858</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.291052051682697</v>
+        <v>-1.211984122944832</v>
       </c>
       <c r="F1895" t="n">
-        <v>-3.349052982130202</v>
+        <v>-3.155925324960435</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.156304723765115</v>
+        <v>1.272181318066974</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906231</v>
+        <v>3.766313503906227</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.87383855016206</v>
+        <v>-10.6761687283174</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.185989891834712</v>
+        <v>-1.106921963096847</v>
       </c>
       <c r="F1896" t="n">
-        <v>-3.349052982130202</v>
+        <v>-3.155925324960435</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.154470163265741</v>
+        <v>1.2703467575676</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781952</v>
+        <v>3.784680945781949</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.59802938676158</v>
+        <v>-10.40035956491692</v>
       </c>
       <c r="E1897" t="n">
-        <v>-1.075966541447979</v>
+        <v>-0.996898612710114</v>
       </c>
       <c r="F1897" t="n">
-        <v>-3.260033673851468</v>
+        <v>-3.066906016681702</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.20758143325952</v>
+        <v>1.32345802756138</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567248</v>
+        <v>3.800825778567244</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.57407584578562</v>
+        <v>-10.37640602394096</v>
       </c>
       <c r="E1898" t="n">
-        <v>-1.065716618912102</v>
+        <v>-0.9866486901742371</v>
       </c>
       <c r="F1898" t="n">
-        <v>-3.23608013287551</v>
+        <v>-3.042952475705744</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.222622063990588</v>
+        <v>1.338498658292448</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487778</v>
+        <v>3.789307536487774</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.31001590746282</v>
+        <v>-10.11234608561816</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.9733529597447355</v>
+        <v>-0.89428503100687</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.972020194552714</v>
+        <v>-2.778892537382948</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.367797710822513</v>
+        <v>1.483674305124373</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.83324917230973</v>
+        <v>3.833249172309727</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.602936283957987</v>
+        <v>-9.405266462113325</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.6933081440031015</v>
+        <v>-0.6142402152652364</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.972020194552714</v>
+        <v>-2.778892537382948</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.365010677162213</v>
+        <v>1.480887271464072</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858733</v>
+        <v>3.83937087185873</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.562751985591797</v>
+        <v>-9.365082163747134</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.6768908007687839</v>
+        <v>-0.5978228720309189</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.931835896186524</v>
+        <v>-2.738708239016757</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.389464880069768</v>
+        <v>1.505341474371628</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096479</v>
+        <v>3.856158176096476</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.482682190053993</v>
+        <v>-9.28501236820933</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.645496061332905</v>
+        <v>-0.56642813259504</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.85176610064872</v>
+        <v>-2.658638443478953</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.436873578613208</v>
+        <v>1.552750172915067</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761811</v>
+        <v>3.787326853761809</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-9.249200967824393</v>
+        <v>-9.05153114597973</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.5441791436032131</v>
+        <v>-0.465111214865348</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.618284878419121</v>
+        <v>-2.425157221249355</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.584886740788819</v>
+        <v>1.700763335090679</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255788</v>
+        <v>3.801633547255786</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-9.06949243768052</v>
+        <v>-8.871822615835857</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.4751879418586227</v>
+        <v>-0.3961200131207576</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.561113374256425</v>
+        <v>-2.367985717086659</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.616297432973478</v>
+        <v>1.732174027275337</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.76317867286043</v>
+        <v>3.763178672860428</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.937216964049632</v>
+        <v>-8.73954714220497</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.4269102656592407</v>
+        <v>-0.3478423369213757</v>
       </c>
       <c r="F1905" t="n">
-        <v>-2.428837900625539</v>
+        <v>-2.235710243455773</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.691030203899037</v>
+        <v>1.806906798200896</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575956</v>
+        <v>3.784715218575954</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.746617289376479</v>
+        <v>-8.548947467531816</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.3478553351023428</v>
+        <v>-0.2687874063644777</v>
       </c>
       <c r="F1906" t="n">
-        <v>-2.238238225952386</v>
+        <v>-2.04511056878262</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.808205069390565</v>
+        <v>1.924081663692425</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.75387899643099</v>
+        <v>3.753878996430989</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.497617490692898</v>
+        <v>-8.299947668848235</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.2353490744052515</v>
+        <v>-0.1562811456673865</v>
       </c>
       <c r="F1907" t="n">
-        <v>-2.238238225952386</v>
+        <v>-2.04511056878262</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.821111410614224</v>
+        <v>1.936988004916083</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077648</v>
+        <v>3.692928280077646</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.603207480466002</v>
+        <v>-8.40553765862134</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.4055609999137122</v>
+        <v>-0.3264930711758467</v>
       </c>
       <c r="F1908" t="n">
-        <v>-2.343828215725491</v>
+        <v>-2.150700558555724</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.629781487151142</v>
+        <v>1.745658081453002</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457906</v>
+        <v>3.770419008457903</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.621942382584599</v>
+        <v>-8.424272560739936</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.3645106188840646</v>
+        <v>-0.2854426901461995</v>
       </c>
       <c r="F1909" t="n">
-        <v>-2.343828215725491</v>
+        <v>-2.150700558555724</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.678325829028229</v>
+        <v>1.794202423330088</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180812</v>
+        <v>3.760330111180811</v>
       </c>
       <c r="C1910" t="n">
         <v>3.088001770449517</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.345204207913786</v>
+        <v>-8.147534386069124</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.2504363370297447</v>
+        <v>-0.1713684082918796</v>
       </c>
       <c r="F1910" t="n">
-        <v>-2.162011554615565</v>
+        <v>-1.968883897445799</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.790794837680179</v>
+        <v>1.906671431982039</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>3.079287784196039</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.218311801478716</v>
+        <v>-8.020641979634053</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.2083933607091946</v>
+        <v>-0.1293254319713295</v>
       </c>
       <c r="F1911" t="n">
-        <v>-2.035119148180495</v>
+        <v>-1.841991491010729</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.858216295287743</v>
+        <v>1.974092889589602</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>3.072327172100946</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.174763394708025</v>
+        <v>-7.977093572863363</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.1979346100960115</v>
+        <v>-0.1188666813581465</v>
       </c>
       <c r="F1912" t="n">
-        <v>-2.035119148180495</v>
+        <v>-1.841991491010729</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.851255683192649</v>
+        <v>1.967132277494509</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>3.086789526482089</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.932615001254167</v>
+        <v>-7.734945179409505</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.08661289833332519</v>
+        <v>-0.007544969595460138</v>
       </c>
       <c r="F1913" t="n">
-        <v>-2.035119148180495</v>
+        <v>-1.841991491010729</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.865718037573793</v>
+        <v>1.981594631875652</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>3.081321646941284</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.869385629485818</v>
+        <v>-7.671715807641156</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.06678902916679075</v>
+        <v>0.01227889957107431</v>
       </c>
       <c r="F1914" t="n">
-        <v>-2.035119148180495</v>
+        <v>-1.841991491010729</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.860250158032988</v>
+        <v>1.976126752334847</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262049</v>
+        <v>3.828049353262048</v>
       </c>
       <c r="C1915" t="n">
         <v>3.078819740951861</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.682897937108812</v>
+        <v>-7.48522811526415</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.005304141794588713</v>
+        <v>0.08437207053245332</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.848631455803489</v>
+        <v>-1.655503798633722</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.969640867469768</v>
+        <v>2.085517461771628</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389911</v>
+        <v>3.81245010338991</v>
       </c>
       <c r="C1916" t="n">
         <v>3.086520719189187</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.661748738205369</v>
+        <v>-7.464078916360707</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.02146479959329151</v>
+        <v>0.1005327283311566</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.827482256900045</v>
+        <v>-1.634354599730279</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.99003136504916</v>
+        <v>2.105907959351019</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788096</v>
+        <v>3.748324832788095</v>
       </c>
       <c r="C1917" t="n">
         <v>3.082301427536237</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.417983296221925</v>
+        <v>-7.220313474377263</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.11475168473372</v>
+        <v>0.1938196134715846</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.827482256900045</v>
+        <v>-1.634354599730279</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.98581207339621</v>
+        <v>2.10168866769807</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527528</v>
+        <v>3.824307657527527</v>
       </c>
       <c r="C1918" t="n">
         <v>3.084425741456253</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.153955229028664</v>
+        <v>-6.956285407184003</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.2224872255310402</v>
+        <v>0.3015551542689048</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.625616858084092</v>
+        <v>-1.432489200914326</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.109055626605798</v>
+        <v>2.224932220907658</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>3.077167816439955</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.90410483507959</v>
+        <v>-6.706435013234929</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.3151694580943722</v>
+        <v>0.3942373868322364</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.625616858084092</v>
+        <v>-1.432489200914326</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.101797701589501</v>
+        <v>2.21767429589136</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.8359544114815</v>
+        <v>3.835954411481499</v>
       </c>
       <c r="C1920" t="n">
         <v>3.080766939960604</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.600537346075611</v>
+        <v>-6.40286752423095</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.4401955772166124</v>
+        <v>0.519263505954477</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.625616858084092</v>
+        <v>-1.432489200914326</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.105396825110149</v>
+        <v>2.221273419412009</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862989</v>
+        <v>3.780930335862988</v>
       </c>
       <c r="C1921" t="n">
         <v>3.094094446015158</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.527057437223597</v>
+        <v>-6.329387615378936</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.4829150468119718</v>
+        <v>0.561982975549836</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.552136949232077</v>
+        <v>-1.359009292062311</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.162812276475912</v>
+        <v>2.278688870777771</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102784</v>
+        <v>3.773761647102783</v>
       </c>
       <c r="C1922" t="n">
         <v>3.093114923631455</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.302024437554774</v>
+        <v>-6.104354615710113</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.5719487242957979</v>
+        <v>0.6510166530336621</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.327103949563254</v>
+        <v>-1.133976292393488</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.296852553893503</v>
+        <v>2.412729148195362</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353079</v>
+        <v>3.764614304353077</v>
       </c>
       <c r="C1923" t="n">
         <v>3.097809724685772</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.087390059918367</v>
+        <v>-5.889720238073706</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.6624972764046779</v>
+        <v>0.7415652051425425</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.112469571926848</v>
+        <v>-0.9193419147570814</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.430327981529664</v>
+        <v>2.546204575831524</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544786</v>
+        <v>3.798811195544785</v>
       </c>
       <c r="C1924" t="n">
         <v>3.079003983469568</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.820789702944015</v>
+        <v>-5.623119881099354</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.7503316779782141</v>
+        <v>0.8293996067160787</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.112469571926848</v>
+        <v>-0.9193419147570814</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.41152224031346</v>
+        <v>2.527398834615319</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712298</v>
+        <v>3.797691308712297</v>
       </c>
       <c r="C1925" t="n">
         <v>3.080747060094445</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.580359206139155</v>
+        <v>-5.382689384294494</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.8482469533250359</v>
+        <v>0.9273148820629</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.8720390751219873</v>
+        <v>-0.6789114179522211</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.557523615021253</v>
+        <v>2.673400209323113</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837689</v>
+        <v>3.821589933837688</v>
       </c>
       <c r="C1926" t="n">
         <v>3.084676373929265</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.33756839848971</v>
+        <v>-5.139898576645049</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.9492925902196343</v>
+        <v>1.028360518957498</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.8720390751219873</v>
+        <v>-0.6789114179522211</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.561452928856073</v>
+        <v>2.677329523157933</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349971</v>
+        <v>3.822323422349969</v>
       </c>
       <c r="C1927" t="n">
         <v>3.085354957846605</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.097963306882621</v>
+        <v>-4.90029348503796</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.04581321077981</v>
+        <v>1.124881139517674</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.8049911274534928</v>
+        <v>-0.6118634702837266</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.60236028137451</v>
+        <v>2.71823687567637</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972345</v>
+        <v>3.848613050972342</v>
       </c>
       <c r="C1928" t="n">
         <v>3.082353029066599</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.855307718459457</v>
+        <v>-4.657637896614796</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.139873517369069</v>
+        <v>1.218941446106933</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.8049911274534928</v>
+        <v>-0.6118634702837266</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.599358352594503</v>
+        <v>2.715234946896363</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145945</v>
+        <v>3.818665376145942</v>
       </c>
       <c r="C1929" t="n">
         <v>3.083932066077213</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.635286920422446</v>
+        <v>-4.437617098577785</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.229460873594487</v>
+        <v>1.308528802332352</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.6637712823855125</v>
+        <v>-0.4706436252157463</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.685669296645906</v>
+        <v>2.801545890947765</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009957</v>
+        <v>3.843270952009954</v>
       </c>
       <c r="C1930" t="n">
         <v>3.099826248879036</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.436038290517637</v>
+        <v>-4.238368468672976</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.325054508358234</v>
+        <v>1.404122437096099</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.6637712823855125</v>
+        <v>-0.4706436252157463</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.701563479447729</v>
+        <v>2.817440073749589</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966261</v>
+        <v>3.84504381096626</v>
       </c>
       <c r="C1931" t="n">
         <v>3.100972093319338</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.276523186998268</v>
+        <v>-4.078853365153607</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.390006394206284</v>
+        <v>1.469074322944148</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.5042561788661426</v>
+        <v>-0.3111285216963764</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.798418385999653</v>
+        <v>2.914294980301512</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046998</v>
+        <v>3.791269976046996</v>
       </c>
       <c r="C1932" t="n">
         <v>3.111060195880778</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.13185104189853</v>
+        <v>-3.934181220053869</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.457963354807619</v>
+        <v>1.537031283545483</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.3595840337664052</v>
+        <v>-0.166456376596639</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.895309775620935</v>
+        <v>3.011186369922795</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,19 +46004,19 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.445944781420092</v>
+        <v>3.44594478142009</v>
       </c>
       <c r="C1933" t="n">
         <v>2.922598507788898</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.13185104189853</v>
+        <v>-3.934181220053869</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.457963354807619</v>
+        <v>1.537031283545483</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.3595840337664052</v>
+        <v>-0.166456376596639</v>
       </c>
       <c r="G1933" t="n">
         <v>2.915662304775266</v>

--- a/tame_output/ON/bt/strategyON_20240413.xlsx
+++ b/tame_output/ON/bt/strategyON_20240413.xlsx
@@ -46007,7 +46007,7 @@
         <v>3.44594478142009</v>
       </c>
       <c r="C1933" t="n">
-        <v>2.922598507788898</v>
+        <v>2.922598507788897</v>
       </c>
       <c r="D1933" t="n">
         <v>-3.934181220053869</v>
@@ -46019,7 +46019,7 @@
         <v>-0.166456376596639</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.915662304775266</v>
+        <v>2.915662304775265</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240413.xlsx
+++ b/tame_output/ON/bt/strategyON_20240413.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>51.3%</t>
+          <t>56.3%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.8%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>68.6%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.9%</t>
+          <t>-12.4%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>16.5%</t>
+          <t>28.9%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>65.9%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>33.1%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>25.5%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-15.8%</t>
+          <t>-15.3%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>51.5%</t>
+          <t>51.7%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>23.6%</t>
+          <t>23.7%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-18.8%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.3%</t>
+          <t>-79.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>119.0%</t>
+          <t>119.1%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>138.9%</t>
+          <t>139.0%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>29.1%</t>
+          <t>29.0%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-57.6%</t>
+          <t>-57.7%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>601.4%</t>
+          <t>671.2%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>-0.6%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-555.0%</t>
+          <t>-559.5%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>9.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.5%</t>
+          <t>56.1%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1150,47 +1150,47 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>14.1%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-45.0%</t>
+          <t>-45.1%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>11.4%</t>
+          <t>5.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-19.1%</t>
+          <t>-18.2%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-516.7%</t>
+          <t>-181.9%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-222.5%</t>
+          <t>-242.6%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-28.5%</t>
+          <t>-27.5%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>71.5%</t>
+          <t>71.6%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>70.2%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-304.7%</t>
+          <t>-295.4%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-37.7%</t>
+          <t>-37.1%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-22.2%</t>
+          <t>-20.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>34.9%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-151.5%</t>
+          <t>-147.6%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-240.6%</t>
+          <t>-232.8%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>50.2%</t>
+          <t>48.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>51.8%</t>
+          <t>52.3%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>59.3%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.8%</t>
+          <t>64.8%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>97.8%</t>
+          <t>97.7%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-183.2%</t>
+          <t>-177.7%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-32.5%</t>
+          <t>-32.0%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>44.6%</t>
+          <t>42.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.2%</t>
+          <t>43.6%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.7%</t>
+          <t>-16.3%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.0%</t>
+          <t>34.1%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-154.5%</t>
+          <t>-158.5%</t>
         </is>
       </c>
     </row>
@@ -43779,16 +43779,16 @@
         <v>3.118001050765402</v>
       </c>
       <c r="D1836" t="n">
-        <v>0.5071246096708681</v>
+        <v>0.4760989193967312</v>
       </c>
       <c r="E1836" t="n">
-        <v>3.320494470320002</v>
+        <v>3.308084194210347</v>
       </c>
       <c r="F1836" t="n">
-        <v>1.88540607818898</v>
+        <v>1.978119055628494</v>
       </c>
       <c r="G1836" t="n">
-        <v>4.249244697678789</v>
+        <v>4.304872484142498</v>
       </c>
     </row>
     <row r="1837">
@@ -43802,16 +43802,16 @@
         <v>3.118490189491276</v>
       </c>
       <c r="D1837" t="n">
-        <v>0.5129739907861125</v>
+        <v>0.4819483005119756</v>
       </c>
       <c r="E1837" t="n">
-        <v>3.323323361491973</v>
+        <v>3.310913085382319</v>
       </c>
       <c r="F1837" t="n">
-        <v>1.88540607818898</v>
+        <v>1.978119055628494</v>
       </c>
       <c r="G1837" t="n">
-        <v>4.249733836404664</v>
+        <v>4.305361622868372</v>
       </c>
     </row>
     <row r="1838">
@@ -43825,16 +43825,16 @@
         <v>3.122570172112943</v>
       </c>
       <c r="D1838" t="n">
-        <v>0.464751723939029</v>
+        <v>0.433726033664892</v>
       </c>
       <c r="E1838" t="n">
-        <v>3.308114437374807</v>
+        <v>3.295704161265152</v>
       </c>
       <c r="F1838" t="n">
-        <v>1.837183811341896</v>
+        <v>1.92989678878141</v>
       </c>
       <c r="G1838" t="n">
-        <v>4.224880458918081</v>
+        <v>4.280508245381789</v>
       </c>
     </row>
     <row r="1839">
@@ -43848,16 +43848,16 @@
         <v>3.157511256610484</v>
       </c>
       <c r="D1839" t="n">
-        <v>0.2276202320892339</v>
+        <v>0.1965945418150969</v>
       </c>
       <c r="E1839" t="n">
-        <v>3.248202925132431</v>
+        <v>3.235792649022776</v>
       </c>
       <c r="F1839" t="n">
-        <v>1.837183811341896</v>
+        <v>1.92989678878141</v>
       </c>
       <c r="G1839" t="n">
-        <v>4.259821543415622</v>
+        <v>4.31544932987933</v>
       </c>
     </row>
     <row r="1840">
@@ -43871,16 +43871,16 @@
         <v>3.156088696795822</v>
       </c>
       <c r="D1840" t="n">
-        <v>0.2326578228168204</v>
+        <v>0.2016321325426835</v>
       </c>
       <c r="E1840" t="n">
-        <v>3.248795401608803</v>
+        <v>3.236385125499149</v>
       </c>
       <c r="F1840" t="n">
-        <v>1.892828267608213</v>
+        <v>1.985541245047727</v>
       </c>
       <c r="G1840" t="n">
-        <v>4.291785657360751</v>
+        <v>4.347413443824458</v>
       </c>
     </row>
     <row r="1841">
@@ -43894,16 +43894,16 @@
         <v>3.13483507841956</v>
       </c>
       <c r="D1841" t="n">
-        <v>0.1761881916405236</v>
+        <v>0.1451625013663867</v>
       </c>
       <c r="E1841" t="n">
-        <v>3.204953930762022</v>
+        <v>3.192543654652367</v>
       </c>
       <c r="F1841" t="n">
-        <v>1.836358636431916</v>
+        <v>1.92907161387143</v>
       </c>
       <c r="G1841" t="n">
-        <v>4.23665026027871</v>
+        <v>4.292278046742418</v>
       </c>
     </row>
     <row r="1842">
@@ -43917,16 +43917,16 @@
         <v>3.13585268755003</v>
       </c>
       <c r="D1842" t="n">
-        <v>0.1104208015911116</v>
+        <v>0.07939511131697463</v>
       </c>
       <c r="E1842" t="n">
-        <v>3.179664583872727</v>
+        <v>3.167254307763072</v>
       </c>
       <c r="F1842" t="n">
-        <v>1.836358636431916</v>
+        <v>1.92907161387143</v>
       </c>
       <c r="G1842" t="n">
-        <v>4.237667869409179</v>
+        <v>4.293295655872888</v>
       </c>
     </row>
     <row r="1843">
@@ -43940,16 +43940,16 @@
         <v>3.126480719537785</v>
       </c>
       <c r="D1843" t="n">
-        <v>0.09688531781440196</v>
+        <v>0.06585962754026503</v>
       </c>
       <c r="E1843" t="n">
-        <v>3.164878422349799</v>
+        <v>3.152468146240144</v>
       </c>
       <c r="F1843" t="n">
-        <v>1.836358636431916</v>
+        <v>1.92907161387143</v>
       </c>
       <c r="G1843" t="n">
-        <v>4.228295901396935</v>
+        <v>4.283923687860644</v>
       </c>
     </row>
     <row r="1844">
@@ -43963,16 +43963,16 @@
         <v>3.116563445493024</v>
       </c>
       <c r="D1844" t="n">
-        <v>0.01511341738665029</v>
+        <v>-0.01591227288748664</v>
       </c>
       <c r="E1844" t="n">
-        <v>3.122252388133937</v>
+        <v>3.109842112024282</v>
       </c>
       <c r="F1844" t="n">
-        <v>1.863394209838053</v>
+        <v>1.956107187277567</v>
       </c>
       <c r="G1844" t="n">
-        <v>4.234599971395856</v>
+        <v>4.290227757859563</v>
       </c>
     </row>
     <row r="1845">
@@ -43986,16 +43986,16 @@
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.05209569048522739</v>
+        <v>-0.08312138075936432</v>
       </c>
       <c r="E1845" t="n">
-        <v>3.100134061818888</v>
+        <v>3.087723785709233</v>
       </c>
       <c r="F1845" t="n">
-        <v>1.863394209838053</v>
+        <v>1.956107187277567</v>
       </c>
       <c r="G1845" t="n">
-        <v>4.239365288229558</v>
+        <v>4.294993074693267</v>
       </c>
     </row>
     <row r="1846">
@@ -44009,16 +44009,16 @@
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-0.04810423769003719</v>
+        <v>-0.07912992796417412</v>
       </c>
       <c r="E1846" t="n">
-        <v>3.099555439056204</v>
+        <v>3.087145162946549</v>
       </c>
       <c r="F1846" t="n">
-        <v>1.867385662633243</v>
+        <v>1.960098640072757</v>
       </c>
       <c r="G1846" t="n">
-        <v>4.239584956025912</v>
+        <v>4.29521274248962</v>
       </c>
     </row>
     <row r="1847">
@@ -44032,16 +44032,16 @@
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-0.4658582612368742</v>
+        <v>-0.4968839515110111</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.930380721142532</v>
+        <v>2.917970445032878</v>
       </c>
       <c r="F1847" t="n">
-        <v>1.449631639086406</v>
+        <v>1.54234461652592</v>
       </c>
       <c r="G1847" t="n">
-        <v>3.986859433402874</v>
+        <v>4.042487219866581</v>
       </c>
     </row>
     <row r="1848">
@@ -44055,16 +44055,16 @@
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-0.6874801947949917</v>
+        <v>-0.7185058850691286</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.841598164318207</v>
+        <v>2.829187888208553</v>
       </c>
       <c r="F1848" t="n">
-        <v>1.412105505399037</v>
+        <v>1.504818482838551</v>
       </c>
       <c r="G1848" t="n">
-        <v>3.964209969789374</v>
+        <v>4.019837756253082</v>
       </c>
     </row>
     <row r="1849">
@@ -44078,16 +44078,16 @@
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-0.8954842531480689</v>
+        <v>-0.9265099434222058</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.763288685530902</v>
+        <v>2.750878409421247</v>
       </c>
       <c r="F1849" t="n">
-        <v>1.412105505399037</v>
+        <v>1.504818482838551</v>
       </c>
       <c r="G1849" t="n">
-        <v>3.969102114343299</v>
+        <v>4.024729900807007</v>
       </c>
     </row>
     <row r="1850">
@@ -44101,16 +44101,16 @@
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.165884215856954</v>
+        <v>-1.196909906131091</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.650210156785335</v>
+        <v>2.637799880675681</v>
       </c>
       <c r="F1850" t="n">
-        <v>1.141705542690152</v>
+        <v>1.234418520129666</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.801943593055956</v>
+        <v>3.857571379519664</v>
       </c>
     </row>
     <row r="1851">
@@ -44124,16 +44124,16 @@
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-1.505042593445476</v>
+        <v>-1.536068283719613</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.507631105056376</v>
+        <v>2.495220828946721</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.8025471651016296</v>
+        <v>0.8952601425411435</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.591532865809292</v>
+        <v>3.647160652273</v>
       </c>
     </row>
     <row r="1852">
@@ -44147,16 +44147,16 @@
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-1.833059815172956</v>
+        <v>-1.864085505447092</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.396762506104152</v>
+        <v>2.384352229994498</v>
       </c>
       <c r="F1852" t="n">
-        <v>0.4745299433741504</v>
+        <v>0.5672429208136643</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.415060822511572</v>
+        <v>3.470688608975281</v>
       </c>
     </row>
     <row r="1853">
@@ -44170,16 +44170,16 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.326384686708134</v>
+        <v>-2.35741037698227</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.20753130789865</v>
+        <v>2.195121031788995</v>
       </c>
       <c r="F1853" t="n">
-        <v>0.3695438291345317</v>
+        <v>0.4622568065740456</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.36016790437637</v>
+        <v>3.415795690840078</v>
       </c>
     </row>
     <row r="1854">
@@ -44193,16 +44193,16 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-2.818769714732231</v>
+        <v>-2.849795405006367</v>
       </c>
       <c r="E1854" t="n">
-        <v>2.011683688732743</v>
+        <v>1.999273412623088</v>
       </c>
       <c r="F1854" t="n">
-        <v>-0.122841198889565</v>
+        <v>-0.03012822145005112</v>
       </c>
       <c r="G1854" t="n">
-        <v>3.065843279605644</v>
+        <v>3.121471066069352</v>
       </c>
     </row>
     <row r="1855">
@@ -44216,16 +44216,16 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.203950105662303</v>
+        <v>-3.234975795936439</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.856154071173577</v>
+        <v>1.843743795063923</v>
       </c>
       <c r="F1855" t="n">
-        <v>-0.122841198889565</v>
+        <v>-0.03012822145005112</v>
       </c>
       <c r="G1855" t="n">
-        <v>3.064385818418507</v>
+        <v>3.120013604882216</v>
       </c>
     </row>
     <row r="1856">
@@ -44239,16 +44239,16 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-3.547632878888966</v>
+        <v>-3.578658569163102</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.720450085337528</v>
+        <v>1.708039809227874</v>
       </c>
       <c r="F1856" t="n">
-        <v>-0.2307472509167832</v>
+        <v>-0.1380342734772693</v>
       </c>
       <c r="G1856" t="n">
-        <v>3.001411310656792</v>
+        <v>3.057039097120501</v>
       </c>
     </row>
     <row r="1857">
@@ -44262,16 +44262,16 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-3.905283229127314</v>
+        <v>-3.93630891940145</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.573496003898447</v>
+        <v>1.561085727788792</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.5883976011551313</v>
+        <v>-0.4956846237156174</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.782927159170042</v>
+        <v>2.83855494563375</v>
       </c>
     </row>
     <row r="1858">
@@ -44285,16 +44285,16 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.214517332123365</v>
+        <v>-4.2455430223975</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.451575289400286</v>
+        <v>1.439165013290632</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.5883976011551313</v>
+        <v>-0.4956846237156174</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.784700085870301</v>
+        <v>2.840327872334009</v>
       </c>
     </row>
     <row r="1859">
@@ -44308,16 +44308,16 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.646323125273152</v>
+        <v>-4.677348815547288</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.265185859607776</v>
+        <v>1.252775583498121</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.7248150975963983</v>
+        <v>-0.6321021201568844</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.689182475472945</v>
+        <v>2.744810261936653</v>
       </c>
     </row>
     <row r="1860">
@@ -44331,16 +44331,16 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-4.972755654140896</v>
+        <v>-5.003781344415032</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.122897623062769</v>
+        <v>1.110487346953114</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.8072833481035464</v>
+        <v>-0.7145703706640325</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.627986300170747</v>
+        <v>2.683614086634455</v>
       </c>
     </row>
     <row r="1861">
@@ -44354,16 +44354,16 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.308418301371349</v>
+        <v>-5.339443991645484</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.9872131558265527</v>
+        <v>0.9748028797168984</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.8072833481035464</v>
+        <v>-0.7145703706640325</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.626566891826712</v>
+        <v>2.68219467829042</v>
       </c>
     </row>
     <row r="1862">
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.672044546271662</v>
+        <v>-5.703070236545797</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.8482502181006693</v>
+        <v>0.8358399419910145</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.9055049849706722</v>
+        <v>-0.8127920075311583</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.574121469940678</v>
+        <v>2.629749256404387</v>
       </c>
     </row>
     <row r="1863">
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.037171928910409</v>
+        <v>-6.068197619184544</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.7014537800510019</v>
+        <v>0.6890435039413472</v>
       </c>
       <c r="F1863" t="n">
-        <v>-1.201815769269685</v>
+        <v>-1.109102791830171</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.395589514367102</v>
+        <v>2.451217300830811</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.445760706091088</v>
+        <v>-6.476786396365223</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.5367798131934891</v>
+        <v>0.5243695370838348</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.610404546450363</v>
+        <v>-1.517691569010849</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.149197792073454</v>
+        <v>2.204825578537163</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.858743190232182</v>
+        <v>-6.889768880506317</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.3667722520085124</v>
+        <v>0.3543619758988577</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.610404546450363</v>
+        <v>-1.517691569010849</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.144383224544915</v>
+        <v>2.200011011008623</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.275135064519179</v>
+        <v>-7.306160754793314</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.1982095529025907</v>
+        <v>0.1857992767929364</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.610404546450363</v>
+        <v>-1.517691569010849</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.142377275153792</v>
+        <v>2.198005061617501</v>
       </c>
     </row>
     <row r="1867">
@@ -44492,16 +44492,16 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.651812075049023</v>
+        <v>-7.682837765323159</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.0577974393593319</v>
+        <v>0.04538716324967762</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.610404546450363</v>
+        <v>-1.517691569010849</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.152635965822471</v>
+        <v>2.20826375228618</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-7.997686897033832</v>
+        <v>-8.028712587307968</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.08445292428889628</v>
+        <v>-0.09686320039855056</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.610404546450363</v>
+        <v>-1.517691569010849</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.148735530968166</v>
+        <v>2.204363317431874</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.310511696278811</v>
+        <v>-8.341537386552947</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.2111779239318867</v>
+        <v>-0.2235882000415415</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.610404546450363</v>
+        <v>-1.517691569010849</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.147140451023167</v>
+        <v>2.202768237486875</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.607173038089009</v>
+        <v>-8.638198728363145</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.3260634847267578</v>
+        <v>-0.3384737608364126</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.679147682184242</v>
+        <v>-1.586434704744728</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.109673545512048</v>
+        <v>2.165301331975757</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-9.040522146199244</v>
+        <v>-9.07154783647338</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.5034294325052553</v>
+        <v>-0.5158397086149096</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.679147682184242</v>
+        <v>-1.586434704744728</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.105647240977645</v>
+        <v>2.161275027441353</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.423523534941875</v>
+        <v>-9.454549225216011</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.6567320893238917</v>
+        <v>-0.669142365433546</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.679147682184242</v>
+        <v>-1.586434704744728</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.105545139656061</v>
+        <v>2.161172926119769</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.798508861113152</v>
+        <v>-9.829534551387288</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.8041547038209722</v>
+        <v>-0.8165649799306269</v>
       </c>
       <c r="F1873" t="n">
-        <v>-2.054133008355519</v>
+        <v>-1.961420030916005</v>
       </c>
       <c r="G1873" t="n">
-        <v>1.883125459924725</v>
+        <v>1.938753246388433</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-10.15803918361715</v>
+        <v>-10.18906487389129</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.942616529524523</v>
+        <v>-0.9550268056341773</v>
       </c>
       <c r="F1874" t="n">
-        <v>-2.054133008355519</v>
+        <v>-1.961420030916005</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.888475763222775</v>
+        <v>1.944103549686483</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-10.48443921228217</v>
+        <v>-10.5154649025563</v>
       </c>
       <c r="E1875" t="n">
-        <v>-1.065260521033351</v>
+        <v>-1.077670797143005</v>
       </c>
       <c r="F1875" t="n">
-        <v>-2.380533037020532</v>
+        <v>-2.287820059581018</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.700551765980945</v>
+        <v>1.756179552444653</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.70358818035636</v>
+        <v>-10.7346138706305</v>
       </c>
       <c r="E1876" t="n">
-        <v>-1.14987835764126</v>
+        <v>-1.162288633750916</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.59968200509473</v>
+        <v>-2.506969027655216</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.572104135758195</v>
+        <v>1.627731922221903</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.69989725539995</v>
+        <v>-10.73092294567409</v>
       </c>
       <c r="E1877" t="n">
-        <v>-1.148401987658696</v>
+        <v>-1.160812263768351</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.59968200509473</v>
+        <v>-2.506969027655216</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.572104135758195</v>
+        <v>1.627731922221903</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.90415543072982</v>
+        <v>-10.93518112100395</v>
       </c>
       <c r="E1878" t="n">
-        <v>-1.224592060671999</v>
+        <v>-1.237002336781654</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.727320949708719</v>
+        <v>-2.634607972269205</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.501033966108444</v>
+        <v>1.556661752572152</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-11.12219320236099</v>
+        <v>-11.15321889263513</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.307324614840035</v>
+        <v>-1.319734890949689</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.902091717804617</v>
+        <v>-2.809378740365104</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.400654059735341</v>
+        <v>1.456281846199049</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-11.04872337069355</v>
+        <v>-11.07974906096768</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.262564980679634</v>
+        <v>-1.274975256789288</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.828621886137169</v>
+        <v>-2.735908908697655</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.460107660229231</v>
+        <v>1.515735446692939</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-11.22384778808009</v>
+        <v>-11.25487347835423</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.318059526886734</v>
+        <v>-1.330469802996388</v>
       </c>
       <c r="F1881" t="n">
-        <v>-3.003746303523713</v>
+        <v>-2.911033326084199</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.369588230544821</v>
+        <v>1.42521601700853</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-11.45829988209458</v>
+        <v>-11.48932557236872</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.419059529394126</v>
+        <v>-1.43146980550378</v>
       </c>
       <c r="F1882" t="n">
-        <v>-3.003746303523713</v>
+        <v>-2.911033326084199</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.362369065643225</v>
+        <v>1.417996852106934</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.74610372663182</v>
+        <v>-11.77712941690595</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.540853257982997</v>
+        <v>-1.553263534092653</v>
       </c>
       <c r="F1883" t="n">
-        <v>-3.291550148060951</v>
+        <v>-3.198837170621437</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.183014568146906</v>
+        <v>1.238642354610615</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-11.97592817379564</v>
+        <v>-12.00695386406978</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.631667247009972</v>
+        <v>-1.644077523119626</v>
       </c>
       <c r="F1884" t="n">
-        <v>-3.454197685131112</v>
+        <v>-3.361484707691598</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.086541835743366</v>
+        <v>1.142169622207075</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-12.2079570935319</v>
+        <v>-12.23898278380604</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.721785086275362</v>
+        <v>-1.734195362385016</v>
       </c>
       <c r="F1885" t="n">
-        <v>-3.516210382319535</v>
+        <v>-3.423497404880021</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.052027946059427</v>
+        <v>1.107655732523135</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-12.15594157956309</v>
+        <v>-12.18696726983723</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.696988545001435</v>
+        <v>-1.70939882111109</v>
       </c>
       <c r="F1886" t="n">
-        <v>-3.516210382319535</v>
+        <v>-3.423497404880021</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.056018281745828</v>
+        <v>1.111646068209536</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-12.29761342128721</v>
+        <v>-12.32863911156135</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.755132508589825</v>
+        <v>-1.76754278469948</v>
       </c>
       <c r="F1887" t="n">
-        <v>-3.516210382319535</v>
+        <v>-3.423497404880021</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.054543054847086</v>
+        <v>1.110170841310794</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-12.39652016174649</v>
+        <v>-12.42754585202062</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.779641794608664</v>
+        <v>-1.792052070718318</v>
       </c>
       <c r="F1888" t="n">
-        <v>-3.61511712277881</v>
+        <v>-3.522404145339296</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.010252420736393</v>
+        <v>1.065880207200101</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-12.19736805450939</v>
+        <v>-12.22839374478352</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.713032085360507</v>
+        <v>-1.725442361470161</v>
       </c>
       <c r="F1889" t="n">
-        <v>-3.449794596828997</v>
+        <v>-3.357081619389483</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.096394802659598</v>
+        <v>1.152022589123306</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-11.97152290178998</v>
+        <v>-12.00254859206411</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.613114951236534</v>
+        <v>-1.625525227346187</v>
       </c>
       <c r="F1890" t="n">
-        <v>-3.407867921241833</v>
+        <v>-3.31515494380232</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.131129881048105</v>
+        <v>1.186757667511813</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.68524808946728</v>
+        <v>-11.71627377974142</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.497465881751397</v>
+        <v>-1.509876157861051</v>
       </c>
       <c r="F1891" t="n">
-        <v>-3.407867921241833</v>
+        <v>-3.31515494380232</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.132269025604164</v>
+        <v>1.187896812067872</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.73814337751157</v>
+        <v>-11.7691690677857</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.515990222807004</v>
+        <v>-1.528400498916658</v>
       </c>
       <c r="F1892" t="n">
-        <v>-3.402912575153387</v>
+        <v>-3.310199597713873</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.137876007419339</v>
+        <v>1.193503793883048</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.45423464658282</v>
+        <v>-11.48526033685696</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.396693026196868</v>
+        <v>-1.409103302306522</v>
       </c>
       <c r="F1893" t="n">
-        <v>-3.402912575153387</v>
+        <v>-3.310199597713873</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.143609711657976</v>
+        <v>1.199237498121684</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-11.20724739638987</v>
+        <v>-11.238273086664</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.307635388513552</v>
+        <v>-1.320045664623207</v>
       </c>
       <c r="F1894" t="n">
-        <v>-3.155925324960435</v>
+        <v>-3.063212347520921</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.282064799379882</v>
+        <v>1.33769258584359</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.9434105291858</v>
+        <v>-10.97443621945993</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.211984122944832</v>
+        <v>-1.224394399054486</v>
       </c>
       <c r="F1895" t="n">
-        <v>-3.155925324960435</v>
+        <v>-3.063212347520921</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.272181318066974</v>
+        <v>1.327809104530682</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.6761687283174</v>
+        <v>-10.70719441859154</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.106921963096847</v>
+        <v>-1.1193322392065</v>
       </c>
       <c r="F1896" t="n">
-        <v>-3.155925324960435</v>
+        <v>-3.063212347520921</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.2703467575676</v>
+        <v>1.325974544031309</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.40035956491692</v>
+        <v>-10.43138525519105</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.996898612710114</v>
+        <v>-1.009308888819767</v>
       </c>
       <c r="F1897" t="n">
-        <v>-3.066906016681702</v>
+        <v>-2.974193039242188</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.32345802756138</v>
+        <v>1.379085814025088</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.37640602394096</v>
+        <v>-10.40743171421509</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.9866486901742371</v>
+        <v>-0.9990589662838905</v>
       </c>
       <c r="F1898" t="n">
-        <v>-3.042952475705744</v>
+        <v>-2.95023949826623</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.338498658292448</v>
+        <v>1.394126444756156</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.11234608561816</v>
+        <v>-10.1433717758923</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.89428503100687</v>
+        <v>-0.9066953071165242</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.778892537382948</v>
+        <v>-2.686179559943434</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.483674305124373</v>
+        <v>1.539302091588082</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.405266462113325</v>
+        <v>-9.436292152387459</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.6142402152652364</v>
+        <v>-0.6266504913748898</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.778892537382948</v>
+        <v>-2.686179559943434</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.480887271464072</v>
+        <v>1.536515057927781</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.365082163747134</v>
+        <v>-9.396107854021269</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.5978228720309189</v>
+        <v>-0.6102331481405723</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.738708239016757</v>
+        <v>-2.645995261577244</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.505341474371628</v>
+        <v>1.560969260835336</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.28501236820933</v>
+        <v>-9.316038058483464</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.56642813259504</v>
+        <v>-0.5788384087046938</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.658638443478953</v>
+        <v>-2.565925466039439</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.552750172915067</v>
+        <v>1.608377959378776</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-9.05153114597973</v>
+        <v>-9.082556836253865</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.465111214865348</v>
+        <v>-0.4775214909750014</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.425157221249355</v>
+        <v>-2.332444243809841</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.700763335090679</v>
+        <v>1.756391121554387</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.871822615835857</v>
+        <v>-8.902848306109991</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.3961200131207576</v>
+        <v>-0.4085302892304115</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.367985717086659</v>
+        <v>-2.275272739647145</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.732174027275337</v>
+        <v>1.787801813739046</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.73954714220497</v>
+        <v>-8.770572832479104</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.3478423369213757</v>
+        <v>-0.3602526130310295</v>
       </c>
       <c r="F1905" t="n">
-        <v>-2.235710243455773</v>
+        <v>-2.142997266016259</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.806906798200896</v>
+        <v>1.862534584664605</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.548947467531816</v>
+        <v>-8.57997315780595</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.2687874063644777</v>
+        <v>-0.2811976824741311</v>
       </c>
       <c r="F1906" t="n">
-        <v>-2.04511056878262</v>
+        <v>-1.952397591343106</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.924081663692425</v>
+        <v>1.979709450156133</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.299947668848235</v>
+        <v>-8.330973359122369</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.1562811456673865</v>
+        <v>-0.1686914217770403</v>
       </c>
       <c r="F1907" t="n">
-        <v>-2.04511056878262</v>
+        <v>-1.952397591343106</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.936988004916083</v>
+        <v>1.992615791379792</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.40553765862134</v>
+        <v>-8.436563348895474</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.3264930711758467</v>
+        <v>-0.3389033472855005</v>
       </c>
       <c r="F1908" t="n">
-        <v>-2.150700558555724</v>
+        <v>-2.05798758111621</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.745658081453002</v>
+        <v>1.801285867916711</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.424272560739936</v>
+        <v>-8.455298251014071</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.2854426901461995</v>
+        <v>-0.2978529662558529</v>
       </c>
       <c r="F1909" t="n">
-        <v>-2.150700558555724</v>
+        <v>-2.05798758111621</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.794202423330088</v>
+        <v>1.849830209793797</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>3.088001770449517</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.147534386069124</v>
+        <v>-8.178560076343258</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.1713684082918796</v>
+        <v>-0.1837786844015334</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.968883897445799</v>
+        <v>-1.876170920006284</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.906671431982039</v>
+        <v>1.962299218445747</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>3.079287784196039</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.020641979634053</v>
+        <v>-8.051667669908188</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.1293254319713295</v>
+        <v>-0.1417357080809833</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.841991491010729</v>
+        <v>-1.749278513571214</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.974092889589602</v>
+        <v>2.029720676053311</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>3.072327172100946</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.977093572863363</v>
+        <v>-8.008119263137498</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.1188666813581465</v>
+        <v>-0.1312769574678003</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.841991491010729</v>
+        <v>-1.749278513571214</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.967132277494509</v>
+        <v>2.022760063958218</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>3.086789526482089</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.734945179409505</v>
+        <v>-7.76597086968364</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.007544969595460138</v>
+        <v>-0.01995524570511398</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.841991491010729</v>
+        <v>-1.749278513571214</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.981594631875652</v>
+        <v>2.037222418339361</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>3.081321646941284</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.671715807641156</v>
+        <v>-7.702741497915292</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.01227889957107431</v>
+        <v>-0.0001313765385795307</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.841991491010729</v>
+        <v>-1.749278513571214</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.976126752334847</v>
+        <v>2.031754538798556</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>3.078819740951861</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.48522811526415</v>
+        <v>-7.516253805538286</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.08437207053245332</v>
+        <v>0.07196179442279949</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.655503798633722</v>
+        <v>-1.562790821194208</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.085517461771628</v>
+        <v>2.141145248235336</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>3.086520719189187</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.464078916360707</v>
+        <v>-7.495104606634842</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.1005327283311566</v>
+        <v>0.08812245222150272</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.634354599730279</v>
+        <v>-1.541641622290765</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.105907959351019</v>
+        <v>2.161535745814728</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>3.082301427536237</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.220313474377263</v>
+        <v>-7.251339164651398</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.1938196134715846</v>
+        <v>0.1814093373619312</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.634354599730279</v>
+        <v>-1.541641622290765</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.10168866769807</v>
+        <v>2.157316454161779</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>3.084425741456253</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.956285407184003</v>
+        <v>-6.987311097458138</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.3015551542689048</v>
+        <v>0.2891448781592509</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.432489200914326</v>
+        <v>-1.339776223474811</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.224932220907658</v>
+        <v>2.280560007371367</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>3.077167816439955</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.706435013234929</v>
+        <v>-6.737460703509064</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.3942373868322364</v>
+        <v>0.381827110722583</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.432489200914326</v>
+        <v>-1.339776223474811</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.21767429589136</v>
+        <v>2.273302082355069</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>3.080766939960604</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.40286752423095</v>
+        <v>-6.433893214505085</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.519263505954477</v>
+        <v>0.5068532298448232</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.432489200914326</v>
+        <v>-1.339776223474811</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.221273419412009</v>
+        <v>2.276901205875718</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>3.094094446015158</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.329387615378936</v>
+        <v>-6.360413305653071</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.561982975549836</v>
+        <v>0.5495726994401822</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.359009292062311</v>
+        <v>-1.266296314622797</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.278688870777771</v>
+        <v>2.33431665724148</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>3.093114923631455</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.104354615710113</v>
+        <v>-6.135380305984248</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.6510166530336621</v>
+        <v>0.6386063769240087</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.133976292393488</v>
+        <v>-1.041263314953974</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.412729148195362</v>
+        <v>2.468356934659071</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>3.097809724685772</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.889720238073706</v>
+        <v>-5.920745928347841</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.7415652051425425</v>
+        <v>0.7291549290328887</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.9193419147570814</v>
+        <v>-0.826628937317567</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.546204575831524</v>
+        <v>2.601832362295232</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>3.079003983469568</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.623119881099354</v>
+        <v>-5.65414557137349</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.8293996067160787</v>
+        <v>0.8169893306064249</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.9193419147570814</v>
+        <v>-0.826628937317567</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.527398834615319</v>
+        <v>2.583026621079028</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>3.080747060094445</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.382689384294494</v>
+        <v>-5.413715074568629</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.9273148820629</v>
+        <v>0.9149046059532466</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.6789114179522211</v>
+        <v>-0.5861984405127068</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.673400209323113</v>
+        <v>2.729027995786821</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>3.084676373929265</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.139898576645049</v>
+        <v>-5.170924266919184</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.028360518957498</v>
+        <v>1.015950242847845</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.6789114179522211</v>
+        <v>-0.5861984405127068</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.677329523157933</v>
+        <v>2.732957309621642</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>3.085354957846605</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.90029348503796</v>
+        <v>-4.931319175312095</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.124881139517674</v>
+        <v>1.11247086340802</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.6118634702837266</v>
+        <v>-0.5191504928442122</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.71823687567637</v>
+        <v>2.773864662140078</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>3.082353029066599</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.657637896614796</v>
+        <v>-4.688663586888931</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.218941446106933</v>
+        <v>1.206531169997279</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.6118634702837266</v>
+        <v>-0.5191504928442122</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.715234946896363</v>
+        <v>2.770862733360072</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>3.083932066077213</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.437617098577785</v>
+        <v>-4.468642788851921</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.308528802332352</v>
+        <v>1.296118526222698</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.4706436252157463</v>
+        <v>-0.377930647776232</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.801545890947765</v>
+        <v>2.857173677411474</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>3.099826248879036</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.238368468672976</v>
+        <v>-4.269394158947112</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.404122437096099</v>
+        <v>1.391712160986445</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.4706436252157463</v>
+        <v>-0.377930647776232</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.817440073749589</v>
+        <v>2.873067860213297</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>3.100972093319338</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.078853365153607</v>
+        <v>-4.109879055427742</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.469074322944148</v>
+        <v>1.456664046834494</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.3111285216963764</v>
+        <v>-0.218415544256862</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.914294980301512</v>
+        <v>2.969922766765221</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>3.111060195880778</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.934181220053869</v>
+        <v>-3.965206910328004</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.537031283545483</v>
+        <v>1.524621007435829</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.166456376596639</v>
+        <v>-0.07374339915712463</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.011186369922795</v>
+        <v>3.066814156386504</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.44594478142009</v>
+        <v>3.569387784790372</v>
       </c>
       <c r="C1933" t="n">
-        <v>2.922598507788897</v>
+        <v>2.928245287988333</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.934181220053869</v>
+        <v>-3.979297438538508</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.537031283545483</v>
+        <v>1.336169888259183</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.166456376596639</v>
+        <v>-0.08783392736762768</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.915662304775265</v>
+        <v>2.875544931567756</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240413.xlsx
+++ b/tame_output/ON/bt/strategyON_20240413.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>56.3%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>67.7%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.4%</t>
+          <t>-12.7%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>28.9%</t>
+          <t>21.0%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>69.7%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>29.9%</t>
+          <t>29.0%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>33.1%</t>
+          <t>31.3%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>16.0%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -819,12 +819,12 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-15.3%</t>
+          <t>-11.3%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-6.0%</t>
+          <t>-5.2%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-4.4%</t>
+          <t>-3.6%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>51.7%</t>
+          <t>56.1%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>23.7%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.4%</t>
+          <t>-4.7%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-18.8%</t>
+          <t>-9.0%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.5%</t>
+          <t>-79.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>119.1%</t>
+          <t>118.3%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>139.0%</t>
+          <t>138.4%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>97.7%</t>
+          <t>96.7%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>29.0%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-57.7%</t>
+          <t>-57.3%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.8%</t>
+          <t>-75.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>98.8%</t>
+          <t>98.1%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>671.2%</t>
+          <t>538.2%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-0.6%</t>
+          <t>2.7%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-559.5%</t>
+          <t>-563.2%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>11.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>55.3%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.9%</t>
+          <t>57.8%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>45.9%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,32 +1150,32 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>14.2%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-45.1%</t>
+          <t>-44.8%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>5.4%</t>
+          <t>8.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-18.2%</t>
+          <t>-20.7%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-181.9%</t>
+          <t>-68.6%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-242.6%</t>
+          <t>-234.3%</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-27.5%</t>
+          <t>-27.2%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>71.6%</t>
+          <t>71.7%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>70.2%</t>
+          <t>70.5%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-295.4%</t>
+          <t>-306.6%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-37.1%</t>
+          <t>-37.8%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-20.7%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>36.7%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-147.6%</t>
+          <t>-152.2%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-232.8%</t>
+          <t>-230.6%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>48.6%</t>
+          <t>52.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>51.6%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>64.8%</t>
+          <t>63.4%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>97.7%</t>
+          <t>97.9%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-177.7%</t>
+          <t>-184.4%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1466,32 +1466,32 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-32.0%</t>
+          <t>-32.6%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>42.4%</t>
+          <t>47.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.6%</t>
+          <t>43.1%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.3%</t>
+          <t>-17.1%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.1%</t>
+          <t>34.0%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-158.5%</t>
+          <t>-147.3%</t>
         </is>
       </c>
     </row>
@@ -43750,22 +43750,22 @@
         <v>45297</v>
       </c>
       <c r="B1835" t="n">
-        <v>3.320996253831153</v>
+        <v>3.320996253831154</v>
       </c>
       <c r="C1835" t="n">
         <v>3.138175778137954</v>
       </c>
       <c r="D1835" t="n">
-        <v>0.6128114976131679</v>
+        <v>0.8580776593093818</v>
       </c>
       <c r="E1835" t="n">
-        <v>3.382943952869474</v>
+        <v>3.48105041754796</v>
       </c>
       <c r="F1835" t="n">
-        <v>1.899967151891663</v>
+        <v>1.881174505190975</v>
       </c>
       <c r="G1835" t="n">
-        <v>4.278156069272953</v>
+        <v>4.26688048125254</v>
       </c>
     </row>
     <row r="1836">
@@ -43779,16 +43779,16 @@
         <v>3.118001050765402</v>
       </c>
       <c r="D1836" t="n">
-        <v>0.4760989193967312</v>
+        <v>0.7523907713670821</v>
       </c>
       <c r="E1836" t="n">
-        <v>3.308084194210347</v>
+        <v>3.418600934998487</v>
       </c>
       <c r="F1836" t="n">
-        <v>1.978119055628494</v>
+        <v>1.866613431488292</v>
       </c>
       <c r="G1836" t="n">
-        <v>4.304872484142498</v>
+        <v>4.237969109658377</v>
       </c>
     </row>
     <row r="1837">
@@ -43796,22 +43796,22 @@
         <v>45299</v>
       </c>
       <c r="B1837" t="n">
-        <v>3.385382209279814</v>
+        <v>3.385382209279813</v>
       </c>
       <c r="C1837" t="n">
         <v>3.118490189491276</v>
       </c>
       <c r="D1837" t="n">
-        <v>0.4819483005119756</v>
+        <v>0.5915988189611285</v>
       </c>
       <c r="E1837" t="n">
-        <v>3.310913085382319</v>
+        <v>3.35477329276198</v>
       </c>
       <c r="F1837" t="n">
-        <v>1.978119055628494</v>
+        <v>1.866613431488292</v>
       </c>
       <c r="G1837" t="n">
-        <v>4.305361622868372</v>
+        <v>4.238458248384251</v>
       </c>
     </row>
     <row r="1838">
@@ -43819,22 +43819,22 @@
         <v>45300</v>
       </c>
       <c r="B1838" t="n">
-        <v>3.367379938511405</v>
+        <v>3.367379938511404</v>
       </c>
       <c r="C1838" t="n">
         <v>3.122570172112943</v>
       </c>
       <c r="D1838" t="n">
-        <v>0.433726033664892</v>
+        <v>0.543376552114045</v>
       </c>
       <c r="E1838" t="n">
-        <v>3.295704161265152</v>
+        <v>3.339564368644814</v>
       </c>
       <c r="F1838" t="n">
-        <v>1.92989678878141</v>
+        <v>1.818391164641208</v>
       </c>
       <c r="G1838" t="n">
-        <v>4.280508245381789</v>
+        <v>4.213604870897668</v>
       </c>
     </row>
     <row r="1839">
@@ -43842,22 +43842,22 @@
         <v>45301</v>
       </c>
       <c r="B1839" t="n">
-        <v>3.376932391386094</v>
+        <v>3.376932391386093</v>
       </c>
       <c r="C1839" t="n">
         <v>3.157511256610484</v>
       </c>
       <c r="D1839" t="n">
-        <v>0.1965945418150969</v>
+        <v>0.3062450602642499</v>
       </c>
       <c r="E1839" t="n">
-        <v>3.235792649022776</v>
+        <v>3.279652856402437</v>
       </c>
       <c r="F1839" t="n">
-        <v>1.92989678878141</v>
+        <v>1.818391164641208</v>
       </c>
       <c r="G1839" t="n">
-        <v>4.31544932987933</v>
+        <v>4.24854595539521</v>
       </c>
     </row>
     <row r="1840">
@@ -43865,22 +43865,22 @@
         <v>45302</v>
       </c>
       <c r="B1840" t="n">
-        <v>3.367370539998561</v>
+        <v>3.36737053999856</v>
       </c>
       <c r="C1840" t="n">
         <v>3.156088696795822</v>
       </c>
       <c r="D1840" t="n">
-        <v>0.2016321325426835</v>
+        <v>0.3112826509918364</v>
       </c>
       <c r="E1840" t="n">
-        <v>3.236385125499149</v>
+        <v>3.28024533287881</v>
       </c>
       <c r="F1840" t="n">
-        <v>1.985541245047727</v>
+        <v>1.874035620907526</v>
       </c>
       <c r="G1840" t="n">
-        <v>4.347413443824458</v>
+        <v>4.280510069340338</v>
       </c>
     </row>
     <row r="1841">
@@ -43888,22 +43888,22 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082126</v>
+        <v>3.299560092082125</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
       </c>
       <c r="D1841" t="n">
-        <v>0.1451625013663867</v>
+        <v>0.2548130198155397</v>
       </c>
       <c r="E1841" t="n">
-        <v>3.192543654652367</v>
+        <v>3.236403862032028</v>
       </c>
       <c r="F1841" t="n">
-        <v>1.92907161387143</v>
+        <v>1.817565989731229</v>
       </c>
       <c r="G1841" t="n">
-        <v>4.292278046742418</v>
+        <v>4.225374672258297</v>
       </c>
     </row>
     <row r="1842">
@@ -43911,22 +43911,22 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.293490533757924</v>
+        <v>3.293490533757923</v>
       </c>
       <c r="C1842" t="n">
         <v>3.13585268755003</v>
       </c>
       <c r="D1842" t="n">
-        <v>0.07939511131697463</v>
+        <v>0.1890456297661276</v>
       </c>
       <c r="E1842" t="n">
-        <v>3.167254307763072</v>
+        <v>3.211114515142734</v>
       </c>
       <c r="F1842" t="n">
-        <v>1.92907161387143</v>
+        <v>1.817565989731229</v>
       </c>
       <c r="G1842" t="n">
-        <v>4.293295655872888</v>
+        <v>4.226392281388767</v>
       </c>
     </row>
     <row r="1843">
@@ -43934,22 +43934,22 @@
         <v>45305</v>
       </c>
       <c r="B1843" t="n">
-        <v>3.293766719760742</v>
+        <v>3.293766719760741</v>
       </c>
       <c r="C1843" t="n">
         <v>3.126480719537785</v>
       </c>
       <c r="D1843" t="n">
-        <v>0.06585962754026503</v>
+        <v>0.175510145989418</v>
       </c>
       <c r="E1843" t="n">
-        <v>3.152468146240144</v>
+        <v>3.196328353619805</v>
       </c>
       <c r="F1843" t="n">
-        <v>1.92907161387143</v>
+        <v>1.817565989731229</v>
       </c>
       <c r="G1843" t="n">
-        <v>4.283923687860644</v>
+        <v>4.217020313376523</v>
       </c>
     </row>
     <row r="1844">
@@ -43957,22 +43957,22 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.298730590706672</v>
+        <v>3.298730590706671</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
       </c>
       <c r="D1844" t="n">
-        <v>-0.01591227288748664</v>
+        <v>0.09373824556166632</v>
       </c>
       <c r="E1844" t="n">
-        <v>3.109842112024282</v>
+        <v>3.153702319403943</v>
       </c>
       <c r="F1844" t="n">
-        <v>1.956107187277567</v>
+        <v>1.844601563137365</v>
       </c>
       <c r="G1844" t="n">
-        <v>4.290227757859563</v>
+        <v>4.223324383375443</v>
       </c>
     </row>
     <row r="1845">
@@ -43980,22 +43980,22 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296839</v>
+        <v>3.299918119296838</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.08312138075936432</v>
+        <v>0.02652913768978865</v>
       </c>
       <c r="E1845" t="n">
-        <v>3.087723785709233</v>
+        <v>3.131583993088894</v>
       </c>
       <c r="F1845" t="n">
-        <v>1.956107187277567</v>
+        <v>1.844601563137365</v>
       </c>
       <c r="G1845" t="n">
-        <v>4.294993074693267</v>
+        <v>4.228089700209145</v>
       </c>
     </row>
     <row r="1846">
@@ -44009,16 +44009,16 @@
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-0.07912992796417412</v>
+        <v>0.03052059048497885</v>
       </c>
       <c r="E1846" t="n">
-        <v>3.087145162946549</v>
+        <v>3.131005370326211</v>
       </c>
       <c r="F1846" t="n">
-        <v>1.960098640072757</v>
+        <v>1.848593015932555</v>
       </c>
       <c r="G1846" t="n">
-        <v>4.29521274248962</v>
+        <v>4.228309368005499</v>
       </c>
     </row>
     <row r="1847">
@@ -44032,16 +44032,16 @@
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-0.4968839515110111</v>
+        <v>-0.3872334330618581</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.917970445032878</v>
+        <v>2.961830652412539</v>
       </c>
       <c r="F1847" t="n">
-        <v>1.54234461652592</v>
+        <v>1.430838992385719</v>
       </c>
       <c r="G1847" t="n">
-        <v>4.042487219866581</v>
+        <v>3.975583845382461</v>
       </c>
     </row>
     <row r="1848">
@@ -44055,16 +44055,16 @@
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-0.7185058850691286</v>
+        <v>-0.6088553666199756</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.829187888208553</v>
+        <v>2.873048095588214</v>
       </c>
       <c r="F1848" t="n">
-        <v>1.504818482838551</v>
+        <v>1.393312858698349</v>
       </c>
       <c r="G1848" t="n">
-        <v>4.019837756253082</v>
+        <v>3.952934381768961</v>
       </c>
     </row>
     <row r="1849">
@@ -44072,22 +44072,22 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382193</v>
+        <v>3.272760131382192</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-0.9265099434222058</v>
+        <v>-0.8168594249730529</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.750878409421247</v>
+        <v>2.794738616800908</v>
       </c>
       <c r="F1849" t="n">
-        <v>1.504818482838551</v>
+        <v>1.393312858698349</v>
       </c>
       <c r="G1849" t="n">
-        <v>4.024729900807007</v>
+        <v>3.957826526322886</v>
       </c>
     </row>
     <row r="1850">
@@ -44095,22 +44095,22 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074624</v>
+        <v>3.251475576074623</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.196909906131091</v>
+        <v>-1.087259387681938</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.637799880675681</v>
+        <v>2.681660088055342</v>
       </c>
       <c r="F1850" t="n">
-        <v>1.234418520129666</v>
+        <v>1.122912895989464</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.857571379519664</v>
+        <v>3.790668005035543</v>
       </c>
     </row>
     <row r="1851">
@@ -44118,22 +44118,22 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911641</v>
+        <v>3.233800325911639</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-1.536068283719613</v>
+        <v>-1.42641776527046</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.495220828946721</v>
+        <v>2.539081036326382</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.8952601425411435</v>
+        <v>0.783754518400942</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.647160652273</v>
+        <v>3.580257277788879</v>
       </c>
     </row>
     <row r="1852">
@@ -44141,22 +44141,22 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213497</v>
+        <v>3.223539378213496</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-1.864085505447092</v>
+        <v>-1.754434986997939</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.384352229994498</v>
+        <v>2.428212437374159</v>
       </c>
       <c r="F1852" t="n">
-        <v>0.5672429208136643</v>
+        <v>0.4557372966734629</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.470688608975281</v>
+        <v>3.40378523449116</v>
       </c>
     </row>
     <row r="1853">
@@ -44164,22 +44164,22 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416047</v>
+        <v>3.231167537416045</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.35741037698227</v>
+        <v>-2.247759858533118</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.195121031788995</v>
+        <v>2.238981239168656</v>
       </c>
       <c r="F1853" t="n">
-        <v>0.4622568065740456</v>
+        <v>0.3507511824338441</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.415795690840078</v>
+        <v>3.348892316355957</v>
       </c>
     </row>
     <row r="1854">
@@ -44187,22 +44187,22 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.23598197738233</v>
+        <v>3.235981977382329</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-2.849795405006367</v>
+        <v>-2.740144886557215</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.999273412623088</v>
+        <v>2.04313362000275</v>
       </c>
       <c r="F1854" t="n">
-        <v>-0.03012822145005112</v>
+        <v>-0.1416338455902526</v>
       </c>
       <c r="G1854" t="n">
-        <v>3.121471066069352</v>
+        <v>3.054567691585231</v>
       </c>
     </row>
     <row r="1855">
@@ -44210,22 +44210,22 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495501</v>
+        <v>3.278199702495499</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.234975795936439</v>
+        <v>-3.125325277487287</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.843743795063923</v>
+        <v>1.887604002443584</v>
       </c>
       <c r="F1855" t="n">
-        <v>-0.03012822145005112</v>
+        <v>-0.1416338455902526</v>
       </c>
       <c r="G1855" t="n">
-        <v>3.120013604882216</v>
+        <v>3.053110230398095</v>
       </c>
     </row>
     <row r="1856">
@@ -44233,22 +44233,22 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347057</v>
+        <v>3.299136146347054</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-3.578658569163102</v>
+        <v>-3.46900805071395</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.708039809227874</v>
+        <v>1.751900016607535</v>
       </c>
       <c r="F1856" t="n">
-        <v>-0.1380342734772693</v>
+        <v>-0.2495398976174708</v>
       </c>
       <c r="G1856" t="n">
-        <v>3.057039097120501</v>
+        <v>2.99013572263638</v>
       </c>
     </row>
     <row r="1857">
@@ -44256,22 +44256,22 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130019</v>
+        <v>3.287377576130016</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-3.93630891940145</v>
+        <v>-3.826658400952298</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.561085727788792</v>
+        <v>1.604945935168453</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.4956846237156174</v>
+        <v>-0.6071902478558189</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.83855494563375</v>
+        <v>2.771651571149629</v>
       </c>
     </row>
     <row r="1858">
@@ -44279,22 +44279,22 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178246</v>
+        <v>3.315884374178243</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.2455430223975</v>
+        <v>-4.135892503948349</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.439165013290632</v>
+        <v>1.483025220670293</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.4956846237156174</v>
+        <v>-0.6071902478558189</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.840327872334009</v>
+        <v>2.773424497849888</v>
       </c>
     </row>
     <row r="1859">
@@ -44302,22 +44302,22 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207815</v>
+        <v>3.305316798207812</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.677348815547288</v>
+        <v>-4.567698297098136</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.252775583498121</v>
+        <v>1.296635790877782</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.6321021201568844</v>
+        <v>-0.7436077442970859</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.744810261936653</v>
+        <v>2.677906887452532</v>
       </c>
     </row>
     <row r="1860">
@@ -44325,22 +44325,22 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310984</v>
+        <v>3.28461951331098</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.003781344415032</v>
+        <v>-4.89413082596588</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.110487346953114</v>
+        <v>1.154347554332775</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.7145703706640325</v>
+        <v>-0.826075994804234</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.683614086634455</v>
+        <v>2.616710712150335</v>
       </c>
     </row>
     <row r="1861">
@@ -44348,22 +44348,22 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006534</v>
+        <v>3.305849539006531</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.339443991645484</v>
+        <v>-5.229793473196333</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.9748028797168984</v>
+        <v>1.018663087096559</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.7145703706640325</v>
+        <v>-0.826075994804234</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.68219467829042</v>
+        <v>2.6152913038063</v>
       </c>
     </row>
     <row r="1862">
@@ -44371,22 +44371,22 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309426</v>
+        <v>3.311086391309422</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.703070236545797</v>
+        <v>-5.593419718096646</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.8358399419910145</v>
+        <v>0.8797001493706755</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.8127920075311583</v>
+        <v>-0.9242976316713598</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.629749256404387</v>
+        <v>2.562845881920266</v>
       </c>
     </row>
     <row r="1863">
@@ -44394,22 +44394,22 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970907</v>
+        <v>3.304715716970902</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.068197619184544</v>
+        <v>-5.958547100735393</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.6890435039413472</v>
+        <v>0.7329037113210082</v>
       </c>
       <c r="F1863" t="n">
-        <v>-1.109102791830171</v>
+        <v>-1.220608415970372</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.451217300830811</v>
+        <v>2.38431392634669</v>
       </c>
     </row>
     <row r="1864">
@@ -44417,22 +44417,22 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330524</v>
+        <v>3.30081581833052</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.476786396365223</v>
+        <v>-6.367135877916072</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.5243695370838348</v>
+        <v>0.5682297444634958</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.517691569010849</v>
+        <v>-1.629197193151051</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.204825578537163</v>
+        <v>2.137922204053042</v>
       </c>
     </row>
     <row r="1865">
@@ -44440,22 +44440,22 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.30261819419174</v>
+        <v>3.302618194191735</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.889768880506317</v>
+        <v>-6.780118362057165</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.3543619758988577</v>
+        <v>0.3982221832785187</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.517691569010849</v>
+        <v>-1.629197193151051</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.200011011008623</v>
+        <v>2.133107636524502</v>
       </c>
     </row>
     <row r="1866">
@@ -44463,22 +44463,22 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108642</v>
+        <v>3.305023265108638</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.306160754793314</v>
+        <v>-7.196510236344163</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.1857992767929364</v>
+        <v>0.229659484172597</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.517691569010849</v>
+        <v>-1.629197193151051</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.198005061617501</v>
+        <v>2.13110168713338</v>
       </c>
     </row>
     <row r="1867">
@@ -44486,22 +44486,22 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097824</v>
+        <v>3.341378723097819</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.682837765323159</v>
+        <v>-7.573187246874007</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.04538716324967762</v>
+        <v>0.08924737062933819</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.517691569010849</v>
+        <v>-1.629197193151051</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.20826375228618</v>
+        <v>2.141360377802059</v>
       </c>
     </row>
     <row r="1868">
@@ -44509,22 +44509,22 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.37443904309412</v>
+        <v>3.374439043094116</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.028712587307968</v>
+        <v>-7.919062068858816</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.09686320039855056</v>
+        <v>-0.05300299301889</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.517691569010849</v>
+        <v>-1.629197193151051</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.204363317431874</v>
+        <v>2.137459942947754</v>
       </c>
     </row>
     <row r="1869">
@@ -44532,22 +44532,22 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199289</v>
+        <v>3.405960511199285</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.341537386552947</v>
+        <v>-8.231886868103794</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.2235882000415415</v>
+        <v>-0.1797279926618804</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.517691569010849</v>
+        <v>-1.629197193151051</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.202768237486875</v>
+        <v>2.135864863002755</v>
       </c>
     </row>
     <row r="1870">
@@ -44555,22 +44555,22 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969597</v>
+        <v>3.424633354969592</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.638198728363145</v>
+        <v>-8.528548209913993</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.3384737608364126</v>
+        <v>-0.2946135534567516</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.586434704744728</v>
+        <v>-1.697940328884929</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.165301331975757</v>
+        <v>2.098397957491636</v>
       </c>
     </row>
     <row r="1871">
@@ -44578,22 +44578,22 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.41997943392309</v>
+        <v>3.419979433923086</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-9.07154783647338</v>
+        <v>-8.961897318024228</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.5158397086149096</v>
+        <v>-0.4719795012352486</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.586434704744728</v>
+        <v>-1.697940328884929</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.161275027441353</v>
+        <v>2.094371652957232</v>
       </c>
     </row>
     <row r="1872">
@@ -44601,22 +44601,22 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297753</v>
+        <v>3.458100091297749</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.454549225216011</v>
+        <v>-9.344898706766859</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.669142365433546</v>
+        <v>-0.625282158053885</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.586434704744728</v>
+        <v>-1.697940328884929</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.161172926119769</v>
+        <v>2.094269551635648</v>
       </c>
     </row>
     <row r="1873">
@@ -44624,22 +44624,22 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.44775050131762</v>
+        <v>3.447750501317616</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.829534551387288</v>
+        <v>-9.719884032938136</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.8165649799306269</v>
+        <v>-0.7727047725509659</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.961420030916005</v>
+        <v>-2.072925655056207</v>
       </c>
       <c r="G1873" t="n">
-        <v>1.938753246388433</v>
+        <v>1.871849871904312</v>
       </c>
     </row>
     <row r="1874">
@@ -44647,22 +44647,22 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737174</v>
+        <v>3.503515506737169</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-10.18906487389129</v>
+        <v>-10.07941435544214</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.9550268056341773</v>
+        <v>-0.9111665982545167</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.961420030916005</v>
+        <v>-2.072925655056207</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.944103549686483</v>
+        <v>1.877200175202362</v>
       </c>
     </row>
     <row r="1875">
@@ -44670,22 +44670,22 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341316</v>
+        <v>3.503170282341312</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-10.5154649025563</v>
+        <v>-10.40581438410715</v>
       </c>
       <c r="E1875" t="n">
-        <v>-1.077670797143005</v>
+        <v>-1.033810589763344</v>
       </c>
       <c r="F1875" t="n">
-        <v>-2.287820059581018</v>
+        <v>-2.39932568372122</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.756179552444653</v>
+        <v>1.689276177960532</v>
       </c>
     </row>
     <row r="1876">
@@ -44693,22 +44693,22 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.50044609677668</v>
+        <v>3.500446096776676</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.7346138706305</v>
+        <v>-10.62496335218135</v>
       </c>
       <c r="E1876" t="n">
-        <v>-1.162288633750916</v>
+        <v>-1.118428426371254</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.506969027655216</v>
+        <v>-2.618474651795417</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.627731922221903</v>
+        <v>1.560828547737782</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,22 +44716,22 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407494</v>
+        <v>3.492445136407492</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.73092294567409</v>
+        <v>-10.62127242722494</v>
       </c>
       <c r="E1877" t="n">
-        <v>-1.160812263768351</v>
+        <v>-1.11695205638869</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.506969027655216</v>
+        <v>-2.618474651795417</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.627731922221903</v>
+        <v>1.560828547737782</v>
       </c>
     </row>
     <row r="1878">
@@ -44739,22 +44739,22 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611697</v>
+        <v>3.502786823611694</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.93518112100395</v>
+        <v>-10.8255306025548</v>
       </c>
       <c r="E1878" t="n">
-        <v>-1.237002336781654</v>
+        <v>-1.193142129401993</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.634607972269205</v>
+        <v>-2.746113596409406</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.556661752572152</v>
+        <v>1.489758378088031</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199886</v>
+        <v>3.496848329199884</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-11.15321889263513</v>
+        <v>-11.04356837418598</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.319734890949689</v>
+        <v>-1.275874683570028</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.809378740365104</v>
+        <v>-2.920884364505305</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.456281846199049</v>
+        <v>1.389378471714928</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910629</v>
+        <v>3.499968163910626</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-11.07974906096768</v>
+        <v>-10.97009854251853</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.274975256789288</v>
+        <v>-1.231115049409627</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.735908908697655</v>
+        <v>-2.847414532837857</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.515735446692939</v>
+        <v>1.448832072208818</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078597</v>
+        <v>3.490055666078593</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-11.25487347835423</v>
+        <v>-11.14522295990507</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.330469802996388</v>
+        <v>-1.286609595616728</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.911033326084199</v>
+        <v>-3.0225389502244</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.42521601700853</v>
+        <v>1.358312642524409</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880269</v>
+        <v>3.485875018880265</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-11.48932557236872</v>
+        <v>-11.37967505391956</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.43146980550378</v>
+        <v>-1.38760959812412</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.911033326084199</v>
+        <v>-3.0225389502244</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.417996852106934</v>
+        <v>1.351093477622813</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234395</v>
+        <v>3.48068891723439</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.77712941690595</v>
+        <v>-11.6674788984568</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.553263534092653</v>
+        <v>-1.509403326712991</v>
       </c>
       <c r="F1883" t="n">
-        <v>-3.198837170621437</v>
+        <v>-3.310342794761639</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.238642354610615</v>
+        <v>1.171738980126494</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860584</v>
+        <v>3.49371243886058</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-12.00695386406978</v>
+        <v>-11.89730334562063</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.644077523119626</v>
+        <v>-1.600217315739965</v>
       </c>
       <c r="F1884" t="n">
-        <v>-3.361484707691598</v>
+        <v>-3.472990331831799</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.142169622207075</v>
+        <v>1.075266247722954</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767398</v>
+        <v>3.492098065767394</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-12.23898278380604</v>
+        <v>-12.12933226535689</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.734195362385016</v>
+        <v>-1.690335155005355</v>
       </c>
       <c r="F1885" t="n">
-        <v>-3.423497404880021</v>
+        <v>-3.535003029020222</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.107655732523135</v>
+        <v>1.040752358039014</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792542</v>
+        <v>3.573670449792538</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-12.18696726983723</v>
+        <v>-12.07731675138808</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.70939882111109</v>
+        <v>-1.665538613731429</v>
       </c>
       <c r="F1886" t="n">
-        <v>-3.423497404880021</v>
+        <v>-3.535003029020222</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.111646068209536</v>
+        <v>1.044742693725415</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628919</v>
+        <v>3.600034689628916</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-12.32863911156135</v>
+        <v>-12.2189885931122</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.76754278469948</v>
+        <v>-1.723682577319819</v>
       </c>
       <c r="F1887" t="n">
-        <v>-3.423497404880021</v>
+        <v>-3.535003029020222</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.110170841310794</v>
+        <v>1.043267466826673</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410717</v>
+        <v>3.691568158410714</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-12.42754585202062</v>
+        <v>-12.31789533357147</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.792052070718318</v>
+        <v>-1.748191863338657</v>
       </c>
       <c r="F1888" t="n">
-        <v>-3.522404145339296</v>
+        <v>-3.633909769479498</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.065880207200101</v>
+        <v>0.9989768327159809</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240577</v>
+        <v>3.676837974240573</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-12.22839374478352</v>
+        <v>-12.11874322633437</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.725442361470161</v>
+        <v>-1.6815821540905</v>
       </c>
       <c r="F1889" t="n">
-        <v>-3.357081619389483</v>
+        <v>-3.468587243529684</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.152022589123306</v>
+        <v>1.085119214639186</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085279</v>
+        <v>3.685157806085276</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-12.00254859206411</v>
+        <v>-11.89289807361496</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.625525227346187</v>
+        <v>-1.581665019966528</v>
       </c>
       <c r="F1890" t="n">
-        <v>-3.31515494380232</v>
+        <v>-3.426660567942521</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.186757667511813</v>
+        <v>1.119854293027692</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.6848402482821</v>
+        <v>3.684840248282097</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.71627377974142</v>
+        <v>-11.60662326129227</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.509876157861051</v>
+        <v>-1.466015950481391</v>
       </c>
       <c r="F1891" t="n">
-        <v>-3.31515494380232</v>
+        <v>-3.426660567942521</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.187896812067872</v>
+        <v>1.120993437583751</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116215</v>
+        <v>3.710931958116212</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.7691690677857</v>
+        <v>-11.65951854933655</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.528400498916658</v>
+        <v>-1.484540291536997</v>
       </c>
       <c r="F1892" t="n">
-        <v>-3.310199597713873</v>
+        <v>-3.421705221854074</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.193503793883048</v>
+        <v>1.126600419398927</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081567</v>
+        <v>3.768948099081563</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.48526033685696</v>
+        <v>-11.3756098184078</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.409103302306522</v>
+        <v>-1.365243094926861</v>
       </c>
       <c r="F1893" t="n">
-        <v>-3.310199597713873</v>
+        <v>-3.421705221854074</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.199237498121684</v>
+        <v>1.132334123637563</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425326</v>
+        <v>3.728574354425324</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-11.238273086664</v>
+        <v>-11.12862256821485</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.320045664623207</v>
+        <v>-1.276185457243546</v>
       </c>
       <c r="F1894" t="n">
-        <v>-3.063212347520921</v>
+        <v>-3.174717971661122</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.33769258584359</v>
+        <v>1.270789211359469</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702411</v>
+        <v>3.747699084702408</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.97443621945993</v>
+        <v>-10.86478570101078</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.224394399054486</v>
+        <v>-1.180534191674826</v>
       </c>
       <c r="F1895" t="n">
-        <v>-3.063212347520921</v>
+        <v>-3.174717971661122</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.327809104530682</v>
+        <v>1.260905730046562</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906227</v>
+        <v>3.766313503906224</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.70719441859154</v>
+        <v>-10.59754390014239</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.1193322392065</v>
+        <v>-1.075472031826841</v>
       </c>
       <c r="F1896" t="n">
-        <v>-3.063212347520921</v>
+        <v>-3.174717971661122</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.325974544031309</v>
+        <v>1.259071169547188</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781949</v>
+        <v>3.784680945781945</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.43138525519105</v>
+        <v>-10.3217347367419</v>
       </c>
       <c r="E1897" t="n">
-        <v>-1.009308888819767</v>
+        <v>-0.9654486814401069</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.974193039242188</v>
+        <v>-3.085698663382389</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.379085814025088</v>
+        <v>1.312182439540967</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567244</v>
+        <v>3.800825778567241</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.40743171421509</v>
+        <v>-10.29778119576594</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.9990589662838905</v>
+        <v>-0.9551987589042308</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.95023949826623</v>
+        <v>-3.061745122406431</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.394126444756156</v>
+        <v>1.327223070272036</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487774</v>
+        <v>3.78930753648777</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.1433717758923</v>
+        <v>-10.03372125744315</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.9066953071165242</v>
+        <v>-0.8628350997368637</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.686179559943434</v>
+        <v>-2.797685184083635</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.539302091588082</v>
+        <v>1.472398717103961</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309727</v>
+        <v>3.833249172309722</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.436292152387459</v>
+        <v>-9.326641633938308</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.6266504913748898</v>
+        <v>-0.5827902839952297</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.686179559943434</v>
+        <v>-2.797685184083635</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.536515057927781</v>
+        <v>1.46961168344366</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.83937087185873</v>
+        <v>3.839370871858726</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.396107854021269</v>
+        <v>-9.286457335572118</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.6102331481405723</v>
+        <v>-0.5663729407609122</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.645995261577244</v>
+        <v>-2.757500885717445</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.560969260835336</v>
+        <v>1.494065886351216</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096476</v>
+        <v>3.856158176096471</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.316038058483464</v>
+        <v>-9.206387540034314</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.5788384087046938</v>
+        <v>-0.5349782013250337</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.565925466039439</v>
+        <v>-2.677431090179641</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.608377959378776</v>
+        <v>1.541474584894655</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761809</v>
+        <v>3.787326853761805</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-9.082556836253865</v>
+        <v>-8.972906317804714</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.4775214909750014</v>
+        <v>-0.4336612835953413</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.332444243809841</v>
+        <v>-2.443949867950042</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.756391121554387</v>
+        <v>1.689487747070267</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255786</v>
+        <v>3.801633547255783</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.902848306109991</v>
+        <v>-8.793197787660841</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.4085302892304115</v>
+        <v>-0.3646700818507513</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.275272739647145</v>
+        <v>-2.386778363787346</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.787801813739046</v>
+        <v>1.720898439254925</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860428</v>
+        <v>3.763178672860423</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.770572832479104</v>
+        <v>-8.660922314029953</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.3602526130310295</v>
+        <v>-0.3163924056513694</v>
       </c>
       <c r="F1905" t="n">
-        <v>-2.142997266016259</v>
+        <v>-2.25450289015646</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.862534584664605</v>
+        <v>1.795631210180484</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575954</v>
+        <v>3.784715218575949</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.57997315780595</v>
+        <v>-8.4703226393568</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.2811976824741311</v>
+        <v>-0.237337475094471</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.952397591343106</v>
+        <v>-2.063903215483307</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.979709450156133</v>
+        <v>1.912806075672012</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430989</v>
+        <v>3.753878996430984</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.330973359122369</v>
+        <v>-8.221322840673219</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.1686914217770403</v>
+        <v>-0.1248312143973798</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.952397591343106</v>
+        <v>-2.063903215483307</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.992615791379792</v>
+        <v>1.925712416895671</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077646</v>
+        <v>3.692928280077641</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.436563348895474</v>
+        <v>-8.326912830446323</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.3389033472855005</v>
+        <v>-0.2950431399058404</v>
       </c>
       <c r="F1908" t="n">
-        <v>-2.05798758111621</v>
+        <v>-2.169493205256412</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.801285867916711</v>
+        <v>1.73438249343259</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457903</v>
+        <v>3.770419008457899</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.455298251014071</v>
+        <v>-8.34564773256492</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.2978529662558529</v>
+        <v>-0.2539927588761928</v>
       </c>
       <c r="F1909" t="n">
-        <v>-2.05798758111621</v>
+        <v>-2.169493205256412</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.849830209793797</v>
+        <v>1.782926835309676</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180811</v>
+        <v>3.760330111180807</v>
       </c>
       <c r="C1910" t="n">
         <v>3.088001770449517</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.178560076343258</v>
+        <v>-8.068909557894107</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.1837786844015334</v>
+        <v>-0.1399184770218729</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.876170920006284</v>
+        <v>-1.987676544146486</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.962299218445747</v>
+        <v>1.895395843961626</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879204</v>
+        <v>3.723562653879201</v>
       </c>
       <c r="C1911" t="n">
         <v>3.079287784196039</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.051667669908188</v>
+        <v>-7.942017151459037</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.1417357080809833</v>
+        <v>-0.09787550070132323</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.749278513571214</v>
+        <v>-1.860784137711416</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.029720676053311</v>
+        <v>1.96281730156919</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568108</v>
+        <v>3.729966140568105</v>
       </c>
       <c r="C1912" t="n">
         <v>3.072327172100946</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.008119263137498</v>
+        <v>-7.898468744688347</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.1312769574678003</v>
+        <v>-0.0874167500881402</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.749278513571214</v>
+        <v>-1.860784137711416</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.022760063958218</v>
+        <v>1.955856689474097</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.78291895796342</v>
+        <v>3.782918957963416</v>
       </c>
       <c r="C1913" t="n">
         <v>3.086789526482089</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.76597086968364</v>
+        <v>-7.825299627723254</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.01995524570511398</v>
+        <v>-0.04368674892096003</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.749278513571214</v>
+        <v>-1.860784137711416</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.037222418339361</v>
+        <v>1.97031904385524</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192818</v>
+        <v>3.828547911192812</v>
       </c>
       <c r="C1914" t="n">
         <v>3.081321646941284</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.702741497915292</v>
+        <v>-7.762070255954906</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.0001313765385795307</v>
+        <v>-0.02386287975442558</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.749278513571214</v>
+        <v>-1.860784137711416</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.031754538798556</v>
+        <v>1.964851164314435</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262048</v>
+        <v>3.828049353262043</v>
       </c>
       <c r="C1915" t="n">
         <v>3.078819740951861</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.516253805538286</v>
+        <v>-7.5755825635779</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.07196179442279949</v>
+        <v>0.04823029120695388</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.562790821194208</v>
+        <v>-1.67429644533441</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.141145248235336</v>
+        <v>2.074241873751216</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.81245010338991</v>
+        <v>3.812450103389905</v>
       </c>
       <c r="C1916" t="n">
         <v>3.086520719189187</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.495104606634842</v>
+        <v>-7.554433364674456</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.08812245222150272</v>
+        <v>0.06439094900565667</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.541641622290765</v>
+        <v>-1.653147246430966</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.161535745814728</v>
+        <v>2.094632371330607</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788095</v>
+        <v>3.748324832788089</v>
       </c>
       <c r="C1917" t="n">
         <v>3.082301427536237</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.251339164651398</v>
+        <v>-7.310667922691012</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.1814093373619312</v>
+        <v>0.1576778341460852</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.541641622290765</v>
+        <v>-1.653147246430966</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.157316454161779</v>
+        <v>2.090413079677658</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527527</v>
+        <v>3.824307657527521</v>
       </c>
       <c r="C1918" t="n">
         <v>3.084425741456253</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.987311097458138</v>
+        <v>-7.046639855497752</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.2891448781592509</v>
+        <v>0.2654133749434053</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.339776223474811</v>
+        <v>-1.451281847615013</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.280560007371367</v>
+        <v>2.213656632887246</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749186</v>
+        <v>3.82635139874918</v>
       </c>
       <c r="C1919" t="n">
         <v>3.077167816439955</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.737460703509064</v>
+        <v>-6.796789461548677</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.381827110722583</v>
+        <v>0.3580956075067374</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.339776223474811</v>
+        <v>-1.451281847615013</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.273302082355069</v>
+        <v>2.206398707870948</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481499</v>
+        <v>3.835954411481493</v>
       </c>
       <c r="C1920" t="n">
         <v>3.080766939960604</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.433893214505085</v>
+        <v>-6.493221972544698</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.5068532298448232</v>
+        <v>0.4831217266289776</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.339776223474811</v>
+        <v>-1.451281847615013</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.276901205875718</v>
+        <v>2.209997831391597</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862988</v>
+        <v>3.780930335862982</v>
       </c>
       <c r="C1921" t="n">
         <v>3.094094446015158</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.360413305653071</v>
+        <v>-6.419742063692684</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.5495726994401822</v>
+        <v>0.5258411962243366</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.266296314622797</v>
+        <v>-1.377801938762998</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.33431665724148</v>
+        <v>2.267413282757359</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102783</v>
+        <v>3.773761647102777</v>
       </c>
       <c r="C1922" t="n">
         <v>3.093114923631455</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.135380305984248</v>
+        <v>-6.194709064023861</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.6386063769240087</v>
+        <v>0.6148748737081631</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.041263314953974</v>
+        <v>-1.152768939094175</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.468356934659071</v>
+        <v>2.40145356017495</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353077</v>
+        <v>3.76461430435307</v>
       </c>
       <c r="C1923" t="n">
         <v>3.097809724685772</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.920745928347841</v>
+        <v>-5.980074686387455</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.7291549290328887</v>
+        <v>0.7054234258170431</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.826628937317567</v>
+        <v>-0.9381345614577685</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.601832362295232</v>
+        <v>2.534928987811111</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544785</v>
+        <v>3.798811195544778</v>
       </c>
       <c r="C1924" t="n">
         <v>3.079003983469568</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.65414557137349</v>
+        <v>-5.713474329413103</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.8169893306064249</v>
+        <v>0.7932578273905793</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.826628937317567</v>
+        <v>-0.9381345614577685</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.583026621079028</v>
+        <v>2.516123246594907</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712297</v>
+        <v>3.79769130871229</v>
       </c>
       <c r="C1925" t="n">
         <v>3.080747060094445</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.413715074568629</v>
+        <v>-5.473043832608242</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.9149046059532466</v>
+        <v>0.891173102737401</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.5861984405127068</v>
+        <v>-0.6977040646529082</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.729027995786821</v>
+        <v>2.6621246213027</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837688</v>
+        <v>3.82158993383768</v>
       </c>
       <c r="C1926" t="n">
         <v>3.084676373929265</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.170924266919184</v>
+        <v>-5.230253024958797</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.015950242847845</v>
+        <v>0.992218739631999</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.5861984405127068</v>
+        <v>-0.6977040646529082</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.732957309621642</v>
+        <v>2.666053935137521</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349969</v>
+        <v>3.822323422349962</v>
       </c>
       <c r="C1927" t="n">
         <v>3.085354957846605</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.931319175312095</v>
+        <v>-4.990647933351708</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.11247086340802</v>
+        <v>1.088739360192175</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.5191504928442122</v>
+        <v>-0.6306561169844137</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.773864662140078</v>
+        <v>2.706961287655957</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972342</v>
+        <v>3.848613050972335</v>
       </c>
       <c r="C1928" t="n">
         <v>3.082353029066599</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.688663586888931</v>
+        <v>-4.747992344928544</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.206531169997279</v>
+        <v>1.182799666781434</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.5191504928442122</v>
+        <v>-0.6306561169844137</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.770862733360072</v>
+        <v>2.703959358875951</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145942</v>
+        <v>3.818665376145935</v>
       </c>
       <c r="C1929" t="n">
         <v>3.083932066077213</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.468642788851921</v>
+        <v>-4.527971546891534</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.296118526222698</v>
+        <v>1.272387023006852</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.377930647776232</v>
+        <v>-0.4894362719164335</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.857173677411474</v>
+        <v>2.790270302927353</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009954</v>
+        <v>3.843270952009947</v>
       </c>
       <c r="C1930" t="n">
         <v>3.099826248879036</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.269394158947112</v>
+        <v>-4.328722916986725</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.391712160986445</v>
+        <v>1.367980657770599</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.377930647776232</v>
+        <v>-0.4894362719164335</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.873067860213297</v>
+        <v>2.806164485729176</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.84504381096626</v>
+        <v>3.845043810966255</v>
       </c>
       <c r="C1931" t="n">
         <v>3.100972093319338</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.109879055427742</v>
+        <v>-4.169207813467355</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.456664046834494</v>
+        <v>1.432932543618649</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.218415544256862</v>
+        <v>-0.3299211683970635</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.969922766765221</v>
+        <v>2.9030193922811</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046996</v>
+        <v>3.791269976046991</v>
       </c>
       <c r="C1932" t="n">
         <v>3.111060195880778</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.965206910328004</v>
+        <v>-4.024535668367617</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.524621007435829</v>
+        <v>1.500889504219984</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.07374339915712463</v>
+        <v>-0.1852490232973261</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.066814156386504</v>
+        <v>2.999910781902383</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.569387784790372</v>
+        <v>3.490356567803609</v>
       </c>
       <c r="C1933" t="n">
-        <v>2.928245287988333</v>
+        <v>3.0263998879675</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.979297438538508</v>
+        <v>-4.016285040644376</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.336169888259183</v>
+        <v>1.419529447396002</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.08783392736762768</v>
+        <v>-0.0660415925914643</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.875544931567756</v>
+        <v>2.986774932412621</v>
       </c>
     </row>
   </sheetData>
